--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -483,10 +483,10 @@
         <v>-0.019</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -510,10 +510,10 @@
         <v>-0.037</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.038</v>
+        <v>-0.037</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.001000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.045</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.029</v>
+        <v>-0.014</v>
       </c>
       <c r="E4" t="n">
-        <v>0.016</v>
+        <v>-0.002</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.061</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.044</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.017</v>
+        <v>0.035</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -591,10 +591,10 @@
         <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -645,10 +645,10 @@
         <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -672,10 +672,10 @@
         <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -699,10 +699,10 @@
         <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.041</v>
+        <v>-0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03299999999999999</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -726,10 +726,10 @@
         <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -753,10 +753,10 @@
         <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.017</v>
+        <v>-0.018</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -807,10 +807,10 @@
         <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.039</v>
+        <v>0.038</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -834,10 +834,10 @@
         <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.012</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -861,10 +861,10 @@
         <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.005999999999999998</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -888,10 +888,10 @@
         <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>-0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -915,10 +915,10 @@
         <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -969,10 +969,10 @@
         <v>0.077</v>
       </c>
       <c r="D20" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="E20" t="n">
-        <v>0.043</v>
+        <v>0.046</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.022</v>
+        <v>-0.023</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.002999999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1023,10 +1023,10 @@
         <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.055</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>0.058</v>
+        <v>0.063</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1050,10 +1050,10 @@
         <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>0.068</v>
+        <v>0.065</v>
       </c>
       <c r="E23" t="n">
-        <v>0.129</v>
+        <v>0.132</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.043</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1104,10 +1104,10 @@
         <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.028</v>
+        <v>-0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1131,10 +1131,10 @@
         <v>-0.128</v>
       </c>
       <c r="D26" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="E26" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1158,10 +1158,10 @@
         <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.027</v>
+        <v>0.022</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2</v>
+        <v>0.205</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1185,10 +1185,10 @@
         <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="E28" t="n">
-        <v>0.357</v>
+        <v>0.362</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1212,10 +1212,10 @@
         <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.048</v>
+        <v>-0.038</v>
       </c>
       <c r="E29" t="n">
-        <v>0.353</v>
+        <v>0.363</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1239,10 +1239,10 @@
         <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1266,10 +1266,10 @@
         <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.01</v>
+        <v>-0.013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.031</v>
+        <v>0.028</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1293,10 +1293,10 @@
         <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.058</v>
+        <v>-0.057</v>
       </c>
       <c r="E32" t="n">
-        <v>0.008</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1388,22 +1388,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7100.892033747257</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="C2" t="n">
-        <v>0.994936431681357</v>
+        <v>0.9957648995493169</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1288663006716531</v>
+        <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.612879304103456</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
-        <v>1.125850702242218</v>
+        <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.612462982328197</v>
+        <v>1.678043421071839</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.754512869007924</v>
+        <v>1.667251009830694</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09933100092346644</v>
+        <v>0.1039505645896264</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559827684649615</v>
+        <v>1.463511647062421</v>
       </c>
       <c r="E2" t="n">
-        <v>1.949198053366233</v>
+        <v>1.870990372598966</v>
       </c>
       <c r="F2" t="n">
-        <v>8.040441814883746e-70</v>
+        <v>6.837236032556501e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0247598395400246</v>
+        <v>-0.02463484865352593</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02003374869498218</v>
+        <v>0.02140527657651925</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.064025265457516</v>
+        <v>-0.06658841982262249</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01450558637746678</v>
+        <v>0.01731872251557064</v>
       </c>
       <c r="F3" t="n">
-        <v>0.216493333458463</v>
+        <v>0.2497826842838111</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07571000955410477</v>
+        <v>-0.07540915009642354</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05112637237841644</v>
+        <v>0.05279509857940833</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1759158580759844</v>
+        <v>-0.1788856418723057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02449583896777488</v>
+        <v>0.02806734167945855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1386490463766038</v>
+        <v>0.1531951152281513</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07856299588114521</v>
+        <v>-0.07777010843832736</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03405158832866617</v>
+        <v>0.03746669966516233</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1453028826217154</v>
+        <v>-0.1512034904016245</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01182310914057506</v>
+        <v>-0.004336726475030292</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02104502924715573</v>
+        <v>0.03792052047519422</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02831544568658506</v>
+        <v>0.02910393820822489</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03231459158429648</v>
+        <v>0.03598696595065997</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03501998999375718</v>
+        <v>-0.04142921896793787</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0916508813669273</v>
+        <v>0.09963709538438766</v>
       </c>
       <c r="F6" t="n">
-        <v>0.380897759581917</v>
+        <v>0.4186672829157794</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02205226969107453</v>
+        <v>0.02381528941209116</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03330982112657673</v>
+        <v>0.03444948165300098</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04323378004848727</v>
+        <v>-0.04370445391386412</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08733831943063633</v>
+        <v>0.09133503273804644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5079487476459772</v>
+        <v>0.4893704159956827</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03486844805869609</v>
+        <v>0.034009470652529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03352830234892717</v>
+        <v>0.03572753009575892</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03084581700797085</v>
+        <v>-0.03601520159172934</v>
       </c>
       <c r="E8" t="n">
-        <v>0.100582713125363</v>
+        <v>0.1040341428967873</v>
       </c>
       <c r="F8" t="n">
-        <v>0.298353568970926</v>
+        <v>0.3411415276602039</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03776583204626978</v>
+        <v>0.03806830840584245</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03281559861986921</v>
+        <v>0.03435019598273854</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02655155937979617</v>
+        <v>-0.02925683858221755</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1020832234723357</v>
+        <v>0.1053934553939024</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2497939460141906</v>
+        <v>0.2677575867271226</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.001433471577265606</v>
+        <v>0.002048208353331455</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05673268085163177</v>
+        <v>0.05422289275560453</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1097605396383378</v>
+        <v>-0.1042267085852312</v>
       </c>
       <c r="E10" t="n">
-        <v>0.112627482792869</v>
+        <v>0.1083231252918941</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9798418982736162</v>
+        <v>0.9698679804037627</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.003171891843002228</v>
+        <v>-0.002592226077109234</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05646578395047322</v>
+        <v>0.05602652915899796</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1138427947447496</v>
+        <v>-0.1124022054075284</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1074990110587451</v>
+        <v>0.1072177532533099</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9552034347574987</v>
+        <v>0.9630967776380727</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0964359095336724</v>
+        <v>-0.09685847877529372</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05588348181776841</v>
+        <v>0.05376448018771047</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2059655212271974</v>
+        <v>-0.2022349235907235</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01309370215985263</v>
+        <v>0.008517966040136091</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08440853281646646</v>
+        <v>0.07161892986848886</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05980769938543536</v>
+        <v>0.05872986129122737</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05553591338513311</v>
+        <v>0.05289827688087852</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04904069069796145</v>
+        <v>-0.04494885623952233</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1686560894688321</v>
+        <v>0.1624085788219771</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2815163005423185</v>
+        <v>0.2668949821258348</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0128533948388004</v>
+        <v>0.01177434185712823</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05688654660420558</v>
+        <v>0.05286151476865377</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09864218771030185</v>
+        <v>-0.09183232325766533</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1243489773879027</v>
+        <v>0.1153810069719218</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8212419545530024</v>
+        <v>0.8237383381340919</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08061192698920415</v>
+        <v>-0.08022934381684173</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0554929274876811</v>
+        <v>0.05335891402080929</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1893760662617519</v>
+        <v>-0.1848108935517973</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02815221228334359</v>
+        <v>0.0243522059181138</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1463203259223282</v>
+        <v>0.1326897956946215</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02794846610921984</v>
+        <v>0.02854452070261676</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05356404296810444</v>
+        <v>0.05244177820955687</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07703512897462081</v>
+        <v>-0.07423947587335211</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1329320611930605</v>
+        <v>0.1313285172785856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6018258594140455</v>
+        <v>0.5862290010152402</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.009660118628928028</v>
+        <v>0.009535077288637514</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0530206416785098</v>
+        <v>0.05256744027004793</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09425842949815449</v>
+        <v>-0.09349521240011692</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1135786667560106</v>
+        <v>0.112565366977392</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8554293590160085</v>
+        <v>0.8560634189937389</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09335347629425512</v>
+        <v>-0.09439860867570263</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05631191780012855</v>
+        <v>0.054849587123976</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2037228070828871</v>
+        <v>-0.2019018240055875</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01701585449437683</v>
+        <v>0.01310460665418221</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09735935097611813</v>
+        <v>0.08524265511921764</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03347242360437157</v>
+        <v>-0.03376783026243117</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05434369177175782</v>
+        <v>0.0519423700807748</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1399841022639626</v>
+        <v>-0.1355730048924007</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07303925505521945</v>
+        <v>0.06803734436753829</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5379344835839286</v>
+        <v>0.515626442035312</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.02792131744085185</v>
+        <v>-0.02764259828225426</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05604078738514527</v>
+        <v>0.05243646023149141</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1377592423810032</v>
+        <v>-0.1304161718127443</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08191660749929947</v>
+        <v>0.07513097524823573</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6183204816607821</v>
+        <v>0.5980799157062469</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05288632466064912</v>
+        <v>-0.05277599238898858</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05293131078624972</v>
+        <v>0.05170157742489218</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1566297874561951</v>
+        <v>-0.1541092220856864</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05085713813489682</v>
+        <v>0.0485572373077092</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3177219826947859</v>
+        <v>0.3073581670729142</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03657321818718794</v>
+        <v>-0.03816573212201312</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05308364162783067</v>
+        <v>0.0520073026219301</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1406152439459672</v>
+        <v>-0.1400981721940716</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06746880757159135</v>
+        <v>0.06376670795004538</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4908399936189964</v>
+        <v>0.4630381345915042</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05861162972623239</v>
+        <v>-0.05938706149335559</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05437821107931171</v>
+        <v>0.05429573538926745</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1651909649854003</v>
+        <v>-0.1658047473704367</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04796770553293549</v>
+        <v>0.04703062438372547</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2811000869936449</v>
+        <v>0.274055743506364</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.01005162745768696</v>
+        <v>0.00845175867266053</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0481512118192649</v>
+        <v>0.04715478622950785</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0843230135200316</v>
+        <v>-0.08396992403586016</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1044262684354055</v>
+        <v>0.1008734413811812</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8346424004677472</v>
+        <v>0.8577536728165651</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.009120099548350819</v>
+        <v>0.008266388421399319</v>
       </c>
       <c r="C25" t="n">
-        <v>0.025808145106854</v>
+        <v>0.02616363601935623</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04146293536886665</v>
+        <v>-0.04301339588115381</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05970313446556828</v>
+        <v>0.05954617272395244</v>
       </c>
       <c r="F25" t="n">
-        <v>0.723803077097364</v>
+        <v>0.7520408188561643</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02407378599099586</v>
+        <v>0.02423811373715811</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03206966367004865</v>
+        <v>0.03264857083896998</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03878159979861211</v>
+        <v>-0.0397519092539277</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08692917178060382</v>
+        <v>0.08822813672824394</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4528503141018294</v>
+        <v>0.4578484564206015</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04060344178148418</v>
+        <v>-0.03915934034912669</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03480802787184433</v>
+        <v>0.03173000514229339</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1088259227831654</v>
+        <v>-0.1013490076572925</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02761903922019709</v>
+        <v>0.02303032695903907</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2434137733407732</v>
+        <v>0.2171498974623943</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.01801405069627489</v>
+        <v>0.01922954242420748</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03287348973086943</v>
+        <v>0.03227805668499569</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0464168052223765</v>
+        <v>-0.04403428616932641</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08244490661492627</v>
+        <v>0.08249337101774136</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5837048880928343</v>
+        <v>0.5513445242495119</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06618766670670986</v>
+        <v>0.06730170037260194</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03244015315049077</v>
+        <v>0.03196767543970731</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002606134878784402</v>
+        <v>0.004646207841309966</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1297691985346353</v>
+        <v>0.1299571929038939</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04132038659943603</v>
+        <v>0.03526478503851296</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.04209890969082612</v>
+        <v>-0.0405928052277169</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04324539512942533</v>
+        <v>0.04219295914182774</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1268583266417037</v>
+        <v>-0.1232894855468693</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0426605072600514</v>
+        <v>0.04210387509143549</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3303104023814746</v>
+        <v>0.3360117637295972</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4490588044047898</v>
+        <v>3.375687514582784e-05</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01025438241335627</v>
+        <v>0.004788621486128041</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4289605841909106</v>
+        <v>-0.009351768773259803</v>
       </c>
       <c r="E31" t="n">
-        <v>0.469157024618669</v>
+        <v>0.00941928252355146</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.9943754446864004</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001833534192516898</v>
+        <v>0.4490526515310966</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001473009292431332</v>
+        <v>0.01068393144388246</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004720579354575137</v>
+        <v>0.428112530687792</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001053510969541341</v>
+        <v>0.4699927723744013</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2132221937698843</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001024010673638308</v>
+        <v>0.001861597274177133</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001512842840425173</v>
+        <v>0.00157784605265147</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003989128155140923</v>
+        <v>-0.001230924162168439</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001941106807864308</v>
+        <v>0.004954118710522704</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4984830962483939</v>
+        <v>0.2380660284989642</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.003347989103712482</v>
+        <v>0.003364288003062576</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001737598355069264</v>
+        <v>0.001764656162787935</v>
       </c>
       <c r="D34" t="n">
-        <v>-5.764109181931581e-05</v>
+        <v>-9.437452109842736e-05</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00675361929924428</v>
+        <v>0.00682295052722358</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0540056649367114</v>
+        <v>0.05658749372658953</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.02837099432574491</v>
+        <v>-0.0009948915328936558</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02415274779799336</v>
+        <v>0.001577711740423721</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.075709510137491</v>
+        <v>-0.004087149722110156</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01896752148600118</v>
+        <v>0.002097366656322844</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2401352823955832</v>
+        <v>0.5283076912307978</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.00203246791119006</v>
+        <v>-0.02814404589903957</v>
       </c>
       <c r="C36" t="n">
-        <v>0.004434828361796976</v>
+        <v>0.02420739120983632</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0107245717779289</v>
+        <v>-0.07558966082999025</v>
       </c>
       <c r="E36" t="n">
-        <v>0.006659635955548782</v>
+        <v>0.0193015690319111</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6467391799967959</v>
+        <v>0.244982895476078</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.350970771285248</v>
+        <v>-2.68060017980294</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4605522587714034</v>
+        <v>0.4771933030981267</v>
       </c>
       <c r="D2" t="n">
-        <v>3.313590542287848e-07</v>
+        <v>1.93818176827037e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02128055977478192</v>
+        <v>-0.02542074333516159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09751395156308111</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.827249191641336</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2245966634275915</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2329354389845562</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3349449904957182</v>
+        <v>0.3364439424069164</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8167052829997485</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1617156577703267</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>4.412210487480358e-07</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03599538577094948</v>
+        <v>0.03527526670387294</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1898688322218615</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8496380437366924</v>
+        <v>0.8539945454713553</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2765708211818085</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1824472225347018</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.129545920374235</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1102648615599912</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1853641405651108</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5519401263365121</v>
+        <v>0.5954095400432468</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8745743640527194</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1615402513662274</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>6.164188141358052e-08</v>
+        <v>2.539495077342719e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04349724922704642</v>
+        <v>-0.04456520772617057</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2655215602978132</v>
+        <v>0.2604021031716314</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8698743077153893</v>
+        <v>0.8641137091517844</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2685655156863916</v>
+        <v>-0.2737623724798145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2761865361461748</v>
+        <v>0.2787881385465063</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3308484806726052</v>
+        <v>0.3261132423877634</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08406558527820192</v>
+        <v>0.08100487957118158</v>
       </c>
       <c r="C12" t="n">
-        <v>0.251020166800007</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7377037334343584</v>
+        <v>0.7550514391424689</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04159103469582721</v>
+        <v>0.03917827337461771</v>
       </c>
       <c r="C13" t="n">
-        <v>0.255561465250315</v>
+        <v>0.2572958805743772</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8707201879025983</v>
+        <v>0.8789745077123736</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05097157642059893</v>
+        <v>-0.05296103812307912</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2615504699624188</v>
+        <v>0.2610089865588722</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8454850334004391</v>
+        <v>0.8392062624375538</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1235593461635321</v>
+        <v>0.1181322726534163</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2569613848518211</v>
+        <v>0.2572294350577189</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6306245929938302</v>
+        <v>0.6460556128984085</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002490750131026257</v>
+        <v>-0.00400098624037939</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2457746491930773</v>
+        <v>0.2383903410311194</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9919141495524532</v>
+        <v>0.9866094604655136</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1110262478895003</v>
+        <v>0.1057185310395308</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2594324060220158</v>
+        <v>0.2543340222421757</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6686814903924607</v>
+        <v>0.6776529122567302</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1338440250599403</v>
+        <v>-0.1377694895733253</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2694490717592011</v>
+        <v>0.2636874203313639</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6193779257550096</v>
+        <v>0.6013412201546287</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02068301206114321</v>
+        <v>-0.0255715409422322</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2629683391871477</v>
+        <v>0.2527597901538112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9373093461992266</v>
+        <v>0.9194160355966682</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0686991433762508</v>
+        <v>-0.07344622569376394</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2617458461247386</v>
+        <v>0.2674578609541013</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7929629071620667</v>
+        <v>0.7836169672222786</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2112158738988716</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2400889859196068</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3790001987958982</v>
+        <v>0.3983578134719856</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.159933319308369</v>
+        <v>-0.1704634573362025</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2649283257747139</v>
+        <v>0.2696748454965907</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5460529306471213</v>
+        <v>0.5273167196806369</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4920005620651325</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2884409459397611</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08805953197431808</v>
+        <v>0.08105838975171867</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9425285809878476</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1559773650465781</v>
+        <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>1.515312581506736e-09</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5768512495314141</v>
+        <v>-0.5776106069409676</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1130405709043027</v>
+        <v>0.1143619392421805</v>
       </c>
       <c r="D25" t="n">
-        <v>3.342294640071132e-07</v>
+        <v>4.401383208103756e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2384858887162336</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1457315480836286</v>
+        <v>0.1503781926377478</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1017404238903948</v>
+        <v>0.1145360411757809</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04585234373593617</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1593109532353293</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7734870970055308</v>
+        <v>0.7872365295400219</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07857740431296747</v>
+        <v>-0.07514354096975731</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1565335672967476</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6156785148897228</v>
+        <v>0.6414556246120153</v>
       </c>
     </row>
     <row r="29">
@@ -2807,45 +2807,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09755305493394664</v>
+        <v>0.09749293462742098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1499487653516257</v>
+        <v>0.1543265796290168</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5153202832397639</v>
+        <v>0.5275624553510017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.006860378637723895</v>
+        <v>-0.004129656026475424</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006945236405256705</v>
+        <v>0.02222260881033181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3232594861617505</v>
+        <v>0.8525770672961283</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002646425713821547</v>
+        <v>0.006335499136474501</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007095424075339026</v>
+        <v>0.006871422968197188</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7091660102282209</v>
+        <v>0.3565249957666434</v>
       </c>
     </row>
     <row r="32">
@@ -2855,45 +2855,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004895000819746557</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008684655396149939</v>
+        <v>0.008304876992454852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5730005966817302</v>
+        <v>0.5461741835341496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2261835420647834</v>
+        <v>-0.00241813341219285</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1139281184793711</v>
+        <v>0.007135781003458538</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04710910483736543</v>
+        <v>0.7347043603418298</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01540023496026497</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0213723694247541</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D34" t="n">
-        <v>0.47117565131408</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.227</v>
+        <v>-0.008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.021</v>
+        <v>-0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.206</v>
+        <v>0.008</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.143</v>
+        <v>-0.066</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.042</v>
+        <v>-0.057</v>
       </c>
       <c r="E8" t="n">
-        <v>0.101</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.054</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.002</v>
+        <v>-0.028</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.024</v>
+        <v>0.041</v>
       </c>
       <c r="D10" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>0.007</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>0.026</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>-0.019</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.107</v>
+        <v>-0.074</v>
       </c>
       <c r="D12" t="n">
-        <v>0.042</v>
+        <v>-0.042</v>
       </c>
       <c r="E12" t="n">
-        <v>0.065</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.034</v>
       </c>
       <c r="D13" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.026</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.019</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.128</v>
+        <v>-0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.019</v>
+        <v>-0.012</v>
       </c>
       <c r="E14" t="n">
-        <v>0.109</v>
+        <v>0.029</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.013</v>
+        <v>0.03</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.013</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.046</v>
+        <v>-0.401</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002</v>
+        <v>-0.037</v>
       </c>
       <c r="E17" t="n">
-        <v>0.044</v>
+        <v>0.364</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.392</v>
+        <v>-0.014</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03</v>
+        <v>-0.003</v>
       </c>
       <c r="E18" t="n">
-        <v>0.362</v>
+        <v>0.011</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.143</v>
       </c>
       <c r="D19" t="n">
-        <v>-0</v>
+        <v>-0.042</v>
       </c>
       <c r="E19" t="n">
-        <v>0.008</v>
+        <v>0.101</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.197</v>
+        <v>-0.019</v>
       </c>
       <c r="D20" t="n">
-        <v>0.065</v>
+        <v>-0.023</v>
       </c>
       <c r="E20" t="n">
-        <v>0.132</v>
+        <v>-0.004</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.074</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.042</v>
+        <v>-0.002</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.023</v>
+        <v>-0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01</v>
+        <v>-0.004</v>
       </c>
       <c r="E23" t="n">
-        <v>0.013</v>
+        <v>-0.004</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.401</v>
+        <v>0.022</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.037</v>
+        <v>0.014</v>
       </c>
       <c r="E24" t="n">
-        <v>0.364</v>
+        <v>0.007999999999999998</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.041</v>
+        <v>-0.024</v>
       </c>
       <c r="D25" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003000000000000003</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.066</v>
+        <v>0.197</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.057</v>
+        <v>0.065</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.041</v>
+        <v>0.046</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="E28" t="n">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.022</v>
+        <v>0.227</v>
       </c>
       <c r="D29" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="E29" t="n">
-        <v>0.007999999999999998</v>
+        <v>0.206</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.054</v>
+        <v>0.005</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.028</v>
+        <v>-0.013</v>
       </c>
       <c r="E30" t="n">
-        <v>0.026</v>
+        <v>-0.008</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.019</v>
+        <v>0.107</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.023</v>
+        <v>0.042</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.004</v>
+        <v>0.065</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.014</v>
+        <v>-0.128</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.003</v>
+        <v>0.019</v>
       </c>
       <c r="E32" t="n">
-        <v>0.011</v>
+        <v>0.109</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>0.392</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004</v>
+        <v>0.03</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.004</v>
+        <v>0.362</v>
       </c>
       <c r="F33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
@@ -1494,16 +1494,16 @@
         <v>1.667057534699058</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1039364500786116</v>
+        <v>0.1039364500786131</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463345835864034</v>
+        <v>1.463345835864031</v>
       </c>
       <c r="E2" t="n">
-        <v>1.870769233534082</v>
+        <v>1.870769233534085</v>
       </c>
       <c r="F2" t="n">
-        <v>6.802471999941005e-58</v>
+        <v>6.802471999965267e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02459156738062896</v>
+        <v>-0.02459156738062897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02140527432766426</v>
+        <v>0.02140527432766425</v>
       </c>
       <c r="D3" t="n">
         <v>-0.06654513414205072</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01736199938079281</v>
+        <v>0.01736199938079278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2506155650116352</v>
+        <v>0.2506155650116347</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07551420708983096</v>
+        <v>-0.07551420708983102</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05280032846285383</v>
+        <v>0.05280032846285382</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1790009492489096</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02797253506924764</v>
+        <v>0.02797253506924757</v>
       </c>
       <c r="F4" t="n">
-        <v>0.152664096098382</v>
+        <v>0.1526640960983817</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07779512547504261</v>
+        <v>-0.07779512547504262</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03745864396191226</v>
+        <v>0.03745864396191223</v>
       </c>
       <c r="D5" t="n">
         <v>-0.1512127185500994</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004377532399985826</v>
+        <v>-0.004377532399985895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03781752357803488</v>
+        <v>0.0378175235780347</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02905433458750139</v>
+        <v>0.02905433458750136</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0359841378195719</v>
+        <v>0.03598413781957187</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0414732795535852</v>
+        <v>-0.04147327955358517</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09958194872858797</v>
+        <v>0.09958194872858789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4194241955012055</v>
+        <v>0.4194241955012057</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03407929589427781</v>
+        <v>0.03407929589427779</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03572350274317036</v>
+        <v>0.03572350274317035</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03593748288395392</v>
+        <v>-0.03593748288395391</v>
       </c>
       <c r="E8" t="n">
         <v>0.1040960746725095</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03802463954938589</v>
+        <v>0.03802463954938588</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03434053922890857</v>
+        <v>0.03434053922890858</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02928158054895979</v>
+        <v>-0.02928158054895983</v>
       </c>
       <c r="E9" t="n">
         <v>0.1053308596477316</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2681722936342085</v>
+        <v>0.2681722936342088</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002108926766444169</v>
+        <v>0.002108926766444237</v>
       </c>
       <c r="C10" t="n">
         <v>0.05423092905058527</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1041817410208499</v>
+        <v>-0.1041817410208498</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1083995945537382</v>
+        <v>0.1083995945537383</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9689797663112281</v>
+        <v>0.9689797663112271</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.002698318963696225</v>
+        <v>-0.002698318963696172</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05603185984561369</v>
+        <v>0.05603185984561364</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1125187462478951</v>
+        <v>-0.1125187462478949</v>
       </c>
       <c r="E11" t="n">
         <v>0.1071221083205026</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9615912234151366</v>
+        <v>0.9615912234151374</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.09690684290742647</v>
+        <v>-0.09690684290742646</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05376611743977976</v>
+        <v>0.05376611743977971</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2022864966779457</v>
+        <v>-0.2022864966779456</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008472810863092747</v>
+        <v>0.008472810863092664</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07148602519025385</v>
+        <v>0.07148602519025365</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05861966677649851</v>
+        <v>0.05861966677649853</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05290215792217631</v>
+        <v>0.05290215792217636</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04506665745541735</v>
+        <v>-0.04506665745541744</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1623059910084144</v>
+        <v>0.1623059910084145</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2678285440445223</v>
+        <v>0.2678285440445227</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01179934497704003</v>
+        <v>0.01179934497704005</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05285544422806162</v>
+        <v>0.05285544422806156</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09179542209682622</v>
+        <v>-0.09179542209682609</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1153941120509063</v>
+        <v>0.1153941120509062</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8233502589464913</v>
+        <v>0.8233502589464908</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08024560007397158</v>
+        <v>-0.08024560007397152</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0533592988010333</v>
+        <v>0.05335929880103314</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1848279039643081</v>
+        <v>-0.1848279039643078</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02433670381636498</v>
+        <v>0.02433670381636473</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1326141122249531</v>
+        <v>0.1326141122249523</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0284603148838417</v>
+        <v>0.02846031488384175</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05244704774958041</v>
+        <v>0.05244704774958035</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0743340098007884</v>
+        <v>-0.07433400980078823</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1312546395684718</v>
+        <v>0.1312546395684717</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5873717984965583</v>
+        <v>0.5873717984965572</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.009622939087805975</v>
+        <v>0.009622939087806004</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05256092363330972</v>
+        <v>0.05256092363330968</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09339457822764125</v>
+        <v>-0.09339457822764112</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1126404564032532</v>
+        <v>0.1126404564032531</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8547339765348235</v>
+        <v>0.8547339765348231</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1894,16 +1894,16 @@
         <v>-0.09464919935341419</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05485507866520829</v>
+        <v>0.05485507866520825</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.202163177906334</v>
+        <v>-0.2021631779063339</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01286477919950557</v>
+        <v>0.01286477919950549</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08444803584756613</v>
+        <v>0.08444803584756597</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,16 +1916,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03392408388401528</v>
+        <v>-0.03392408388401524</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05195030197739511</v>
+        <v>0.05195030197739505</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1357448047456896</v>
+        <v>-0.1357448047456895</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06789663697765908</v>
+        <v>0.06789663697765901</v>
       </c>
       <c r="F19" t="n">
         <v>0.5137496183866246</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.02760797148779857</v>
+        <v>-0.02760797148779862</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05243884475714469</v>
+        <v>0.0524388447571446</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1303862186026892</v>
+        <v>-0.1303862186026891</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07517027562709205</v>
+        <v>0.07517027562709183</v>
       </c>
       <c r="F20" t="n">
-        <v>0.598555161714674</v>
+        <v>0.5985551617146727</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05288647616397571</v>
+        <v>-0.05288647616397566</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0517043766820859</v>
+        <v>0.05170437668208592</v>
       </c>
       <c r="D21" t="n">
         <v>-0.1542251923039566</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04845223997600524</v>
+        <v>0.04845223997600532</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3063727874189753</v>
+        <v>0.3063727874189759</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03821453321866491</v>
+        <v>-0.0382145332186649</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05200529590021611</v>
+        <v>0.05200529590021597</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.140143040188437</v>
+        <v>-0.1401430401884367</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06371397375110718</v>
+        <v>0.06371397375110693</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4624491052692326</v>
+        <v>0.4624491052692317</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05939396367195354</v>
+        <v>-0.05939396367195351</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05430017231427046</v>
+        <v>0.05430017231427042</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1658203457622426</v>
+        <v>-0.1658203457622425</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04703241841833553</v>
+        <v>0.04703241841833546</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2740391883174071</v>
+        <v>0.274039188317407</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008554251100005588</v>
+        <v>0.008554251100005628</v>
       </c>
       <c r="C24" t="n">
         <v>0.04714697844654479</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08385212863510838</v>
+        <v>-0.08385212863510834</v>
       </c>
       <c r="E24" t="n">
         <v>0.1009606308351196</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8560238336771226</v>
+        <v>0.856023833677122</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.00833053131780615</v>
+        <v>0.008330531317806185</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02616718960488387</v>
+        <v>0.02616718960488383</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04295621788439712</v>
+        <v>-0.04295621788439702</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05961728052000943</v>
+        <v>0.05961728052000939</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7502134753562298</v>
+        <v>0.7502134753562285</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02424714499797291</v>
+        <v>0.02424714499797289</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03265065717218204</v>
+        <v>0.03265065717218203</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03974696713106829</v>
+        <v>-0.0397469671310683</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08824125712701411</v>
+        <v>0.08824125712701407</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4577096625377107</v>
+        <v>0.4577096625377112</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03912913997782914</v>
+        <v>-0.03912913997782923</v>
       </c>
       <c r="C27" t="n">
         <v>0.03172898075157672</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1013167995170841</v>
+        <v>-0.1013167995170842</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02305851956142585</v>
+        <v>0.02305851956142576</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2174898593271098</v>
+        <v>0.2174898593271088</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.01926734751463029</v>
+        <v>0.01926734751463025</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03227922232167938</v>
+        <v>0.0322792223216794</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04399876568482267</v>
+        <v>-0.04399876568482276</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08253346071408327</v>
+        <v>0.08253346071408325</v>
       </c>
       <c r="F28" t="n">
-        <v>0.550576635440338</v>
+        <v>0.5505766354403392</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06728645489710121</v>
+        <v>0.06728645489710117</v>
       </c>
       <c r="C29" t="n">
         <v>0.03196900488547524</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004628356699984695</v>
+        <v>0.004628356699984668</v>
       </c>
       <c r="E29" t="n">
         <v>0.1299445530942177</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03531391507082924</v>
+        <v>0.03531391507082932</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.04071597969725242</v>
+        <v>-0.04071597969725245</v>
       </c>
       <c r="C30" t="n">
         <v>0.04219485817141799</v>
@@ -2200,10 +2200,10 @@
         <v>-0.1234163820460073</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04198442265150243</v>
+        <v>0.0419844226515024</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3345692469681956</v>
+        <v>0.3345692469681951</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0009920422931855093</v>
+        <v>0.001858686570725003</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00157808271839598</v>
+        <v>0.001577825229323158</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004085027585866694</v>
+        <v>-0.001233794052647039</v>
       </c>
       <c r="E31" t="n">
-        <v>0.002100942999495675</v>
+        <v>0.004951167194097044</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5295862719421283</v>
+        <v>0.2387944710485395</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.003368127275367437</v>
+        <v>-0.0009920422931855067</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001764528679284745</v>
+        <v>0.00157808271839598</v>
       </c>
       <c r="D32" t="n">
-        <v>-9.028538571869207e-05</v>
+        <v>-0.004085027585866692</v>
       </c>
       <c r="E32" t="n">
-        <v>0.006826539936453565</v>
+        <v>0.002100942999495679</v>
       </c>
       <c r="F32" t="n">
-        <v>0.056288267505556</v>
+        <v>0.5295862719421294</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.065588116314992e-05</v>
+        <v>0.4490720848345698</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004788074446685941</v>
+        <v>0.01068359759505055</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.009353797589637841</v>
+        <v>0.428132618322952</v>
       </c>
       <c r="E33" t="n">
-        <v>0.009415109351964141</v>
+        <v>0.4700115513461877</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9948915399209101</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2291,19 +2291,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.028159565483449</v>
+        <v>-0.02815956548344902</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02420948131337567</v>
+        <v>0.02420948131337568</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07560927694206077</v>
+        <v>-0.07560927694206079</v>
       </c>
       <c r="E34" t="n">
         <v>0.01929014597516276</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2447634997487504</v>
+        <v>0.2447634997487502</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001858686570725002</v>
+        <v>0.003368127275367432</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001577825229323158</v>
+        <v>0.001764528679284755</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.001233794052647039</v>
+        <v>-9.028538571871636e-05</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004951167194097043</v>
+        <v>0.00682653993645358</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2387944710485393</v>
+        <v>0.05628826750555774</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4490720848345699</v>
+        <v>3.06558811631338e-05</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01068359759505061</v>
+        <v>0.00478807444668594</v>
       </c>
       <c r="D36" t="n">
-        <v>0.428132618322952</v>
+        <v>-0.009353797589637856</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4700115513461878</v>
+        <v>0.009415109351964122</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.9948915399209128</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.713407322158418</v>
+        <v>-2.713407322158419</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5044376034036603</v>
+        <v>0.5044376034036661</v>
       </c>
       <c r="D2" t="n">
-        <v>7.486982883652069e-08</v>
+        <v>7.486982883654581e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02522051520904542</v>
+        <v>-0.02522051520904552</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1001657906734903</v>
+        <v>0.1001657906734904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8012051561485711</v>
+        <v>0.8012051561485702</v>
       </c>
     </row>
     <row r="4">
@@ -2440,7 +2440,7 @@
         <v>0.2334051881144238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.336352536756915</v>
+        <v>0.3363525367569152</v>
       </c>
     </row>
     <row r="5">
@@ -2456,7 +2456,7 @@
         <v>0.1732905987053344</v>
       </c>
       <c r="D5" t="n">
-        <v>2.544403764026986e-06</v>
+        <v>2.544403764027002e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03529662509742185</v>
+        <v>0.03529662509742199</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1917359483069561</v>
+        <v>0.1917359483069559</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539430379367488</v>
+        <v>0.8539430379367481</v>
       </c>
     </row>
     <row r="7">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2770307728862445</v>
+        <v>0.2770307728862446</v>
       </c>
       <c r="C7" t="n">
         <v>0.1900876275228709</v>
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8739030378849016</v>
+        <v>0.8739030378849018</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695379888770781</v>
+        <v>0.169537988877078</v>
       </c>
       <c r="D9" t="n">
-        <v>2.541527320496923e-07</v>
+        <v>2.541527320496866e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,10 +2530,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04298175525170753</v>
+        <v>-0.04298175525170747</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2597533292652202</v>
+        <v>0.2597533292652197</v>
       </c>
       <c r="D10" t="n">
         <v>0.8685729341423553</v>
@@ -2549,10 +2549,10 @@
         <v>-0.2734774183375255</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2785592488643228</v>
+        <v>0.2785592488643225</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3262197079678817</v>
+        <v>0.3262197079678811</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08217580196393716</v>
+        <v>0.08217580196393699</v>
       </c>
       <c r="C12" t="n">
         <v>0.2587287215011221</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7507779355278751</v>
+        <v>0.7507779355278755</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03995788006654508</v>
+        <v>0.03995788006654509</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2568297818201686</v>
+        <v>0.2568297818201681</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8763631618417494</v>
+        <v>0.8763631618417491</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05219347665548976</v>
+        <v>-0.05219347665548984</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2603443755509273</v>
+        <v>0.2603443755509272</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8411062907988994</v>
+        <v>0.8411062907988991</v>
       </c>
     </row>
     <row r="15">
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1183975653249733</v>
+        <v>0.1183975653249732</v>
       </c>
       <c r="C15" t="n">
         <v>0.2570359266688499</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6450665788994044</v>
+        <v>0.6450665788994046</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.00281501118239398</v>
+        <v>-0.002815011182394092</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2376522981116134</v>
+        <v>0.2376522981116133</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9905492122003408</v>
+        <v>0.9905492122003404</v>
       </c>
     </row>
     <row r="17">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1056709152111884</v>
+        <v>0.1056709152111883</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2542906688395363</v>
+        <v>0.2542906688395361</v>
       </c>
       <c r="D17" t="n">
         <v>0.677738089343457</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1371135645044839</v>
+        <v>-0.1371135645044841</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2634072330241232</v>
+        <v>0.263407233024123</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6026884109023545</v>
+        <v>0.6026884109023538</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02475228489410885</v>
+        <v>-0.02475228489410887</v>
       </c>
       <c r="C19" t="n">
         <v>0.2524092973060099</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9218814119969665</v>
+        <v>0.9218814119969664</v>
       </c>
     </row>
     <row r="20">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07246351166486092</v>
+        <v>-0.07246351166486088</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2666987121614957</v>
+        <v>0.2666987121614964</v>
       </c>
       <c r="D20" t="n">
-        <v>0.785848458322071</v>
+        <v>0.7858484583220717</v>
       </c>
     </row>
     <row r="21">
@@ -2709,10 +2709,10 @@
         <v>0.2068090257965718</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2439533267288631</v>
+        <v>0.2439533267288634</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3965827100652906</v>
+        <v>0.3965827100652911</v>
       </c>
     </row>
     <row r="22">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1686288808585498</v>
+        <v>-0.1686288808585497</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2694061394634718</v>
+        <v>0.269406139463471</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5313620833011161</v>
+        <v>0.531362083301115</v>
       </c>
     </row>
     <row r="23">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4997770753001369</v>
+        <v>-0.499777075300137</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2864601345898813</v>
+        <v>0.2864601345898814</v>
       </c>
       <c r="D23" t="n">
         <v>0.08104313551548828</v>
@@ -2757,10 +2757,10 @@
         <v>0.9365913375115046</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1482811706186313</v>
+        <v>0.1482811706186312</v>
       </c>
       <c r="D24" t="n">
-        <v>2.678649464267771e-10</v>
+        <v>2.678649464267732e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2776,7 +2776,7 @@
         <v>0.1145314111910344</v>
       </c>
       <c r="D25" t="n">
-        <v>4.43933787929666e-07</v>
+        <v>4.439337879296676e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2789,10 +2789,10 @@
         <v>0.2379613006187487</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503209475356384</v>
+        <v>0.1503209475356383</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1134165507753407</v>
+        <v>0.1134165507753405</v>
       </c>
     </row>
     <row r="27">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04352683570925984</v>
+        <v>-0.04352683570925985</v>
       </c>
       <c r="C27" t="n">
         <v>0.1612096759797175</v>
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07467572557157248</v>
+        <v>-0.07467572557157245</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1614290026159801</v>
+        <v>0.1614290026159799</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6436570199176102</v>
+        <v>0.6436570199176099</v>
       </c>
     </row>
     <row r="29">
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09777326958921112</v>
+        <v>0.09777326958921104</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543602583723147</v>
+        <v>0.1543602583723145</v>
       </c>
       <c r="D29" t="n">
         <v>0.5264661972233939</v>
@@ -2846,49 +2846,49 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002450883409209257</v>
+        <v>0.006367932838418618</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00712771118784129</v>
+        <v>0.006881672701727233</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7309569941465299</v>
+        <v>0.3547856158497277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004998614827289062</v>
+        <v>-0.002450883409209241</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008307994570919656</v>
+        <v>0.007127711187841283</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5473983322894252</v>
+        <v>0.7309569941465313</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004172683243731415</v>
+        <v>0.01034291492939445</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0222352694573979</v>
+        <v>0.05138615505935789</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8511427450377147</v>
+        <v>0.8404810151443459</v>
       </c>
     </row>
     <row r="33">
@@ -2898,45 +2898,45 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2275650381150179</v>
+        <v>0.227565038115018</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1144549283876821</v>
+        <v>0.114454928387682</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04678402178782448</v>
+        <v>0.04678402178782429</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006367932838418625</v>
+        <v>-0.00499861482728905</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006881672701727249</v>
+        <v>0.008307994570919621</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3547856158497283</v>
+        <v>0.5473983322894246</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01034291492939454</v>
+        <v>-0.004172683243731372</v>
       </c>
       <c r="C35" t="n">
-        <v>0.05138615505935801</v>
+        <v>0.02223526945739788</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8404810151443449</v>
+        <v>0.8511427450377161</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.008</v>
+        <v>0.197</v>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>0.065</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008</v>
+        <v>0.132</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.066</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.057</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.054</v>
+        <v>-0.128</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.028</v>
+        <v>0.019</v>
       </c>
       <c r="E9" t="n">
-        <v>0.026</v>
+        <v>0.109</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.041</v>
+        <v>0.107</v>
       </c>
       <c r="D10" t="n">
-        <v>0.038</v>
+        <v>0.042</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.065</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007</v>
+        <v>0.227</v>
       </c>
       <c r="D11" t="n">
-        <v>0.026</v>
+        <v>0.021</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.019</v>
+        <v>0.206</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.074</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.042</v>
+        <v>-0.004</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03199999999999999</v>
+        <v>-0.004</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.034</v>
+        <v>-0.066</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.008</v>
+        <v>-0.057</v>
       </c>
       <c r="E13" t="n">
-        <v>0.026</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.041</v>
+        <v>0.032</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.012</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>0.029</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.032</v>
+        <v>-0.054</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03</v>
+        <v>-0.028</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.026</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.023</v>
+        <v>0.041</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>0.038</v>
       </c>
       <c r="E16" t="n">
-        <v>0.013</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.401</v>
+        <v>0.005</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.037</v>
+        <v>-0.013</v>
       </c>
       <c r="E17" t="n">
-        <v>0.364</v>
+        <v>-0.008</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.014</v>
+        <v>-0.008</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.143</v>
+        <v>0.022</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.042</v>
+        <v>0.014</v>
       </c>
       <c r="E19" t="n">
-        <v>0.101</v>
+        <v>0.007999999999999998</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.023</v>
+        <v>-0.002</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.004</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.041</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.002</v>
+        <v>-0.012</v>
       </c>
       <c r="E21" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>-0.023</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>-0.004</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0</v>
+        <v>-0.113</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.004</v>
+        <v>-0.05</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.004</v>
+        <v>0.063</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.022</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>0.014</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.007999999999999998</v>
+        <v>0.101</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.024</v>
+        <v>-0.014</v>
       </c>
       <c r="D25" t="n">
-        <v>0.027</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.197</v>
+        <v>0.034</v>
       </c>
       <c r="D27" t="n">
-        <v>0.065</v>
+        <v>-0.008</v>
       </c>
       <c r="E27" t="n">
-        <v>0.132</v>
+        <v>0.026</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.046</v>
+        <v>-0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.002</v>
+        <v>0.027</v>
       </c>
       <c r="E28" t="n">
-        <v>0.044</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.227</v>
+        <v>0.023</v>
       </c>
       <c r="D29" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="E29" t="n">
-        <v>0.206</v>
+        <v>0.013</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.005</v>
+        <v>-0.074</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.013</v>
+        <v>-0.042</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.008</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.107</v>
+        <v>0.392</v>
       </c>
       <c r="D31" t="n">
-        <v>0.042</v>
+        <v>0.03</v>
       </c>
       <c r="E31" t="n">
-        <v>0.065</v>
+        <v>0.362</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.128</v>
+        <v>0.007</v>
       </c>
       <c r="D32" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="E32" t="n">
-        <v>0.109</v>
+        <v>-0.019</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.392</v>
+        <v>-0.401</v>
       </c>
       <c r="D33" t="n">
-        <v>0.03</v>
+        <v>-0.037</v>
       </c>
       <c r="E33" t="n">
-        <v>0.362</v>
+        <v>0.364</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -1421,16 +1421,16 @@
         <v>0.9958005957981426</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1328258918333826</v>
+        <v>0.1328258918333825</v>
       </c>
       <c r="E2" t="n">
-        <v>1.685086418270235</v>
+        <v>1.685086418270234</v>
       </c>
       <c r="F2" t="n">
         <v>1.124755594450756</v>
       </c>
       <c r="G2" t="n">
-        <v>1.683051778403942</v>
+        <v>1.683051778403941</v>
       </c>
     </row>
   </sheetData>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.667057534699058</v>
+        <v>1.667057534699059</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1039364500786131</v>
+        <v>0.1039364500786104</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463345835864031</v>
+        <v>1.463345835864037</v>
       </c>
       <c r="E2" t="n">
-        <v>1.870769233534085</v>
+        <v>1.870769233534081</v>
       </c>
       <c r="F2" t="n">
-        <v>6.802471999965267e-58</v>
+        <v>6.80247199991985e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02459156738062897</v>
+        <v>-0.02459156738062898</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02140527432766425</v>
+        <v>0.02140527432766426</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06654513414205072</v>
+        <v>-0.06654513414205074</v>
       </c>
       <c r="E3" t="n">
         <v>0.01736199938079278</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.07551420708983102</v>
+        <v>-0.07551420708983113</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05280032846285382</v>
+        <v>0.0528003284628538</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1790009492489096</v>
+        <v>-0.1790009492489097</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02797253506924757</v>
+        <v>0.02797253506924745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1526640960983817</v>
+        <v>0.152664096098381</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1569,16 +1569,16 @@
         <v>-0.07779512547504262</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03745864396191223</v>
+        <v>0.03745864396191221</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1512127185500994</v>
+        <v>-0.1512127185500993</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004377532399985895</v>
+        <v>-0.004377532399985937</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0378175235780347</v>
+        <v>0.03781752357803459</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02905433458750136</v>
+        <v>0.02905433458750116</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03598413781957187</v>
+        <v>0.03598413781957185</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.04147327955358517</v>
+        <v>-0.04147327955358535</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09958194872858789</v>
+        <v>0.09958194872858767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4194241955012057</v>
+        <v>0.4194241955012087</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1619,16 +1619,16 @@
         <v>0.02386878238742904</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03444230723095774</v>
+        <v>0.0344423072309577</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04363689932971161</v>
+        <v>-0.04363689932971153</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09137446410456969</v>
+        <v>0.09137446410456961</v>
       </c>
       <c r="F7" t="n">
-        <v>0.48830475081652</v>
+        <v>0.4883047508165194</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03407929589427779</v>
+        <v>0.03407929589427783</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03572350274317035</v>
+        <v>0.03572350274317031</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03593748288395391</v>
+        <v>-0.03593748288395381</v>
       </c>
       <c r="E8" t="n">
         <v>0.1040960746725095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3400967596406821</v>
+        <v>0.3400967596406812</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1669,16 +1669,16 @@
         <v>0.03802463954938588</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03434053922890858</v>
+        <v>0.03434053922890854</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02928158054895983</v>
+        <v>-0.02928158054895974</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1053308596477316</v>
+        <v>0.1053308596477315</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2681722936342088</v>
+        <v>0.2681722936342082</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002108926766444237</v>
+        <v>0.002108926766444069</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05423092905058527</v>
+        <v>0.05423092905058513</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1041817410208498</v>
+        <v>-0.1041817410208497</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1083995945537383</v>
+        <v>0.1083995945537379</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9689797663112271</v>
+        <v>0.9689797663112295</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.002698318963696172</v>
+        <v>-0.002698318963696406</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05603185984561364</v>
+        <v>0.05603185984561351</v>
       </c>
       <c r="D11" t="n">
         <v>-0.1125187462478949</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1071221083205026</v>
+        <v>0.1071221083205021</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9615912234151374</v>
+        <v>0.9615912234151339</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.09690684290742646</v>
+        <v>-0.09690684290742663</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05376611743977971</v>
+        <v>0.05376611743977964</v>
       </c>
       <c r="D12" t="n">
         <v>-0.2022864966779456</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008472810863092664</v>
+        <v>0.008472810863092359</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07148602519025365</v>
+        <v>0.07148602519025281</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05861966677649853</v>
+        <v>0.05861966677649835</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05290215792217636</v>
+        <v>0.05290215792217611</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04506665745541744</v>
+        <v>-0.04506665745541713</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1623059910084145</v>
+        <v>0.1623059910084138</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2678285440445227</v>
+        <v>0.2678285440445217</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01179934497704005</v>
+        <v>0.01179934497703992</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05285544422806156</v>
+        <v>0.05285544422806146</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09179542209682609</v>
+        <v>-0.09179542209682603</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1153941120509062</v>
+        <v>0.1153941120509059</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8233502589464908</v>
+        <v>0.8233502589464925</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08024560007397152</v>
+        <v>-0.08024560007397173</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05335929880103314</v>
+        <v>0.05335929880103309</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1848279039643078</v>
+        <v>-0.1848279039643079</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02433670381636473</v>
+        <v>0.02433670381636442</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1326141122249523</v>
+        <v>0.1326141122249509</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02846031488384175</v>
+        <v>0.02846031488384153</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05244704774958035</v>
+        <v>0.05244704774958016</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07433400980078823</v>
+        <v>-0.07433400980078807</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1312546395684717</v>
+        <v>0.1312546395684711</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5873717984965572</v>
+        <v>0.5873717984965589</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.009622939087806004</v>
+        <v>0.009622939087805808</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05256092363330968</v>
+        <v>0.05256092363330954</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09339457822764112</v>
+        <v>-0.09339457822764105</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1126404564032531</v>
+        <v>0.1126404564032527</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8547339765348231</v>
+        <v>0.8547339765348255</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09464919935341419</v>
+        <v>-0.09464919935341445</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05485507866520825</v>
+        <v>0.0548550786652081</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2021631779063339</v>
+        <v>-0.2021631779063338</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01286477919950549</v>
+        <v>0.01286477919950492</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08444803584756597</v>
+        <v>0.08444803584756413</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03392408388401524</v>
+        <v>-0.03392408388401544</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05195030197739505</v>
+        <v>0.05195030197739482</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1357448047456895</v>
+        <v>-0.1357448047456892</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06789663697765901</v>
+        <v>0.06789663697765835</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5137496183866246</v>
+        <v>0.5137496183866201</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.02760797148779862</v>
+        <v>-0.02760797148779877</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0524388447571446</v>
+        <v>0.05243884475714452</v>
       </c>
       <c r="D20" t="n">
         <v>-0.1303862186026891</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07517027562709183</v>
+        <v>0.07517027562709153</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5985551617146727</v>
+        <v>0.5985551617146703</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05288647616397566</v>
+        <v>-0.05288647616397585</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05170437668208592</v>
+        <v>0.05170437668208575</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1542251923039566</v>
+        <v>-0.1542251923039565</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04845223997600532</v>
+        <v>0.04845223997600479</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3063727874189759</v>
+        <v>0.3063727874189726</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0382145332186649</v>
+        <v>-0.03821453321866519</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05200529590021597</v>
+        <v>0.05200529590021589</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1401430401884367</v>
+        <v>-0.1401430401884369</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06371397375110693</v>
+        <v>0.06371397375110649</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4624491052692317</v>
+        <v>0.4624491052692276</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05939396367195351</v>
+        <v>-0.05939396367195372</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05430017231427042</v>
+        <v>0.05430017231427022</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1658203457622425</v>
+        <v>-0.1658203457622423</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04703241841833546</v>
+        <v>0.04703241841833487</v>
       </c>
       <c r="F23" t="n">
-        <v>0.274039188317407</v>
+        <v>0.2740391883174035</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008554251100005628</v>
+        <v>0.008554251100005563</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04714697844654479</v>
+        <v>0.04714697844654474</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08385212863510834</v>
+        <v>-0.08385212863510833</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1009606308351196</v>
+        <v>0.1009606308351194</v>
       </c>
       <c r="F24" t="n">
-        <v>0.856023833677122</v>
+        <v>0.856023833677123</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2066,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008330531317806185</v>
+        <v>0.008330531317806101</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02616718960488383</v>
+        <v>0.02616718960488377</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04295621788439702</v>
+        <v>-0.04295621788439696</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05961728052000939</v>
+        <v>0.05961728052000917</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7502134753562285</v>
+        <v>0.7502134753562303</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02424714499797289</v>
+        <v>0.02424714499797288</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03265065717218203</v>
+        <v>0.03265065717218204</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0397469671310683</v>
+        <v>-0.03974696713106832</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08824125712701407</v>
+        <v>0.08824125712701408</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4577096625377112</v>
+        <v>0.4577096625377113</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03912913997782923</v>
+        <v>-0.0391291399778292</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03172898075157672</v>
+        <v>0.03172898075157669</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1013167995170842</v>
+        <v>-0.1013167995170841</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02305851956142576</v>
+        <v>0.02305851956142572</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2174898593271088</v>
+        <v>0.2174898593271086</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.01926734751463025</v>
+        <v>0.01926734751463019</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0322792223216794</v>
+        <v>0.03227922232167938</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04399876568482276</v>
+        <v>-0.04399876568482278</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08253346071408325</v>
+        <v>0.08253346071408316</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5505766354403392</v>
+        <v>0.5505766354403401</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06728645489710117</v>
+        <v>0.06728645489710115</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03196900488547524</v>
+        <v>0.0319690048854752</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004628356699984668</v>
+        <v>0.004628356699984723</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1299445530942177</v>
+        <v>0.1299445530942176</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03531391507082932</v>
+        <v>0.03531391507082912</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.04071597969725245</v>
+        <v>-0.04071597969725241</v>
       </c>
       <c r="C30" t="n">
         <v>0.04219485817141799</v>
@@ -2200,10 +2200,10 @@
         <v>-0.1234163820460073</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0419844226515024</v>
+        <v>0.04198442265150244</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3345692469681951</v>
+        <v>0.3345692469681958</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2216,19 +2216,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001858686570725003</v>
+        <v>0.001858686570724999</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001577825229323158</v>
+        <v>0.001577825229323157</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.001233794052647039</v>
+        <v>-0.001233794052647041</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004951167194097044</v>
+        <v>0.004951167194097038</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2387944710485395</v>
+        <v>0.23879447104854</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0009920422931855067</v>
+        <v>-0.02815956548344899</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00157808271839598</v>
+        <v>0.02420948131337567</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004085027585866692</v>
+        <v>-0.07560927694206074</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002100942999495679</v>
+        <v>0.01929014597516277</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5295862719421294</v>
+        <v>0.2447634997487508</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4490720848345698</v>
+        <v>0.003368127275367429</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01068359759505055</v>
+        <v>0.001764528679284796</v>
       </c>
       <c r="D33" t="n">
-        <v>0.428132618322952</v>
+        <v>-9.028538571879789e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4700115513461877</v>
+        <v>0.006826539936453656</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.05628826750556353</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.02815956548344902</v>
+        <v>-0.0009920422931855085</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02420948131337568</v>
+        <v>0.001578082718395982</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.07560927694206079</v>
+        <v>-0.004085027585866698</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01929014597516276</v>
+        <v>0.00210094299949568</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2447634997487502</v>
+        <v>0.5295862719421291</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.003368127275367432</v>
+        <v>0.4490720848345698</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001764528679284755</v>
+        <v>0.01068359759505061</v>
       </c>
       <c r="D35" t="n">
-        <v>-9.028538571871636e-05</v>
+        <v>0.4281326183229519</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00682653993645358</v>
+        <v>0.4700115513461878</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05628826750555774</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2341,19 +2341,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.06558811631338e-05</v>
+        <v>3.06558811631191e-05</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00478807444668594</v>
+        <v>0.004788074446685935</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.009353797589637856</v>
+        <v>-0.00935379758963786</v>
       </c>
       <c r="E36" t="n">
-        <v>0.009415109351964122</v>
+        <v>0.009415109351964098</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9948915399209128</v>
+        <v>0.9948915399209153</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2402,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.713407322158419</v>
+        <v>-2.713407322158418</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5044376034036661</v>
+        <v>0.5044376034036752</v>
       </c>
       <c r="D2" t="n">
-        <v>7.486982883654581e-08</v>
+        <v>7.486982883658673e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02522051520904552</v>
+        <v>-0.02522051520904548</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1001657906734904</v>
+        <v>0.1001657906734903</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8012051561485702</v>
+        <v>0.8012051561485705</v>
       </c>
     </row>
     <row r="4">
@@ -2437,10 +2437,10 @@
         <v>0.2243950733516432</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2334051881144238</v>
+        <v>0.2334051881144239</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3363525367569152</v>
+        <v>0.3363525367569153</v>
       </c>
     </row>
     <row r="5">
@@ -2453,10 +2453,10 @@
         <v>0.8152523591729706</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1732905987053344</v>
+        <v>0.1732905987053342</v>
       </c>
       <c r="D5" t="n">
-        <v>2.544403764027002e-06</v>
+        <v>2.544403764026906e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03529662509742199</v>
+        <v>0.03529662509742187</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1917359483069559</v>
+        <v>0.1917359483069558</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539430379367481</v>
+        <v>0.8539430379367485</v>
       </c>
     </row>
     <row r="7">
@@ -2488,7 +2488,7 @@
         <v>0.1900876275228709</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1450102574315864</v>
+        <v>0.1450102574315863</v>
       </c>
     </row>
     <row r="8">
@@ -2501,10 +2501,10 @@
         <v>0.103322246136425</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1951486965374493</v>
+        <v>0.1951486965374492</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5964905887803371</v>
+        <v>0.5964905887803369</v>
       </c>
     </row>
     <row r="9">
@@ -2520,7 +2520,7 @@
         <v>0.169537988877078</v>
       </c>
       <c r="D9" t="n">
-        <v>2.541527320496866e-07</v>
+        <v>2.541527320496857e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04298175525170747</v>
+        <v>-0.04298175525170726</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2597533292652197</v>
+        <v>0.2597533292652194</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8685729341423553</v>
+        <v>0.8685729341423557</v>
       </c>
     </row>
     <row r="11">
@@ -2546,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2734774183375255</v>
+        <v>-0.2734774183375258</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2785592488643225</v>
+        <v>0.2785592488643224</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3262197079678811</v>
+        <v>0.3262197079678805</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08217580196393699</v>
+        <v>0.08217580196393687</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2587287215011221</v>
+        <v>0.2587287215011222</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7507779355278755</v>
+        <v>0.7507779355278761</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03995788006654509</v>
+        <v>0.03995788006654485</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2568297818201681</v>
+        <v>0.2568297818201689</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8763631618417491</v>
+        <v>0.8763631618417502</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05219347665548984</v>
+        <v>-0.05219347665549038</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2603443755509272</v>
+        <v>0.2603443755509274</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8411062907988991</v>
+        <v>0.8411062907988976</v>
       </c>
     </row>
     <row r="15">
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1183975653249732</v>
+        <v>0.118397565324973</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2570359266688499</v>
+        <v>0.2570359266688501</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6450665788994046</v>
+        <v>0.6450665788994054</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.002815011182394092</v>
+        <v>-0.002815011182394325</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2376522981116133</v>
+        <v>0.237652298111613</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9905492122003404</v>
+        <v>0.9905492122003396</v>
       </c>
     </row>
     <row r="17">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1056709152111883</v>
+        <v>0.1056709152111882</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2542906688395361</v>
+        <v>0.2542906688395365</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677738089343457</v>
+        <v>0.6777380893434579</v>
       </c>
     </row>
     <row r="18">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1371135645044841</v>
+        <v>-0.1371135645044842</v>
       </c>
       <c r="C18" t="n">
-        <v>0.263407233024123</v>
+        <v>0.2634072330241227</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6026884109023538</v>
+        <v>0.6026884109023529</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02475228489410887</v>
+        <v>-0.02475228489410906</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2524092973060099</v>
+        <v>0.2524092973060098</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9218814119969664</v>
+        <v>0.9218814119969658</v>
       </c>
     </row>
     <row r="20">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07246351166486088</v>
+        <v>-0.07246351166486108</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2666987121614964</v>
+        <v>0.2666987121614957</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7858484583220717</v>
+        <v>0.7858484583220705</v>
       </c>
     </row>
     <row r="21">
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2068090257965718</v>
+        <v>0.2068090257965716</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2439533267288634</v>
+        <v>0.2439533267288631</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3965827100652911</v>
+        <v>0.3965827100652909</v>
       </c>
     </row>
     <row r="22">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1686288808585497</v>
+        <v>-0.16862888085855</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269406139463471</v>
+        <v>0.2694061394634717</v>
       </c>
       <c r="D22" t="n">
-        <v>0.531362083301115</v>
+        <v>0.5313620833011155</v>
       </c>
     </row>
     <row r="23">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.499777075300137</v>
+        <v>-0.4997770753001372</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2864601345898814</v>
+        <v>0.2864601345898818</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08104313551548828</v>
+        <v>0.08104313551548872</v>
       </c>
     </row>
     <row r="24">
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9365913375115046</v>
+        <v>0.9365913375115045</v>
       </c>
       <c r="C24" t="n">
         <v>0.1482811706186312</v>
@@ -2773,10 +2773,10 @@
         <v>-0.5782787024565067</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1145314111910344</v>
+        <v>0.1145314111910343</v>
       </c>
       <c r="D25" t="n">
-        <v>4.439337879296676e-07</v>
+        <v>4.439337879296568e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04352683570925985</v>
+        <v>-0.04352683570925996</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1612096759797175</v>
+        <v>0.1612096759797174</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7871591884734985</v>
+        <v>0.7871591884734979</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07467572557157245</v>
+        <v>-0.07467572557157257</v>
       </c>
       <c r="C28" t="n">
         <v>0.1614290026159799</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6436570199176099</v>
+        <v>0.6436570199176094</v>
       </c>
     </row>
     <row r="29">
@@ -2837,10 +2837,10 @@
         <v>0.09777326958921104</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543602583723145</v>
+        <v>0.1543602583723144</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5264661972233939</v>
+        <v>0.5264661972233937</v>
       </c>
     </row>
     <row r="30">
@@ -2850,77 +2850,77 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.006367932838418618</v>
+        <v>0.006367932838418621</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006881672701727233</v>
+        <v>0.006881672701727239</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3547856158497277</v>
+        <v>0.3547856158497279</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002450883409209241</v>
+        <v>0.2275650381150179</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007127711187841283</v>
+        <v>0.1144549283876821</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7309569941465313</v>
+        <v>0.04678402178782457</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01034291492939445</v>
+        <v>-0.004998614827289059</v>
       </c>
       <c r="C32" t="n">
-        <v>0.05138615505935789</v>
+        <v>0.008307994570919569</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8404810151443459</v>
+        <v>0.5473983322894213</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.227565038115018</v>
+        <v>-0.002450883409209261</v>
       </c>
       <c r="C33" t="n">
-        <v>0.114454928387682</v>
+        <v>0.007127711187841269</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04678402178782429</v>
+        <v>0.7309569941465286</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.00499861482728905</v>
+        <v>0.01034291492939454</v>
       </c>
       <c r="C34" t="n">
-        <v>0.008307994570919621</v>
+        <v>0.05138615505935781</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5473983322894246</v>
+        <v>0.8404810151443443</v>
       </c>
     </row>
     <row r="35">
@@ -2930,13 +2930,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.004172683243731372</v>
+        <v>-0.004172683243731415</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02223526945739788</v>
+        <v>0.02223526945739796</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8511427450377161</v>
+        <v>0.8511427450377151</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.215</v>
+        <v>0.351</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.059</v>
+        <v>0.016</v>
       </c>
       <c r="E6" t="n">
-        <v>0.156</v>
+        <v>0.335</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.392</v>
+        <v>-0.215</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.028</v>
+        <v>-0.059</v>
       </c>
       <c r="E7" t="n">
-        <v>0.364</v>
+        <v>0.156</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.095</v>
+        <v>-0.001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09</v>
+        <v>-0.001</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.054</v>
+        <v>0.044</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.023</v>
+        <v>0.026</v>
       </c>
       <c r="E9" t="n">
-        <v>0.031</v>
+        <v>0.018</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001</v>
+        <v>0.025</v>
       </c>
       <c r="E10" t="n">
-        <v>0.035</v>
+        <v>0.008</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.044</v>
+        <v>0.013</v>
       </c>
       <c r="D11" t="n">
-        <v>0.026</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.018</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.033</v>
+        <v>0.368</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008</v>
+        <v>0.362</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.351</v>
+        <v>-0.012</v>
       </c>
       <c r="D14" t="n">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="E14" t="n">
-        <v>0.335</v>
+        <v>0.007</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.019</v>
+        <v>0.036</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.012</v>
+        <v>0.035</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.185</v>
+        <v>-0.181</v>
       </c>
       <c r="D16" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="E16" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.096</v>
+        <v>0.01</v>
       </c>
       <c r="D17" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="E17" t="n">
-        <v>0.078</v>
+        <v>0.006</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.09</v>
+        <v>-0.019</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.03</v>
+        <v>0.007</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06</v>
+        <v>0.012</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.181</v>
+        <v>0.007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.013</v>
+        <v>-0.005</v>
       </c>
       <c r="E19" t="n">
-        <v>0.168</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.002</v>
+        <v>0.021</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.001</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.013</v>
+        <v>-0.054</v>
       </c>
       <c r="D23" t="n">
-        <v>0.006</v>
+        <v>-0.023</v>
       </c>
       <c r="E23" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.059</v>
+        <v>0.075</v>
       </c>
       <c r="D24" t="n">
-        <v>0.021</v>
+        <v>0.005</v>
       </c>
       <c r="E24" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.008</v>
+        <v>-0.015</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.007</v>
+        <v>-0.032</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001</v>
+        <v>-0.017</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.014</v>
+        <v>-0.095</v>
       </c>
       <c r="D26" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.09</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.012</v>
+        <v>0.076</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.007</v>
+        <v>0.074</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.368</v>
+        <v>-0.096</v>
       </c>
       <c r="D28" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="E28" t="n">
-        <v>0.362</v>
+        <v>0.078</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.015</v>
+        <v>-0.008</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.032</v>
+        <v>-0.007</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.017</v>
+        <v>0.001</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.076</v>
+        <v>0.185</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002</v>
+        <v>0.015</v>
       </c>
       <c r="E30" t="n">
-        <v>0.074</v>
+        <v>0.17</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01</v>
+        <v>-0.392</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004</v>
+        <v>-0.028</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006</v>
+        <v>0.364</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.075</v>
+        <v>-0.09</v>
       </c>
       <c r="D32" t="n">
-        <v>0.005</v>
+        <v>-0.03</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1397,13 +1397,13 @@
         <v>0.1624039162238811</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858123712730965</v>
+        <v>1.858123712730966</v>
       </c>
       <c r="F2" t="n">
         <v>1.149442947861497</v>
       </c>
       <c r="G2" t="n">
-        <v>1.858070037641442</v>
+        <v>1.858070037641443</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>2.02836611587179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142797777609084</v>
+        <v>0.1142797777609029</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299168</v>
+        <v>1.804381867299179</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444411</v>
+        <v>2.252350364444401</v>
       </c>
       <c r="F2" t="n">
-        <v>1.75058792474424e-70</v>
+        <v>1.750587924717338e-70</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546852</v>
+        <v>-0.004454066658546844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02264676650011667</v>
+        <v>0.02264676650011666</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04884091336506373</v>
+        <v>-0.04884091336506371</v>
       </c>
       <c r="E3" t="n">
         <v>0.03993278004797002</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8440813962195438</v>
+        <v>0.844081396219544</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464318</v>
+        <v>-0.03389366488464309</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05785807270287899</v>
+        <v>0.05785807270287898</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.147293403597186</v>
+        <v>-0.1472934035971859</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07950607382789966</v>
+        <v>0.07950607382789973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5580052088357444</v>
+        <v>0.5580052088357452</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006875661103275418</v>
+        <v>-0.006875661103275386</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03808494585975138</v>
+        <v>0.03808494585975133</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154596</v>
+        <v>-0.08152078334154585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06776946113499512</v>
+        <v>0.06776946113499509</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8567326745156677</v>
+        <v>0.8567326745156683</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856113264</v>
+        <v>-0.001188297856113215</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04119983828117575</v>
+        <v>0.0411998382811757</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609235</v>
+        <v>-0.08193849705609219</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07956190134386582</v>
+        <v>0.07956190134386576</v>
       </c>
       <c r="F6" t="n">
-        <v>0.976990369015947</v>
+        <v>0.9769903690159479</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06305858053336846</v>
+        <v>-0.06305858053336845</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04059008063935424</v>
+        <v>0.0405900806393542</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1426136767160793</v>
+        <v>-0.1426136767160792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01649651564934239</v>
+        <v>0.01649651564934231</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868605</v>
+        <v>0.1202926126868602</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06505644283206324</v>
+        <v>-0.06505644283206323</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04132988827693289</v>
+        <v>0.04132988827693285</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1460615353399159</v>
+        <v>-0.1460615353399158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01594864967578941</v>
+        <v>0.01594864967578934</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1154695580659505</v>
+        <v>0.1154695580659503</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02905623760645399</v>
+        <v>-0.02905623760645398</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03942354109662612</v>
+        <v>0.03942354109662607</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1063249582988759</v>
+        <v>-0.1063249582988758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596791</v>
+        <v>0.04821248308596782</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4611055694915076</v>
+        <v>0.4611055694915072</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.06885067313730633</v>
+        <v>-0.06885067313730658</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06211585669370268</v>
+        <v>0.06211585669370245</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258148</v>
+        <v>-0.1905955151258146</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05289416885120216</v>
+        <v>0.05289416885120145</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2676789754318686</v>
+        <v>0.267678975431865</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1221748468931793</v>
+        <v>-0.1221748468931794</v>
       </c>
       <c r="C11" t="n">
-        <v>0.060924355835231</v>
+        <v>0.06092435583523088</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2415843901115347</v>
+        <v>-0.2415843901115346</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674823832</v>
+        <v>-0.002765303674824179</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04492530998442472</v>
+        <v>0.04492530998442407</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07838540326732411</v>
+        <v>-0.07838540326732424</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06092691482148881</v>
+        <v>0.06092691482148863</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065818</v>
+        <v>-0.1977999620065816</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193356</v>
+        <v>0.04102915547193309</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1982518618524645</v>
+        <v>0.1982518618524625</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033667</v>
+        <v>0.008522193482033523</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05836873363374091</v>
+        <v>0.05836873363374077</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1058784222633102</v>
+        <v>-0.1058784222633101</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1229228092273776</v>
+        <v>0.1229228092273772</v>
       </c>
       <c r="F13" t="n">
-        <v>0.883916541523884</v>
+        <v>0.8839165415238857</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04039308737240783</v>
+        <v>-0.04039308737240804</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615595</v>
+        <v>0.05674181331615587</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1516049978895687</v>
+        <v>-0.1516049978895688</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07081882314475307</v>
+        <v>0.07081882314475271</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642792</v>
+        <v>0.4765420859642762</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1154125116566347</v>
+        <v>-0.1154125116566348</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06052942681222915</v>
+        <v>0.06052942681222892</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2340480082134569</v>
+        <v>-0.2340480082134566</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003222984900187548</v>
+        <v>0.003222984900186951</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05655719180604791</v>
+        <v>0.0565571918060466</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1015943982225828</v>
+        <v>-0.1015943982225829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05923345190504571</v>
+        <v>0.05923345190504548</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364579</v>
+        <v>-0.2176898306364575</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01450103419129223</v>
+        <v>0.01450103419129166</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154487</v>
+        <v>0.08631728613154327</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509285</v>
+        <v>-0.08898691774509297</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358287</v>
+        <v>0.05739926877358288</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2014874172802498</v>
+        <v>-0.20148741728025</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02351358179006414</v>
+        <v>0.02351358179006403</v>
       </c>
       <c r="F17" t="n">
-        <v>0.121066052601449</v>
+        <v>0.1210660526014484</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0453506918551119</v>
+        <v>-0.04535069185511192</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06190696804401335</v>
+        <v>0.06190696804401331</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1666861196134501</v>
+        <v>-0.16668611961345</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0759847359032263</v>
+        <v>0.07598473590322619</v>
       </c>
       <c r="F18" t="n">
-        <v>0.463825619620801</v>
+        <v>0.4638256196208006</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01255984200078615</v>
+        <v>-0.01255984200078628</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072953</v>
+        <v>0.06121386203072934</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356199</v>
+        <v>-0.1325368069356197</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340476</v>
+        <v>0.1074171229340471</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8374317271342953</v>
+        <v>0.8374317271342933</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425857</v>
+        <v>-0.06233504608425874</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06145398822825729</v>
+        <v>0.06145398822825707</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1827826497179913</v>
+        <v>-0.182782649717991</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05811255754947416</v>
+        <v>0.05811255754947356</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3104220364751142</v>
+        <v>0.310422036475111</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05962283374156466</v>
+        <v>-0.0596228337415648</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066321</v>
+        <v>0.05902325596066299</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747536</v>
+        <v>-0.1753062896747533</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0560606221916243</v>
+        <v>0.05606062219162373</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3124194392956631</v>
+        <v>0.3124194392956601</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.05042994771853615</v>
+        <v>-0.05042994771853605</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06074201625882807</v>
+        <v>0.06074201625882786</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341856</v>
+        <v>-0.1694821119341851</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711325</v>
+        <v>0.06862221649711295</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516449</v>
+        <v>0.4064077928516442</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641241</v>
+        <v>-0.06558214032641256</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05881748257355478</v>
+        <v>0.05881748257355454</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.180862287831892</v>
+        <v>-0.1808622878318917</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04969800717906722</v>
+        <v>0.0496980071790666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412757</v>
+        <v>0.2648457060412724</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007941985483982042</v>
+        <v>0.00794198548398199</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700066</v>
+        <v>0.05021926948700062</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09048597404045051</v>
+        <v>-0.0904859740404505</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1063699450084146</v>
+        <v>0.1063699450084145</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8743416143866736</v>
+        <v>0.8743416143866743</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04275887538360304</v>
+        <v>0.042758875383603</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02899531241893934</v>
+        <v>0.02899531241893929</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800501</v>
+        <v>-0.01407089267800497</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09958864344521109</v>
+        <v>0.09958864344521096</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1402979641274842</v>
+        <v>0.140297964127484</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01702773825292623</v>
+        <v>0.01702773825292596</v>
       </c>
       <c r="C26" t="n">
         <v>0.03628839344655836</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914749</v>
+        <v>-0.05409620595914776</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499994</v>
+        <v>0.08815168246499967</v>
       </c>
       <c r="F26" t="n">
-        <v>0.638902577413146</v>
+        <v>0.6389025774131514</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0477626583668757</v>
+        <v>0.04776265836687563</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03631243242202285</v>
+        <v>0.0363124324220228</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02340840137133365</v>
+        <v>-0.02340840137133362</v>
       </c>
       <c r="E27" t="n">
-        <v>0.118933718105085</v>
+        <v>0.1189337181050849</v>
       </c>
       <c r="F27" t="n">
         <v>0.1884006237939559</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03849528892250786</v>
+        <v>0.03849528892250782</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03513724130562731</v>
+        <v>0.03513724130562729</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0303724385526148</v>
+        <v>-0.03037243855261482</v>
       </c>
       <c r="E28" t="n">
         <v>0.1073630163976305</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2732672273052891</v>
+        <v>0.2732672273052895</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649758</v>
+        <v>0.005380707237649677</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03555582911908341</v>
+        <v>0.0355558291190834</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06430743727621425</v>
+        <v>-0.06430743727621431</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506885175151377</v>
+        <v>0.07506885175151366</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731915</v>
+        <v>0.8797144375731932</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.003320233432694924</v>
+        <v>-0.003320233432694946</v>
       </c>
       <c r="C30" t="n">
         <v>0.05015882681790457</v>
@@ -2176,7 +2176,7 @@
         <v>0.09498926063717983</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604787</v>
+        <v>0.9472230553604783</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0003007900296359818</v>
+        <v>0.434691752414487</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00194849875400304</v>
+        <v>0.01226316783229004</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.00411977741140311</v>
+        <v>0.4106563851268284</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003518197352131146</v>
+        <v>0.4587271197021456</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8773178945520025</v>
+        <v>3.233495669641422e-275</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.434691752414487</v>
+        <v>-0.000300790029635988</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01226316783229012</v>
+        <v>0.001948498754002998</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4106563851268282</v>
+        <v>-0.004119777411403034</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4587271197021457</v>
+        <v>0.003518197352131058</v>
       </c>
       <c r="F32" t="n">
-        <v>3.233495669664968e-275</v>
+        <v>0.8773178945519974</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002152465134243705</v>
+        <v>0.0002152465134243676</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001692811914196194</v>
+        <v>0.001692811914196195</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003102603871000478</v>
+        <v>-0.003102603871000482</v>
       </c>
       <c r="E33" t="n">
         <v>0.003533096897849218</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8988191168516205</v>
+        <v>0.898819116851622</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.001543895502937995</v>
+        <v>-0.009549274128434508</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001581102582020386</v>
+        <v>0.005236570244876886</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004642799619561239</v>
+        <v>-0.0198127632109073</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001555008613685249</v>
+        <v>0.0007142149540382819</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3288327776696792</v>
+        <v>0.06821647769402343</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.009549274128434492</v>
+        <v>-0.001543895502937994</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005236570244876963</v>
+        <v>0.001581102582020391</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.01981276321090743</v>
+        <v>-0.004642799619561247</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0007142149540384467</v>
+        <v>0.00155500861368526</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0682164776940279</v>
+        <v>0.328832777669681</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2353,10 +2353,10 @@
         <v>-2.589409473419876</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5031045718144671</v>
+        <v>0.503104571814473</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631191234e-07</v>
+        <v>2.648809631192085e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254682</v>
+        <v>0.04318498161254672</v>
       </c>
       <c r="C3" t="n">
         <v>0.1065435099103227</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6852370218892518</v>
+        <v>0.6852370218892525</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3414291668173601</v>
+        <v>0.34142916681736</v>
       </c>
       <c r="C4" t="n">
         <v>0.2253255698874617</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1297039406487215</v>
+        <v>0.1297039406487217</v>
       </c>
     </row>
     <row r="5">
@@ -2404,7 +2404,7 @@
         <v>0.1748738694459633</v>
       </c>
       <c r="D5" t="n">
-        <v>1.52917937368752e-05</v>
+        <v>1.529179373687525e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2417,10 +2417,10 @@
         <v>-0.1784790633221358</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2136767975499139</v>
+        <v>0.213676797549914</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4035624257334069</v>
+        <v>0.4035624257334071</v>
       </c>
     </row>
     <row r="7">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09566226402322781</v>
+        <v>-0.09566226402322776</v>
       </c>
       <c r="C8" t="n">
         <v>0.2104081937814554</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6493604462404061</v>
+        <v>0.6493604462404063</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.070551836763826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645067</v>
+        <v>0.1703735435645068</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524827e-10</v>
+        <v>3.309132456524959e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828863</v>
+        <v>0.09554047552828891</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992087</v>
+        <v>0.2825463042992091</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7352569730944855</v>
+        <v>0.7352569730944851</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2120911081526135</v>
+        <v>0.2120911081526139</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2723979177423711</v>
+        <v>0.2723979177423712</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4362108592987928</v>
+        <v>0.436210859298792</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2444325881052901</v>
+        <v>-0.2444325881052896</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3070429002527503</v>
+        <v>0.3070429002527508</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259819868592513</v>
+        <v>0.4259819868592528</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.249606268006445</v>
+        <v>0.2496062680064454</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718411</v>
+        <v>0.2703388739718412</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3558462903511537</v>
+        <v>0.355846290351153</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2898175614664934</v>
+        <v>0.2898175614664939</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071133</v>
+        <v>0.2803190610071127</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011901132184984</v>
+        <v>0.3011901132184965</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.33982051665361</v>
+        <v>0.3398205166536105</v>
       </c>
       <c r="C15" t="n">
         <v>0.2686928948980222</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404612</v>
+        <v>0.2059727340404605</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1269289753942506</v>
+        <v>0.1269289753942507</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2681297806792983</v>
+        <v>0.2681297806792989</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959074</v>
+        <v>0.6359375739959077</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766418</v>
+        <v>0.1818641012766421</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752098117728792</v>
+        <v>0.2752098117728795</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920085</v>
+        <v>0.5087278635920081</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3864469590948249</v>
+        <v>0.3864469590948251</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451036</v>
+        <v>0.2676140000451044</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1487260018447603</v>
+        <v>0.1487260018447613</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1244402747085719</v>
+        <v>0.1244402747085723</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2778369782669698</v>
+        <v>0.2778369782669697</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218904</v>
+        <v>0.6542329221218893</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230517</v>
+        <v>0.2308101909230521</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2780833406064974</v>
+        <v>0.2780833406064984</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4065367134519954</v>
+        <v>0.4065367134519963</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2330335342161663</v>
+        <v>0.2330335342161668</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673196819648368</v>
+        <v>0.2673196819648372</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885942</v>
+        <v>0.3833496727885939</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05077438800389018</v>
+        <v>0.05077438800389073</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476465</v>
+        <v>0.2847519964476461</v>
       </c>
       <c r="D22" t="n">
-        <v>0.858478810092168</v>
+        <v>0.8584788100921662</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197985</v>
+        <v>-0.01709893916197954</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712264</v>
+        <v>0.2925638244712275</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9533940447535775</v>
+        <v>0.9533940447535785</v>
       </c>
     </row>
     <row r="24">
@@ -2708,7 +2708,7 @@
         <v>0.1599839947303407</v>
       </c>
       <c r="D24" t="n">
-        <v>4.489744023837655e-08</v>
+        <v>4.489744023837672e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5929479835845773</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169096769872892</v>
+        <v>0.1169096769872893</v>
       </c>
       <c r="D25" t="n">
-        <v>3.939732815876591e-07</v>
+        <v>3.939732815876612e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.13835121129842</v>
+        <v>-0.1383512112984199</v>
       </c>
       <c r="C26" t="n">
         <v>0.1508106992062235</v>
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08371120214432412</v>
+        <v>-0.08371120214432408</v>
       </c>
       <c r="C27" t="n">
         <v>0.1573755377854196</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947813778609781</v>
+        <v>0.5947813778609785</v>
       </c>
     </row>
     <row r="28">
@@ -2772,7 +2772,7 @@
         <v>0.1482387657619014</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532697926760262</v>
+        <v>0.4532697926760263</v>
       </c>
     </row>
     <row r="29">
@@ -2782,45 +2782,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.318642717107856</v>
+        <v>-0.3186427171078559</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1545279196022677</v>
+        <v>0.1545279196022679</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03920394898235115</v>
+        <v>0.03920394898235145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0128665535497358</v>
+        <v>0.01704998181899489</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008184547747939364</v>
+        <v>0.0499314946229784</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1159379568009106</v>
+        <v>0.7327516797914981</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01704998181899489</v>
+        <v>-0.01286655354973583</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04993149462297902</v>
+        <v>0.00818454774793914</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7327516797915014</v>
+        <v>0.1159379568008999</v>
       </c>
     </row>
     <row r="32">
@@ -2830,45 +2830,45 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01479837462877071</v>
+        <v>0.01479837462877072</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007085296655765552</v>
+        <v>0.007085296655765545</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03674343959712796</v>
+        <v>0.03674343959712774</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.002589705940363003</v>
+        <v>0.01865810867195035</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007293744184584138</v>
+        <v>0.022866064326211</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7225457586062501</v>
+        <v>0.414515138921986</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01865810867195038</v>
+        <v>0.002589705940363016</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02286606432621098</v>
+        <v>0.007293744184584142</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4145151389219849</v>
+        <v>0.7225457586062489</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.351</v>
+        <v>-0.001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.016</v>
+        <v>-0.002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.335</v>
+        <v>-0.001</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.215</v>
+        <v>-0.096</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.059</v>
+        <v>0.018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.156</v>
+        <v>0.078</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002</v>
+        <v>0.021</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.044</v>
+        <v>-0.007</v>
       </c>
       <c r="D9" t="n">
-        <v>0.026</v>
+        <v>-0.025</v>
       </c>
       <c r="E9" t="n">
-        <v>0.018</v>
+        <v>-0.018</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.013</v>
+        <v>0.368</v>
       </c>
       <c r="D11" t="n">
         <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.362</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.001</v>
+        <v>0.014</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.008</v>
+        <v>0.015</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.007</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.368</v>
+        <v>0.044</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006</v>
+        <v>0.026</v>
       </c>
       <c r="E13" t="n">
-        <v>0.362</v>
+        <v>0.018</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.012</v>
+        <v>-0.181</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
       <c r="E14" t="n">
-        <v>0.007</v>
+        <v>0.168</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.036</v>
+        <v>0.076</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E15" t="n">
-        <v>0.035</v>
+        <v>0.074</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.181</v>
+        <v>0.01</v>
       </c>
       <c r="D16" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.168</v>
+        <v>0.006</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01</v>
+        <v>-0.008</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.019</v>
+        <v>0.351</v>
       </c>
       <c r="D18" t="n">
-        <v>0.007</v>
+        <v>0.016</v>
       </c>
       <c r="E18" t="n">
-        <v>0.012</v>
+        <v>0.335</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.007</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.002</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.014</v>
+        <v>-0.054</v>
       </c>
       <c r="D20" t="n">
-        <v>0.015</v>
+        <v>-0.023</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.031</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.059</v>
+        <v>0.185</v>
       </c>
       <c r="D21" t="n">
-        <v>0.021</v>
+        <v>0.015</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="F21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.007</v>
+        <v>-0.215</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.025</v>
+        <v>-0.059</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.018</v>
+        <v>0.156</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.054</v>
+        <v>-0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.023</v>
+        <v>-0.008</v>
       </c>
       <c r="E23" t="n">
-        <v>0.031</v>
+        <v>-0.007</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.075</v>
+        <v>-0.095</v>
       </c>
       <c r="D24" t="n">
         <v>0.005</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.015</v>
+        <v>0.013</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.032</v>
+        <v>0.006</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.017</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.095</v>
+        <v>0.036</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09</v>
+        <v>0.035</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.002</v>
+        <v>0.005</v>
       </c>
       <c r="E27" t="n">
-        <v>0.074</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.096</v>
+        <v>-0.019</v>
       </c>
       <c r="D28" t="n">
-        <v>0.018</v>
+        <v>0.007</v>
       </c>
       <c r="E28" t="n">
-        <v>0.078</v>
+        <v>0.012</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.008</v>
+        <v>-0.392</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.007</v>
+        <v>-0.028</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001</v>
+        <v>0.364</v>
       </c>
       <c r="F29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.185</v>
+        <v>-0.015</v>
       </c>
       <c r="D30" t="n">
-        <v>0.015</v>
+        <v>-0.032</v>
       </c>
       <c r="E30" t="n">
-        <v>0.17</v>
+        <v>-0.017</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.392</v>
+        <v>0.007</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.028</v>
+        <v>-0.005</v>
       </c>
       <c r="E31" t="n">
-        <v>0.364</v>
+        <v>0.002</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1397,7 +1397,7 @@
         <v>0.1624039162238811</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858123712730966</v>
+        <v>1.858123712730965</v>
       </c>
       <c r="F2" t="n">
         <v>1.149442947861497</v>
@@ -1467,16 +1467,16 @@
         <v>2.02836611587179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142797777609029</v>
+        <v>0.1142797777609083</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299179</v>
+        <v>1.804381867299168</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444401</v>
+        <v>2.252350364444411</v>
       </c>
       <c r="F2" t="n">
-        <v>1.750587924717338e-70</v>
+        <v>1.750587924743941e-70</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546844</v>
+        <v>-0.004454066658546854</v>
       </c>
       <c r="C3" t="n">
         <v>0.02264676650011666</v>
@@ -1498,10 +1498,10 @@
         <v>-0.04884091336506371</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03993278004797002</v>
+        <v>0.03993278004797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.844081396219544</v>
+        <v>0.8440813962195437</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464309</v>
+        <v>-0.03389366488464311</v>
       </c>
       <c r="C4" t="n">
         <v>0.05785807270287898</v>
@@ -1523,7 +1523,7 @@
         <v>-0.1472934035971859</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07950607382789973</v>
+        <v>0.0795060738278997</v>
       </c>
       <c r="F4" t="n">
         <v>0.5580052088357452</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006875661103275386</v>
+        <v>-0.006875661103275396</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03808494585975133</v>
+        <v>0.03808494585975135</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154585</v>
+        <v>-0.08152078334154587</v>
       </c>
       <c r="E5" t="n">
         <v>0.06776946113499509</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8567326745156683</v>
+        <v>0.856732674515668</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856113215</v>
+        <v>-0.001188297856113371</v>
       </c>
       <c r="C6" t="n">
         <v>0.0411998382811757</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609219</v>
+        <v>-0.08193849705609235</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07956190134386576</v>
+        <v>0.07956190134386562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9769903690159479</v>
+        <v>0.9769903690159449</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06305858053336845</v>
+        <v>-0.06305858053336842</v>
       </c>
       <c r="C7" t="n">
         <v>0.0405900806393542</v>
@@ -1598,10 +1598,10 @@
         <v>-0.1426136767160792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01649651564934231</v>
+        <v>0.01649651564934235</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868602</v>
+        <v>0.1202926126868604</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06505644283206323</v>
+        <v>-0.0650564428320632</v>
       </c>
       <c r="C8" t="n">
         <v>0.04132988827693285</v>
@@ -1623,10 +1623,10 @@
         <v>-0.1460615353399158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01594864967578934</v>
+        <v>0.01594864967578936</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1154695580659503</v>
+        <v>0.1154695580659504</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1642,16 +1642,16 @@
         <v>-0.02905623760645398</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03942354109662607</v>
+        <v>0.0394235410966261</v>
       </c>
       <c r="D9" t="n">
         <v>-0.1063249582988758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596782</v>
+        <v>0.04821248308596788</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4611055694915072</v>
+        <v>0.4611055694915076</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.06885067313730658</v>
+        <v>-0.06885067313730646</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06211585669370245</v>
+        <v>0.06211585669370253</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258146</v>
+        <v>-0.1905955151258147</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05289416885120145</v>
+        <v>0.05289416885120174</v>
       </c>
       <c r="F10" t="n">
-        <v>0.267678975431865</v>
+        <v>0.2676789754318667</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1692,16 +1692,16 @@
         <v>-0.1221748468931794</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06092435583523088</v>
+        <v>0.06092435583523097</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2415843901115346</v>
+        <v>-0.2415843901115348</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674824179</v>
+        <v>-0.002765303674823999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04492530998442407</v>
+        <v>0.04492530998442441</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07838540326732424</v>
+        <v>-0.07838540326732421</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06092691482148863</v>
+        <v>0.06092691482148856</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065816</v>
+        <v>-0.1977999620065814</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193309</v>
+        <v>0.04102915547193299</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1982518618524625</v>
+        <v>0.1982518618524621</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033523</v>
+        <v>0.008522193482033581</v>
       </c>
       <c r="C13" t="n">
         <v>0.05836873363374077</v>
@@ -1751,7 +1751,7 @@
         <v>0.1229228092273772</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8839165415238857</v>
+        <v>0.8839165415238849</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04039308737240804</v>
+        <v>-0.04039308737240788</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615587</v>
+        <v>0.05674181331615584</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1516049978895688</v>
+        <v>-0.1516049978895686</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07081882314475271</v>
+        <v>0.07081882314475282</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642762</v>
+        <v>0.4765420859642776</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1792,16 +1792,16 @@
         <v>-0.1154125116566348</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06052942681222892</v>
+        <v>0.06052942681222902</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2340480082134566</v>
+        <v>-0.2340480082134568</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003222984900186951</v>
+        <v>0.003222984900187201</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0565571918060466</v>
+        <v>0.05655719180604712</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1817,16 +1817,16 @@
         <v>-0.1015943982225829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05923345190504548</v>
+        <v>0.05923345190504559</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364575</v>
+        <v>-0.2176898306364577</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01450103419129166</v>
+        <v>0.01450103419129194</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154327</v>
+        <v>0.08631728613154406</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,16 +1839,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509297</v>
+        <v>-0.08898691774509294</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358288</v>
+        <v>0.05739926877358286</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.20148741728025</v>
+        <v>-0.2014874172802499</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02351358179006403</v>
+        <v>0.02351358179006402</v>
       </c>
       <c r="F17" t="n">
         <v>0.1210660526014484</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04535069185511192</v>
+        <v>-0.04535069185511181</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06190696804401331</v>
+        <v>0.06190696804401327</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.16668611961345</v>
+        <v>-0.1666861196134499</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07598473590322619</v>
+        <v>0.07598473590322624</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4638256196208006</v>
+        <v>0.4638256196208014</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01255984200078628</v>
+        <v>-0.01255984200078624</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072934</v>
+        <v>0.06121386203072943</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356197</v>
+        <v>-0.1325368069356198</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340471</v>
+        <v>0.1074171229340473</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8374317271342933</v>
+        <v>0.8374317271342939</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425874</v>
+        <v>-0.06233504608425867</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06145398822825707</v>
+        <v>0.06145398822825709</v>
       </c>
       <c r="D20" t="n">
         <v>-0.182782649717991</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05811255754947356</v>
+        <v>0.05811255754947368</v>
       </c>
       <c r="F20" t="n">
-        <v>0.310422036475111</v>
+        <v>0.3104220364751118</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0596228337415648</v>
+        <v>-0.05962283374156475</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066299</v>
+        <v>0.05902325596066306</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747533</v>
+        <v>-0.1753062896747534</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05606062219162373</v>
+        <v>0.05606062219162392</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3124194392956601</v>
+        <v>0.3124194392956611</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1967,16 +1967,16 @@
         <v>-0.05042994771853605</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06074201625882786</v>
+        <v>0.06074201625882798</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341851</v>
+        <v>-0.1694821119341853</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711295</v>
+        <v>0.06862221649711318</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516442</v>
+        <v>0.4064077928516452</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641256</v>
+        <v>-0.06558214032641249</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05881748257355454</v>
+        <v>0.05881748257355463</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1808622878318917</v>
+        <v>-0.1808622878318918</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0496980071790666</v>
+        <v>0.04969800717906683</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412724</v>
+        <v>0.2648457060412739</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.00794198548398199</v>
+        <v>0.007941985483981985</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700062</v>
+        <v>0.05021926948700068</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0904859740404505</v>
+        <v>-0.09048597404045061</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1063699450084145</v>
+        <v>0.1063699450084146</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8743416143866743</v>
+        <v>0.8743416143866745</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.042758875383603</v>
+        <v>0.04275887538360298</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02899531241893929</v>
+        <v>0.0289953124189394</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800497</v>
+        <v>-0.01407089267800519</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09958864344521096</v>
+        <v>0.09958864344521115</v>
       </c>
       <c r="F25" t="n">
-        <v>0.140297964127484</v>
+        <v>0.1402979641274855</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01702773825292596</v>
+        <v>0.01702773825292613</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03628839344655836</v>
+        <v>0.03628839344655835</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914776</v>
+        <v>-0.05409620595914756</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499967</v>
+        <v>0.08815168246499981</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6389025774131514</v>
+        <v>0.6389025774131478</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04776265836687563</v>
+        <v>0.04776265836687568</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0363124324220228</v>
+        <v>0.03631243242202282</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02340840137133362</v>
+        <v>-0.02340840137133361</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1189337181050849</v>
+        <v>0.118933718105085</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1884006237939559</v>
+        <v>0.1884006237939558</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649677</v>
+        <v>0.005380707237649693</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0355558291190834</v>
+        <v>0.03555582911908339</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06430743727621431</v>
+        <v>-0.06430743727621427</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506885175151366</v>
+        <v>0.07506885175151365</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731932</v>
+        <v>0.8797144375731928</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.003320233432694946</v>
+        <v>-0.003320233432695046</v>
       </c>
       <c r="C30" t="n">
         <v>0.05015882681790457</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1016297275025697</v>
+        <v>-0.1016297275025698</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09498926063717983</v>
+        <v>0.0949892606371797</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604783</v>
+        <v>0.9472230553604767</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.434691752414487</v>
+        <v>-0.001543895502937994</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01226316783229004</v>
+        <v>0.001581102582020392</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4106563851268284</v>
+        <v>-0.004642799619561249</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4587271197021456</v>
+        <v>0.001555008613685262</v>
       </c>
       <c r="F31" t="n">
-        <v>3.233495669641422e-275</v>
+        <v>0.3288327776696814</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.000300790029635988</v>
+        <v>-0.009549274128434504</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001948498754002998</v>
+        <v>0.005236570244876897</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004119777411403034</v>
+        <v>-0.01981276321090731</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003518197352131058</v>
+        <v>0.0007142149540383044</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8773178945519974</v>
+        <v>0.06821647769402407</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0002152465134243676</v>
+        <v>-0.0003007900296359773</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001692811914196195</v>
+        <v>0.001948498754003063</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003102603871000482</v>
+        <v>-0.004119777411403151</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003533096897849218</v>
+        <v>0.003518197352131196</v>
       </c>
       <c r="F33" t="n">
-        <v>0.898819116851622</v>
+        <v>0.8773178945520058</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.009549274128434508</v>
+        <v>0.434691752414487</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005236570244876886</v>
+        <v>0.01226316783229004</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0198127632109073</v>
+        <v>0.4106563851268284</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0007142149540382819</v>
+        <v>0.4587271197021456</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06821647769402343</v>
+        <v>3.233495669641422e-275</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.001543895502937994</v>
+        <v>0.0002152465134243688</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001581102582020391</v>
+        <v>0.001692811914196195</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.004642799619561247</v>
+        <v>-0.003102603871000482</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00155500861368526</v>
+        <v>0.003533096897849219</v>
       </c>
       <c r="F35" t="n">
-        <v>0.328832777669681</v>
+        <v>0.8988191168516214</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2353,10 +2353,10 @@
         <v>-2.589409473419876</v>
       </c>
       <c r="C2" t="n">
-        <v>0.503104571814473</v>
+        <v>0.5031045718144744</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631192085e-07</v>
+        <v>2.648809631192281e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254672</v>
+        <v>0.04318498161254686</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065435099103227</v>
+        <v>0.1065435099103228</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6852370218892525</v>
+        <v>0.6852370218892516</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.34142916681736</v>
+        <v>0.3414291668173601</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2253255698874617</v>
+        <v>0.2253255698874616</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1297039406487217</v>
+        <v>0.1297039406487214</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7562320294942515</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1748738694459633</v>
+        <v>0.1748738694459632</v>
       </c>
       <c r="D5" t="n">
-        <v>1.529179373687525e-05</v>
+        <v>1.529179373687517e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1784790633221358</v>
+        <v>-0.1784790633221359</v>
       </c>
       <c r="C6" t="n">
-        <v>0.213676797549914</v>
+        <v>0.2136767975499138</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4035624257334071</v>
+        <v>0.4035624257334062</v>
       </c>
     </row>
     <row r="7">
@@ -2433,10 +2433,10 @@
         <v>0.1341634292941744</v>
       </c>
       <c r="C7" t="n">
-        <v>0.195320867407642</v>
+        <v>0.1953208674076421</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921537310985465</v>
+        <v>0.4921537310985468</v>
       </c>
     </row>
     <row r="8">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09566226402322776</v>
+        <v>-0.09566226402322772</v>
       </c>
       <c r="C8" t="n">
         <v>0.2104081937814554</v>
@@ -2465,10 +2465,10 @@
         <v>1.070551836763826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645068</v>
+        <v>0.1703735435645066</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524959e-10</v>
+        <v>3.309132456524803e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828891</v>
+        <v>0.09554047552828901</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992091</v>
+        <v>0.2825463042992082</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7352569730944851</v>
+        <v>0.735256973094484</v>
       </c>
     </row>
     <row r="11">
@@ -2497,10 +2497,10 @@
         <v>0.2120911081526139</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2723979177423712</v>
+        <v>0.2723979177423709</v>
       </c>
       <c r="D11" t="n">
-        <v>0.436210859298792</v>
+        <v>0.4362108592987917</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2444325881052896</v>
+        <v>-0.2444325881052897</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3070429002527508</v>
+        <v>0.3070429002527501</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259819868592528</v>
+        <v>0.4259819868592517</v>
       </c>
     </row>
     <row r="13">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2496062680064454</v>
+        <v>0.2496062680064451</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718412</v>
+        <v>0.2703388739718409</v>
       </c>
       <c r="D13" t="n">
         <v>0.355846290351153</v>
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2898175614664939</v>
+        <v>0.2898175614664937</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071127</v>
+        <v>0.2803190610071123</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011901132184965</v>
+        <v>0.3011901132184961</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3398205166536105</v>
+        <v>0.33982051665361</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2686928948980222</v>
+        <v>0.2686928948980221</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404605</v>
+        <v>0.2059727340404611</v>
       </c>
     </row>
     <row r="16">
@@ -2577,10 +2577,10 @@
         <v>0.1269289753942507</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2681297806792989</v>
+        <v>0.2681297806792981</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959077</v>
+        <v>0.6359375739959069</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766421</v>
+        <v>0.1818641012766419</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752098117728795</v>
+        <v>0.2752098117728789</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920081</v>
+        <v>0.5087278635920078</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3864469590948251</v>
+        <v>0.3864469590948249</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451044</v>
+        <v>0.2676140000451041</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1487260018447613</v>
+        <v>0.148726001844761</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1244402747085723</v>
+        <v>0.1244402747085721</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2778369782669697</v>
+        <v>0.2778369782669695</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218893</v>
+        <v>0.6542329221218897</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230521</v>
+        <v>0.2308101909230519</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2780833406064984</v>
+        <v>0.2780833406064973</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4065367134519963</v>
+        <v>0.4065367134519948</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2330335342161668</v>
+        <v>0.2330335342161666</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673196819648372</v>
+        <v>0.2673196819648366</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885939</v>
+        <v>0.3833496727885933</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05077438800389073</v>
+        <v>0.05077438800389044</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476461</v>
+        <v>0.2847519964476458</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8584788100921662</v>
+        <v>0.8584788100921669</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197954</v>
+        <v>-0.01709893916197961</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712275</v>
+        <v>0.2925638244712276</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9533940447535785</v>
+        <v>0.9533940447535783</v>
       </c>
     </row>
     <row r="24">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8751793875051906</v>
+        <v>0.8751793875051905</v>
       </c>
       <c r="C24" t="n">
         <v>0.1599839947303407</v>
@@ -2724,7 +2724,7 @@
         <v>0.1169096769872893</v>
       </c>
       <c r="D25" t="n">
-        <v>3.939732815876612e-07</v>
+        <v>3.939732815876641e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1383512112984199</v>
+        <v>-0.1383512112984198</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1508106992062235</v>
+        <v>0.1508106992062234</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3589418401519302</v>
+        <v>0.3589418401519303</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08371120214432408</v>
+        <v>-0.08371120214432402</v>
       </c>
       <c r="C27" t="n">
         <v>0.1573755377854196</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947813778609785</v>
+        <v>0.5947813778609787</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1111753607446197</v>
+        <v>-0.1111753607446195</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1482387657619014</v>
+        <v>0.1482387657619015</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532697926760263</v>
+        <v>0.4532697926760272</v>
       </c>
     </row>
     <row r="29">
@@ -2785,90 +2785,90 @@
         <v>-0.3186427171078559</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1545279196022679</v>
+        <v>0.1545279196022677</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03920394898235145</v>
+        <v>0.03920394898235115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01704998181899489</v>
+        <v>0.002589705940363017</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0499314946229784</v>
+        <v>0.007293744184584136</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7327516797914981</v>
+        <v>0.7225457586062486</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01286655354973583</v>
+        <v>0.01865810867195037</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00818454774793914</v>
+        <v>0.02286606432621104</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1159379568008999</v>
+        <v>0.4145151389219862</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01479837462877072</v>
+        <v>-0.0128665535497358</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007085296655765545</v>
+        <v>0.008184547747939351</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03674343959712774</v>
+        <v>0.1159379568009101</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01865810867195035</v>
+        <v>0.01704998181899486</v>
       </c>
       <c r="C33" t="n">
-        <v>0.022866064326211</v>
+        <v>0.04993149462297883</v>
       </c>
       <c r="D33" t="n">
-        <v>0.414515138921986</v>
+        <v>0.7327516797915008</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.002589705940363016</v>
+        <v>0.01479837462877072</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007293744184584142</v>
+        <v>0.007085296655765539</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7225457586062489</v>
+        <v>0.0367434395971276</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.059</v>
+        <v>-0.015</v>
       </c>
       <c r="D6" t="n">
-        <v>0.021</v>
+        <v>-0.032</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03799999999999999</v>
+        <v>-0.017</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.095</v>
+        <v>-0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>-0.007</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="D8" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.012</v>
+        <v>0.351</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005</v>
+        <v>0.016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007</v>
+        <v>0.335</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.054</v>
+        <v>0.185</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.023</v>
+        <v>0.015</v>
       </c>
       <c r="E10" t="n">
-        <v>0.031</v>
+        <v>0.17</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.368</v>
+        <v>-0.007</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006</v>
+        <v>-0.025</v>
       </c>
       <c r="E11" t="n">
-        <v>0.362</v>
+        <v>-0.018</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.007</v>
+        <v>-0.181</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.005</v>
+        <v>0.013</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002</v>
+        <v>0.168</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.185</v>
+        <v>-0.054</v>
       </c>
       <c r="D13" t="n">
-        <v>0.015</v>
+        <v>-0.023</v>
       </c>
       <c r="E13" t="n">
-        <v>0.17</v>
+        <v>0.031</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.007</v>
+        <v>-0.392</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.025</v>
+        <v>-0.028</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.018</v>
+        <v>0.364</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.09</v>
+        <v>0.007</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.03</v>
+        <v>-0.005</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06</v>
+        <v>0.002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.014</v>
+        <v>0.036</v>
       </c>
       <c r="D16" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.035</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.096</v>
+        <v>0.368</v>
       </c>
       <c r="D17" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="E17" t="n">
-        <v>0.078</v>
+        <v>0.362</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.351</v>
+        <v>0.059</v>
       </c>
       <c r="D18" t="n">
-        <v>0.016</v>
+        <v>0.021</v>
       </c>
       <c r="E18" t="n">
-        <v>0.335</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.036</v>
+        <v>-0.215</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001</v>
+        <v>-0.059</v>
       </c>
       <c r="E19" t="n">
-        <v>0.035</v>
+        <v>0.156</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.008</v>
+        <v>0.044</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.007</v>
+        <v>0.026</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001</v>
+        <v>0.018</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.076</v>
+        <v>-0.008</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.002</v>
+        <v>-0.007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.074</v>
+        <v>0.001</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="D22" t="n">
-        <v>0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.001</v>
+        <v>-0.095</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.007</v>
+        <v>0.09</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.044</v>
+        <v>-0.019</v>
       </c>
       <c r="D24" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
       <c r="E24" t="n">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.013</v>
+        <v>-0.096</v>
       </c>
       <c r="D25" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="E25" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.015</v>
+        <v>0.01</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.032</v>
+        <v>0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.017</v>
+        <v>0.006</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.181</v>
+        <v>-0.001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.168</v>
+        <v>-0.001</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.019</v>
+        <v>0.075</v>
       </c>
       <c r="D28" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="E28" t="n">
-        <v>0.012</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.215</v>
+        <v>0.014</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.059</v>
+        <v>0.015</v>
       </c>
       <c r="E29" t="n">
-        <v>0.156</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.001</v>
+        <v>0.033</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002</v>
+        <v>0.025</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="D31" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E31" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.392</v>
+        <v>-0.09</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="E32" t="n">
-        <v>0.364</v>
+        <v>0.06</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1388,10 +1388,10 @@
         <v>6217</v>
       </c>
       <c r="B2" t="n">
-        <v>6055.85286362924</v>
+        <v>6055.852863629239</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9954923524565368</v>
+        <v>0.9954923524565367</v>
       </c>
       <c r="D2" t="n">
         <v>0.1624039162238811</v>
@@ -1403,7 +1403,7 @@
         <v>1.149442947861497</v>
       </c>
       <c r="G2" t="n">
-        <v>1.858070037641443</v>
+        <v>1.858070037641444</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>2.02836611587179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142797777609102</v>
+        <v>0.1142797777609108</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299165</v>
+        <v>1.804381867299163</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444415</v>
+        <v>2.252350364444417</v>
       </c>
       <c r="F2" t="n">
-        <v>1.750587924752775e-70</v>
+        <v>1.75058792475567e-70</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546853</v>
+        <v>-0.004454066658546855</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02264676650011667</v>
+        <v>0.02264676650011666</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04884091336506374</v>
+        <v>-0.04884091336506371</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03993278004797002</v>
+        <v>0.03993278004797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8440813962195438</v>
+        <v>0.8440813962195437</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464319</v>
+        <v>-0.03389366488464313</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05785807270287897</v>
+        <v>0.05785807270287898</v>
       </c>
       <c r="D4" t="n">
         <v>-0.147293403597186</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07950607382789962</v>
+        <v>0.07950607382789968</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5580052088357441</v>
+        <v>0.5580052088357449</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0068756611032754</v>
+        <v>-0.006875661103275409</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03808494585975135</v>
+        <v>0.03808494585975138</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154589</v>
+        <v>-0.08152078334154596</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06776946113499507</v>
+        <v>0.06776946113499514</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8567326745156679</v>
+        <v>0.8567326745156678</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856112933</v>
+        <v>-0.001188297856113334</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04119983828117571</v>
+        <v>0.04119983828117574</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609194</v>
+        <v>-0.08193849705609239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07956190134386606</v>
+        <v>0.07956190134386572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9769903690159534</v>
+        <v>0.9769903690159457</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06305858053336842</v>
+        <v>-0.06305858053336841</v>
       </c>
       <c r="C7" t="n">
         <v>0.04059008063935422</v>
@@ -1598,10 +1598,10 @@
         <v>-0.1426136767160792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01649651564934239</v>
+        <v>0.0164965156493424</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868605</v>
+        <v>0.1202926126868607</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0650564428320632</v>
+        <v>-0.06505644283206317</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04132988827693288</v>
+        <v>0.04132988827693287</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1460615353399158</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02905623760645399</v>
+        <v>-0.02905623760645395</v>
       </c>
       <c r="C9" t="n">
         <v>0.0394235410966261</v>
@@ -1648,10 +1648,10 @@
         <v>-0.1063249582988758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596787</v>
+        <v>0.04821248308596791</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4611055694915073</v>
+        <v>0.4611055694915079</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.06885067313730658</v>
+        <v>-0.0688506731373066</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06211585669370253</v>
+        <v>0.0621158566937026</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258148</v>
+        <v>-0.1905955151258149</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05289416885120161</v>
+        <v>0.05289416885120174</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2676789754318657</v>
+        <v>0.2676789754318663</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1221748468931794</v>
+        <v>-0.1221748468931796</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06092435583523093</v>
+        <v>0.06092435583523102</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2415843901115347</v>
+        <v>-0.241584390111535</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674824054</v>
+        <v>-0.002765303674824082</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04492530998442431</v>
+        <v>0.0449253099844243</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0783854032673242</v>
+        <v>-0.07838540326732436</v>
       </c>
       <c r="C12" t="n">
         <v>0.06092691482148867</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065816</v>
+        <v>-0.1977999620065818</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193323</v>
+        <v>0.04102915547193306</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1982518618524631</v>
+        <v>0.198251861852462</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033582</v>
+        <v>0.008522193482033331</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05836873363374081</v>
+        <v>0.05836873363374088</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1058784222633101</v>
+        <v>-0.1058784222633105</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1229228092273773</v>
+        <v>0.1229228092273772</v>
       </c>
       <c r="F13" t="n">
-        <v>0.883916541523885</v>
+        <v>0.8839165415238884</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04039308737240796</v>
+        <v>-0.04039308737240806</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615582</v>
+        <v>0.05674181331615592</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1516049978895686</v>
+        <v>-0.1516049978895689</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0708188231447527</v>
+        <v>0.0708188231447528</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642767</v>
+        <v>0.4765420859642764</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1154125116566348</v>
+        <v>-0.115412511656635</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06052942681222905</v>
+        <v>0.06052942681222912</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2340480082134568</v>
+        <v>-0.2340480082134571</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00322298490018727</v>
+        <v>0.003222984900187201</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05655719180604728</v>
+        <v>0.05655719180604712</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1015943982225829</v>
+        <v>-0.1015943982225831</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05923345190504564</v>
+        <v>0.05923345190504568</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364578</v>
+        <v>-0.2176898306364581</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01450103419129202</v>
+        <v>0.01450103419129189</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154431</v>
+        <v>0.08631728613154382</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509293</v>
+        <v>-0.08898691774509312</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358281</v>
+        <v>0.05739926877358302</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2014874172802498</v>
+        <v>-0.2014874172802504</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02351358179006394</v>
+        <v>0.02351358179006416</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1210660526014482</v>
+        <v>0.1210660526014487</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04535069185511201</v>
+        <v>-0.04535069185511207</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06190696804401333</v>
+        <v>0.06190696804401337</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1666861196134502</v>
+        <v>-0.1666861196134503</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07598473590322613</v>
+        <v>0.07598473590322616</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4638256196207997</v>
+        <v>0.4638256196207995</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01255984200078625</v>
+        <v>-0.01255984200078644</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072945</v>
+        <v>0.06121386203072948</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356199</v>
+        <v>-0.1325368069356201</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340474</v>
+        <v>0.1074171229340472</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8374317271342938</v>
+        <v>0.8374317271342916</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425871</v>
+        <v>-0.06233504608425895</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06145398822825716</v>
+        <v>0.0614539882282572</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1827826497179912</v>
+        <v>-0.1827826497179915</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05811255754947376</v>
+        <v>0.0581125575494736</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3104220364751119</v>
+        <v>0.3104220364751104</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05962283374156474</v>
+        <v>-0.05962283374156495</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066314</v>
+        <v>0.05902325596066319</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747536</v>
+        <v>-0.1753062896747539</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05606062219162408</v>
+        <v>0.05606062219162397</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3124194392956617</v>
+        <v>0.3124194392956607</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.050429947718536</v>
+        <v>-0.05042994771853632</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06074201625882798</v>
+        <v>0.06074201625882806</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341852</v>
+        <v>-0.1694821119341857</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711323</v>
+        <v>0.06862221649711306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516455</v>
+        <v>0.4064077928516433</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641248</v>
+        <v>-0.06558214032641262</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05881748257355475</v>
+        <v>0.05881748257355471</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.180862287831892</v>
+        <v>-0.1808622878318921</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04969800717906708</v>
+        <v>0.04969800717906686</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412749</v>
+        <v>0.2648457060412736</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007941985483981989</v>
+        <v>0.007941985483981963</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700065</v>
+        <v>0.05021926948700068</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09048597404045054</v>
+        <v>-0.09048597404045064</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1063699450084145</v>
+        <v>0.1063699450084146</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8743416143866743</v>
+        <v>0.8743416143866749</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2042,16 +2042,16 @@
         <v>0.04275887538360298</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02899531241893932</v>
+        <v>0.02899531241893941</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800504</v>
+        <v>-0.01407089267800522</v>
       </c>
       <c r="E25" t="n">
-        <v>0.099588643445211</v>
+        <v>0.09958864344521118</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1402979641274845</v>
+        <v>0.1402979641274857</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01702773825292613</v>
+        <v>0.01702773825292605</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03628839344655832</v>
+        <v>0.03628839344655837</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914751</v>
+        <v>-0.05409620595914767</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499976</v>
+        <v>0.08815168246499978</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6389025774131476</v>
+        <v>0.6389025774131496</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0477626583668756</v>
+        <v>0.04776265836687568</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03631243242202279</v>
+        <v>0.03631243242202282</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02340840137133364</v>
+        <v>-0.02340840137133362</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1189337181050848</v>
+        <v>0.118933718105085</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1884006237939562</v>
+        <v>0.1884006237939557</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03849528892250777</v>
+        <v>0.03849528892250782</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03513724130562726</v>
+        <v>0.03513724130562735</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0303724385526148</v>
+        <v>-0.03037243855261493</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1073630163976304</v>
+        <v>0.1073630163976306</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2732672273052897</v>
+        <v>0.2732672273052903</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649666</v>
+        <v>0.005380707237649719</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03555582911908336</v>
+        <v>0.03555582911908343</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06430743727621424</v>
+        <v>-0.06430743727621432</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506885175151357</v>
+        <v>0.07506885175151376</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731933</v>
+        <v>0.8797144375731925</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.00332023343269494</v>
+        <v>-0.003320233432694858</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0501588268179046</v>
+        <v>0.05015882681790457</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1016297275025698</v>
+        <v>-0.1016297275025696</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09498926063717988</v>
+        <v>0.0949892606371799</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604785</v>
+        <v>0.9472230553604797</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002152465134243675</v>
+        <v>-0.001543895502937994</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001692811914196195</v>
+        <v>0.001581102582020389</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003102603871000483</v>
+        <v>-0.004642799619561244</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003533096897849218</v>
+        <v>0.001555008613685256</v>
       </c>
       <c r="F31" t="n">
-        <v>0.898819116851622</v>
+        <v>0.3288327776696803</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001543895502937995</v>
+        <v>0.4346917524144869</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001581102582020392</v>
+        <v>0.01226316783229007</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00464279961956125</v>
+        <v>0.4106563851268283</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00155500861368526</v>
+        <v>0.4587271197021456</v>
       </c>
       <c r="F32" t="n">
-        <v>0.328832777669681</v>
+        <v>3.233495669651723e-275</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.434691752414487</v>
+        <v>-0.0003007900296359786</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0122631678322901</v>
+        <v>0.001948498754003065</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4106563851268283</v>
+        <v>-0.004119777411403157</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4587271197021457</v>
+        <v>0.0035181973521312</v>
       </c>
       <c r="F33" t="n">
-        <v>3.233495669658714e-275</v>
+        <v>0.8773178945520054</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.009549274128434496</v>
+        <v>-0.009549274128434511</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005236570244876901</v>
+        <v>0.00523657024487689</v>
       </c>
       <c r="D34" t="n">
         <v>-0.01981276321090731</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0007142149540383218</v>
+        <v>0.0007142149540382836</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06821647769402457</v>
+        <v>0.0682164776940235</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0003007900296359825</v>
+        <v>0.0002152465134243679</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001948498754003083</v>
+        <v>0.001692811914196197</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.004119777411403195</v>
+        <v>-0.003102603871000486</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00351819735213123</v>
+        <v>0.003533096897849222</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8773178945520049</v>
+        <v>0.898819116851622</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.589409473419878</v>
+        <v>-2.589409473419879</v>
       </c>
       <c r="C2" t="n">
-        <v>0.503104571814456</v>
+        <v>0.5031045718144678</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631189567e-07</v>
+        <v>2.648809631191243e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254691</v>
+        <v>0.04318498161254693</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065435099103226</v>
+        <v>0.1065435099103227</v>
       </c>
       <c r="D3" t="n">
         <v>0.6852370218892512</v>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.34142916681736</v>
+        <v>0.3414291668173601</v>
       </c>
       <c r="C4" t="n">
         <v>0.2253255698874617</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1297039406487218</v>
+        <v>0.1297039406487216</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7562320294942516</v>
+        <v>0.7562320294942515</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1748738694459631</v>
+        <v>0.1748738694459633</v>
       </c>
       <c r="D5" t="n">
-        <v>1.529179373687494e-05</v>
+        <v>1.529179373687534e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1784790633221359</v>
+        <v>-0.1784790633221358</v>
       </c>
       <c r="C6" t="n">
         <v>0.2136767975499138</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4035624257334062</v>
+        <v>0.4035624257334067</v>
       </c>
     </row>
     <row r="7">
@@ -2436,7 +2436,7 @@
         <v>0.195320867407642</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921537310985465</v>
+        <v>0.4921537310985464</v>
       </c>
     </row>
     <row r="8">
@@ -2449,10 +2449,10 @@
         <v>-0.09566226402322769</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2104081937814554</v>
+        <v>0.2104081937814556</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6493604462404065</v>
+        <v>0.6493604462404069</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.070551836763826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645067</v>
+        <v>0.1703735435645068</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524827e-10</v>
+        <v>3.309132456524959e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828877</v>
+        <v>0.09554047552828994</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992076</v>
+        <v>0.2825463042992086</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7352569730944842</v>
+        <v>0.735256973094482</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2120911081526138</v>
+        <v>0.2120911081526146</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2723979177423699</v>
+        <v>0.2723979177423714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4362108592987899</v>
+        <v>0.436210859298791</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2444325881052896</v>
+        <v>-0.244432588105289</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3070429002527494</v>
+        <v>0.3070429002527503</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259819868592508</v>
+        <v>0.4259819868592534</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2496062680064452</v>
+        <v>0.2496062680064458</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718406</v>
+        <v>0.2703388739718407</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3558462903511522</v>
+        <v>0.3558462903511512</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2898175614664938</v>
+        <v>0.2898175614664946</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071128</v>
+        <v>0.2803190610071122</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011901132184968</v>
+        <v>0.3011901132184945</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3398205166536103</v>
+        <v>0.339820516653611</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2686928948980215</v>
+        <v>0.2686928948980225</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404597</v>
+        <v>0.2059727340404603</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1269289753942508</v>
+        <v>0.1269289753942516</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2681297806792982</v>
+        <v>0.2681297806792983</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959066</v>
+        <v>0.6359375739959048</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766422</v>
+        <v>0.1818641012766427</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752098117728785</v>
+        <v>0.275209811772879</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920065</v>
+        <v>0.5087278635920058</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3864469590948251</v>
+        <v>0.386446959094826</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451033</v>
+        <v>0.2676140000451043</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1487260018447597</v>
+        <v>0.1487260018447603</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1244402747085724</v>
+        <v>0.124440274708573</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2778369782669692</v>
+        <v>0.2778369782669697</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218885</v>
+        <v>0.6542329221218877</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230522</v>
+        <v>0.2308101909230528</v>
       </c>
       <c r="C20" t="n">
-        <v>0.278083340606496</v>
+        <v>0.2780833406064979</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4065367134519922</v>
+        <v>0.406536713451994</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2330335342161666</v>
+        <v>0.2330335342161674</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673196819648367</v>
+        <v>0.267319681964837</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885934</v>
+        <v>0.3833496727885921</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05077438800389069</v>
+        <v>0.05077438800389119</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476451</v>
+        <v>0.2847519964476467</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8584788100921659</v>
+        <v>0.8584788100921653</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197956</v>
+        <v>-0.01709893916197874</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712263</v>
+        <v>0.2925638244712273</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9533940447535783</v>
+        <v>0.9533940447535806</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8751793875051905</v>
+        <v>0.8751793875051906</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1599839947303407</v>
+        <v>0.1599839947303408</v>
       </c>
       <c r="D24" t="n">
-        <v>4.489744023837721e-08</v>
+        <v>4.489744023837755e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5929479835845773</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169096769872893</v>
+        <v>0.1169096769872895</v>
       </c>
       <c r="D25" t="n">
-        <v>3.939732815876641e-07</v>
+        <v>3.939732815876808e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1383512112984199</v>
+        <v>-0.13835121129842</v>
       </c>
       <c r="C26" t="n">
         <v>0.1508106992062233</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3589418401519298</v>
+        <v>0.3589418401519294</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08371120214432409</v>
+        <v>-0.08371120214432398</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1573755377854195</v>
+        <v>0.1573755377854196</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947813778609781</v>
+        <v>0.5947813778609787</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1111753607446196</v>
+        <v>-0.1111753607446195</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1482387657619014</v>
+        <v>0.1482387657619016</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532697926760266</v>
+        <v>0.4532697926760273</v>
       </c>
     </row>
     <row r="29">
@@ -2782,61 +2782,61 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3186427171078559</v>
+        <v>-0.3186427171078557</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1545279196022677</v>
+        <v>0.1545279196022678</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03920394898235113</v>
+        <v>0.0392039489823514</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01479837462877072</v>
+        <v>0.002589705940363018</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007085296655765525</v>
+        <v>0.007293744184584124</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03674343959712717</v>
+        <v>0.722545758606248</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002589705940363016</v>
+        <v>0.01704998181899487</v>
       </c>
       <c r="C31" t="n">
-        <v>0.007293744184584129</v>
+        <v>0.04993149462297796</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7225457586062485</v>
+        <v>0.7327516797914961</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01704998181899492</v>
+        <v>-0.01286655354973578</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04993149462297867</v>
+        <v>0.008184547747939277</v>
       </c>
       <c r="D32" t="n">
-        <v>0.732751679791499</v>
+        <v>0.1159379568009074</v>
       </c>
     </row>
     <row r="33">
@@ -2846,29 +2846,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01865810867195039</v>
+        <v>0.01865810867195043</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02286606432621099</v>
+        <v>0.02286606432621109</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4145151389219848</v>
+        <v>0.414515138921986</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01286655354973578</v>
+        <v>0.01479837462877072</v>
       </c>
       <c r="C34" t="n">
-        <v>0.008184547747939126</v>
+        <v>0.007085296655765543</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1159379568009007</v>
+        <v>0.0367434395971276</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.392</v>
+        <v>-0.181</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.028</v>
+        <v>0.013</v>
       </c>
       <c r="E6" t="n">
-        <v>0.364</v>
+        <v>0.168</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.181</v>
+        <v>0.01</v>
       </c>
       <c r="D7" t="n">
-        <v>0.013</v>
+        <v>0.004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.168</v>
+        <v>0.006</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="D8" t="n">
-        <v>0.021</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03799999999999999</v>
+        <v>0.074</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.007</v>
+        <v>-0.095</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.018</v>
+        <v>0.09</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.215</v>
+        <v>-0.008</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.059</v>
+        <v>-0.007</v>
       </c>
       <c r="E10" t="n">
-        <v>0.156</v>
+        <v>0.001</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.015</v>
+        <v>-0.392</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.032</v>
+        <v>-0.028</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.017</v>
+        <v>0.364</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.054</v>
+        <v>-0.001</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.023</v>
+        <v>-0.002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.031</v>
+        <v>-0.001</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.036</v>
+        <v>0.014</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001</v>
+        <v>0.015</v>
       </c>
       <c r="E13" t="n">
-        <v>0.035</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.001</v>
+        <v>0.059</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008</v>
+        <v>0.021</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.007</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.013</v>
+        <v>0.036</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.035</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01</v>
+        <v>-0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004</v>
+        <v>-0.032</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>-0.017</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.014</v>
+        <v>-0.096</v>
       </c>
       <c r="D19" t="n">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.078</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.095</v>
+        <v>-0.001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>-0.007</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.368</v>
+        <v>-0.007</v>
       </c>
       <c r="D21" t="n">
-        <v>0.006</v>
+        <v>-0.025</v>
       </c>
       <c r="E21" t="n">
-        <v>0.362</v>
+        <v>-0.018</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.096</v>
+        <v>0.075</v>
       </c>
       <c r="D22" t="n">
-        <v>0.018</v>
+        <v>0.005</v>
       </c>
       <c r="E22" t="n">
-        <v>0.078</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.012</v>
+        <v>-0.019</v>
       </c>
       <c r="D23" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="E23" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.09</v>
+        <v>0.351</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03</v>
+        <v>0.016</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06</v>
+        <v>0.335</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.008</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.007</v>
+        <v>-0.023</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001</v>
+        <v>0.031</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.019</v>
+        <v>-0.09</v>
       </c>
       <c r="D26" t="n">
-        <v>0.007</v>
+        <v>-0.03</v>
       </c>
       <c r="E26" t="n">
-        <v>0.012</v>
+        <v>0.06</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E27" t="n">
         <v>0.007</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.002</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.351</v>
+        <v>0.368</v>
       </c>
       <c r="D28" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="E28" t="n">
-        <v>0.335</v>
+        <v>0.362</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.075</v>
+        <v>0.013</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.044</v>
+        <v>-0.215</v>
       </c>
       <c r="D30" t="n">
-        <v>0.026</v>
+        <v>-0.059</v>
       </c>
       <c r="E30" t="n">
-        <v>0.018</v>
+        <v>0.156</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.076</v>
+        <v>0.044</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.002</v>
+        <v>0.026</v>
       </c>
       <c r="E32" t="n">
-        <v>0.074</v>
+        <v>0.018</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1397,13 +1397,13 @@
         <v>0.1624039162238811</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858123712730966</v>
+        <v>1.858123712730965</v>
       </c>
       <c r="F2" t="n">
         <v>1.149442947861497</v>
       </c>
       <c r="G2" t="n">
-        <v>1.858070037641444</v>
+        <v>1.858070037641443</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>2.02836611587179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142797777609108</v>
+        <v>0.1142797777609051</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299163</v>
+        <v>1.804381867299175</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444417</v>
+        <v>2.252350364444406</v>
       </c>
       <c r="F2" t="n">
-        <v>1.75058792475567e-70</v>
+        <v>1.750587924728219e-70</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546855</v>
+        <v>-0.004454066658546868</v>
       </c>
       <c r="C3" t="n">
         <v>0.02264676650011666</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04884091336506371</v>
+        <v>-0.04884091336506374</v>
       </c>
       <c r="E3" t="n">
         <v>0.03993278004797</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8440813962195437</v>
+        <v>0.8440813962195433</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464313</v>
+        <v>-0.03389366488464316</v>
       </c>
       <c r="C4" t="n">
         <v>0.05785807270287898</v>
@@ -1523,10 +1523,10 @@
         <v>-0.147293403597186</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07950607382789968</v>
+        <v>0.07950607382789965</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5580052088357449</v>
+        <v>0.5580052088357446</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006875661103275409</v>
+        <v>-0.006875661103275406</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03808494585975138</v>
+        <v>0.03808494585975132</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154596</v>
+        <v>-0.08152078334154585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06776946113499514</v>
+        <v>0.06776946113499503</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8567326745156678</v>
+        <v>0.8567326745156677</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856113334</v>
+        <v>-0.001188297856113079</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04119983828117574</v>
+        <v>0.0411998382811757</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609239</v>
+        <v>-0.08193849705609205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07956190134386572</v>
+        <v>0.0795619013438659</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9769903690159457</v>
+        <v>0.9769903690159506</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06305858053336841</v>
+        <v>-0.06305858053336844</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04059008063935422</v>
+        <v>0.0405900806393542</v>
       </c>
       <c r="D7" t="n">
         <v>-0.1426136767160792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0164965156493424</v>
+        <v>0.01649651564934233</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868607</v>
+        <v>0.1202926126868602</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06505644283206317</v>
+        <v>-0.06505644283206324</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04132988827693287</v>
+        <v>0.04132988827693283</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1460615353399158</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01594864967578943</v>
+        <v>0.01594864967578929</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1154695580659507</v>
+        <v>0.1154695580659501</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02905623760645395</v>
+        <v>-0.02905623760645398</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0394235410966261</v>
+        <v>0.03942354109662608</v>
       </c>
       <c r="D9" t="n">
         <v>-0.1063249582988758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596791</v>
+        <v>0.04821248308596785</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4611055694915079</v>
+        <v>0.4611055694915073</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0688506731373066</v>
+        <v>-0.06885067313730664</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0621158566937026</v>
+        <v>0.0621158566937024</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258149</v>
+        <v>-0.1905955151258146</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05289416885120174</v>
+        <v>0.0528941688512013</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2676789754318663</v>
+        <v>0.2676789754318643</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1221748468931796</v>
+        <v>-0.1221748468931795</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06092435583523102</v>
+        <v>0.06092435583523084</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.241584390111535</v>
+        <v>-0.2415843901115346</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674824082</v>
+        <v>-0.002765303674824346</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0449253099844243</v>
+        <v>0.04492530998442382</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07838540326732436</v>
+        <v>-0.07838540326732434</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06092691482148867</v>
+        <v>0.06092691482148845</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065818</v>
+        <v>-0.1977999620065813</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193306</v>
+        <v>0.04102915547193263</v>
       </c>
       <c r="F12" t="n">
-        <v>0.198251861852462</v>
+        <v>0.1982518618524606</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033331</v>
+        <v>0.008522193482033499</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05836873363374088</v>
+        <v>0.05836873363374073</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1058784222633105</v>
+        <v>-0.10587842226331</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1229228092273772</v>
+        <v>0.122922809227377</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8839165415238884</v>
+        <v>0.8839165415238859</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1767,16 +1767,16 @@
         <v>-0.04039308737240806</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615592</v>
+        <v>0.05674181331615572</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1516049978895689</v>
+        <v>-0.1516049978895685</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0708188231447528</v>
+        <v>0.07081882314475241</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642764</v>
+        <v>0.4765420859642748</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.115412511656635</v>
+        <v>-0.1154125116566349</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06052942681222912</v>
+        <v>0.06052942681222889</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2340480082134571</v>
+        <v>-0.2340480082134566</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003222984900187201</v>
+        <v>0.00322298490018684</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05655719180604712</v>
+        <v>0.05655719180604638</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1015943982225831</v>
+        <v>-0.101594398222583</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05923345190504568</v>
+        <v>0.05923345190504544</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364581</v>
+        <v>-0.2176898306364575</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01450103419129189</v>
+        <v>0.01450103419129155</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154382</v>
+        <v>0.08631728613154301</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509312</v>
+        <v>-0.08898691774509301</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358302</v>
+        <v>0.05739926877358271</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2014874172802504</v>
+        <v>-0.2014874172802497</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02351358179006416</v>
+        <v>0.02351358179006366</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1210660526014487</v>
+        <v>0.1210660526014472</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04535069185511207</v>
+        <v>-0.04535069185511199</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06190696804401337</v>
+        <v>0.06190696804401315</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1666861196134503</v>
+        <v>-0.1666861196134498</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07598473590322616</v>
+        <v>0.07598473590322583</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4638256196207995</v>
+        <v>0.4638256196207988</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01255984200078644</v>
+        <v>-0.0125598420007864</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072948</v>
+        <v>0.06121386203072923</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356201</v>
+        <v>-0.1325368069356196</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340472</v>
+        <v>0.1074171229340468</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8374317271342916</v>
+        <v>0.8374317271342915</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425895</v>
+        <v>-0.06233504608425883</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0614539882282572</v>
+        <v>0.06145398822825695</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1827826497179915</v>
+        <v>-0.1827826497179909</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0581125575494736</v>
+        <v>0.05811255754947324</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3104220364751104</v>
+        <v>0.3104220364751094</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05962283374156495</v>
+        <v>-0.05962283374156484</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066319</v>
+        <v>0.05902325596066291</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747539</v>
+        <v>-0.1753062896747532</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05606062219162397</v>
+        <v>0.05606062219162353</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3124194392956607</v>
+        <v>0.3124194392956592</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.05042994771853632</v>
+        <v>-0.05042994771853613</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06074201625882806</v>
+        <v>0.06074201625882784</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341857</v>
+        <v>-0.1694821119341851</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711306</v>
+        <v>0.06862221649711284</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516433</v>
+        <v>0.4064077928516434</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641262</v>
+        <v>-0.06558214032641259</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05881748257355471</v>
+        <v>0.05881748257355448</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1808622878318921</v>
+        <v>-0.1808622878318916</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04969800717906686</v>
+        <v>0.04969800717906644</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412736</v>
+        <v>0.2648457060412719</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007941985483981963</v>
+        <v>0.007941985483981975</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700068</v>
+        <v>0.05021926948700063</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09048597404045064</v>
+        <v>-0.09048597404045053</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1063699450084146</v>
+        <v>0.1063699450084145</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8743416143866749</v>
+        <v>0.8743416143866746</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04275887538360298</v>
+        <v>0.04275887538360296</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02899531241893941</v>
+        <v>0.02899531241893926</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800522</v>
+        <v>-0.01407089267800495</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09958864344521118</v>
+        <v>0.09958864344521087</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1402979641274857</v>
+        <v>0.1402979641274837</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01702773825292605</v>
+        <v>0.01702773825292614</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03628839344655837</v>
+        <v>0.03628839344655835</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914767</v>
+        <v>-0.05409620595914756</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499978</v>
+        <v>0.08815168246499984</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6389025774131496</v>
+        <v>0.6389025774131476</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04776265836687568</v>
+        <v>0.04776265836687571</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03631243242202282</v>
+        <v>0.03631243242202281</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02340840137133362</v>
+        <v>-0.02340840137133357</v>
       </c>
       <c r="E27" t="n">
         <v>0.118933718105085</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1884006237939557</v>
+        <v>0.1884006237939555</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2117,16 +2117,16 @@
         <v>0.03849528892250782</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03513724130562735</v>
+        <v>0.0351372413056273</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.03037243855261493</v>
+        <v>-0.03037243855261483</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1073630163976306</v>
+        <v>0.1073630163976305</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2732672273052903</v>
+        <v>0.2732672273052895</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649719</v>
+        <v>0.005380707237649681</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03555582911908343</v>
+        <v>0.03555582911908339</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06430743727621432</v>
+        <v>-0.0643074372762143</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506885175151376</v>
+        <v>0.07506885175151365</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731925</v>
+        <v>0.8797144375731931</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.003320233432694858</v>
+        <v>-0.003320233432694951</v>
       </c>
       <c r="C30" t="n">
         <v>0.05015882681790457</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1016297275025696</v>
+        <v>-0.1016297275025697</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0949892606371799</v>
+        <v>0.0949892606371798</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604797</v>
+        <v>0.9472230553604782</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.001543895502937994</v>
+        <v>0.000215246513424368</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001581102582020389</v>
+        <v>0.001692811914196193</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004642799619561244</v>
+        <v>-0.003102603871000477</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001555008613685256</v>
+        <v>0.003533096897849214</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3288327776696803</v>
+        <v>0.8988191168516216</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4346917524144869</v>
+        <v>-0.0003007900296359918</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01226316783229007</v>
+        <v>0.001948498754003041</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4106563851268283</v>
+        <v>-0.004119777411403122</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4587271197021456</v>
+        <v>0.003518197352131138</v>
       </c>
       <c r="F32" t="n">
-        <v>3.233495669651723e-275</v>
+        <v>0.8773178945519985</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0003007900296359786</v>
+        <v>0.4346917524144869</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001948498754003065</v>
+        <v>0.01226316783229004</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004119777411403157</v>
+        <v>0.4106563851268283</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0035181973521312</v>
+        <v>0.4587271197021455</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8773178945520054</v>
+        <v>3.233495669640318e-275</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.009549274128434511</v>
+        <v>-0.001543895502937996</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00523657024487689</v>
+        <v>0.001581102582020384</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.01981276321090731</v>
+        <v>-0.004642799619561235</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0007142149540382836</v>
+        <v>0.001555008613685243</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0682164776940235</v>
+        <v>0.328832777669678</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0002152465134243679</v>
+        <v>-0.009549274128434511</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001692811914196197</v>
+        <v>0.005236570244876912</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003102603871000486</v>
+        <v>-0.01981276321090735</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003533096897849222</v>
+        <v>0.0007142149540383287</v>
       </c>
       <c r="F35" t="n">
-        <v>0.898819116851622</v>
+        <v>0.0682164776940247</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.589409473419879</v>
+        <v>-2.589409473419876</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5031045718144678</v>
+        <v>0.5031045718144668</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631191243e-07</v>
+        <v>2.648809631191155e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254693</v>
+        <v>0.04318498161254683</v>
       </c>
       <c r="C3" t="n">
         <v>0.1065435099103227</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6852370218892512</v>
+        <v>0.6852370218892518</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3414291668173601</v>
+        <v>0.3414291668173602</v>
       </c>
       <c r="C4" t="n">
         <v>0.2253255698874617</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1297039406487216</v>
+        <v>0.1297039406487215</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7562320294942515</v>
+        <v>0.7562320294942516</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1748738694459633</v>
+        <v>0.1748738694459632</v>
       </c>
       <c r="D5" t="n">
-        <v>1.529179373687534e-05</v>
+        <v>1.529179373687506e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1784790633221358</v>
+        <v>-0.1784790633221359</v>
       </c>
       <c r="C6" t="n">
         <v>0.2136767975499138</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4035624257334067</v>
+        <v>0.4035624257334062</v>
       </c>
     </row>
     <row r="7">
@@ -2436,7 +2436,7 @@
         <v>0.195320867407642</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921537310985464</v>
+        <v>0.4921537310985463</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09566226402322769</v>
+        <v>-0.09566226402322774</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2104081937814556</v>
+        <v>0.2104081937814555</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6493604462404069</v>
+        <v>0.6493604462404066</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.070551836763826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645068</v>
+        <v>0.1703735435645067</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524959e-10</v>
+        <v>3.309132456524852e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828994</v>
+        <v>0.09554047552828922</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992086</v>
+        <v>0.2825463042992085</v>
       </c>
       <c r="D10" t="n">
-        <v>0.735256973094482</v>
+        <v>0.7352569730944838</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2120911081526146</v>
+        <v>0.2120911081526143</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2723979177423714</v>
+        <v>0.2723979177423709</v>
       </c>
       <c r="D11" t="n">
-        <v>0.436210859298791</v>
+        <v>0.4362108592987908</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.244432588105289</v>
+        <v>-0.2444325881052893</v>
       </c>
       <c r="C12" t="n">
         <v>0.3070429002527503</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259819868592534</v>
+        <v>0.4259819868592527</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2496062680064458</v>
+        <v>0.2496062680064456</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718407</v>
+        <v>0.2703388739718406</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3558462903511512</v>
+        <v>0.3558462903511516</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2898175614664946</v>
+        <v>0.289817561466494</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071122</v>
+        <v>0.2803190610071128</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011901132184945</v>
+        <v>0.3011901132184963</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.339820516653611</v>
+        <v>0.3398205166536108</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2686928948980225</v>
+        <v>0.2686928948980217</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404603</v>
+        <v>0.2059727340404595</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1269289753942516</v>
+        <v>0.1269289753942511</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2681297806792983</v>
+        <v>0.268129780679298</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959048</v>
+        <v>0.6359375739959057</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766427</v>
+        <v>0.1818641012766426</v>
       </c>
       <c r="C17" t="n">
-        <v>0.275209811772879</v>
+        <v>0.2752098117728786</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920058</v>
+        <v>0.5087278635920056</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.386446959094826</v>
+        <v>0.3864469590948256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451043</v>
+        <v>0.2676140000451047</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1487260018447603</v>
+        <v>0.1487260018447613</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.124440274708573</v>
+        <v>0.1244402747085727</v>
       </c>
       <c r="C19" t="n">
         <v>0.2778369782669697</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218877</v>
+        <v>0.6542329221218884</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230528</v>
+        <v>0.2308101909230525</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2780833406064979</v>
+        <v>0.2780833406064971</v>
       </c>
       <c r="D20" t="n">
-        <v>0.406536713451994</v>
+        <v>0.4065367134519935</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2330335342161674</v>
+        <v>0.2330335342161671</v>
       </c>
       <c r="C21" t="n">
-        <v>0.267319681964837</v>
+        <v>0.2673196819648361</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885921</v>
+        <v>0.3833496727885913</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05077438800389119</v>
+        <v>0.05077438800389093</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476467</v>
+        <v>0.2847519964476465</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8584788100921653</v>
+        <v>0.8584788100921659</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197874</v>
+        <v>-0.01709893916197908</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712273</v>
+        <v>0.2925638244712272</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9533940447535806</v>
+        <v>0.9533940447535797</v>
       </c>
     </row>
     <row r="24">
@@ -2705,10 +2705,10 @@
         <v>0.8751793875051906</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1599839947303408</v>
+        <v>0.1599839947303407</v>
       </c>
       <c r="D24" t="n">
-        <v>4.489744023837755e-08</v>
+        <v>4.489744023837706e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5929479835845773</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169096769872895</v>
+        <v>0.1169096769872892</v>
       </c>
       <c r="D25" t="n">
-        <v>3.939732815876808e-07</v>
+        <v>3.93973281587656e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.13835121129842</v>
+        <v>-0.1383512112984201</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1508106992062233</v>
+        <v>0.1508106992062234</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3589418401519294</v>
+        <v>0.3589418401519292</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08371120214432398</v>
+        <v>-0.08371120214432426</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1573755377854196</v>
+        <v>0.1573755377854195</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947813778609787</v>
+        <v>0.5947813778609774</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1111753607446195</v>
+        <v>-0.1111753607446199</v>
       </c>
       <c r="C28" t="n">
         <v>0.1482387657619016</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532697926760273</v>
+        <v>0.4532697926760261</v>
       </c>
     </row>
     <row r="29">
@@ -2782,93 +2782,93 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3186427171078557</v>
+        <v>-0.3186427171078561</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1545279196022678</v>
+        <v>0.1545279196022679</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0392039489823514</v>
+        <v>0.03920394898235129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002589705940363018</v>
+        <v>0.01479837462877072</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007293744184584124</v>
+        <v>0.00708529665576556</v>
       </c>
       <c r="D30" t="n">
-        <v>0.722545758606248</v>
+        <v>0.03674343959712813</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01704998181899487</v>
+        <v>-0.0128665535497358</v>
       </c>
       <c r="C31" t="n">
-        <v>0.04993149462297796</v>
+        <v>0.008184547747939246</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7327516797914961</v>
+        <v>0.1159379568009055</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.01286655354973578</v>
+        <v>0.01704998181899479</v>
       </c>
       <c r="C32" t="n">
-        <v>0.008184547747939277</v>
+        <v>0.04993149462297924</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1159379568009074</v>
+        <v>0.7327516797915039</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01865810867195043</v>
+        <v>0.00258970594036301</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02286606432621109</v>
+        <v>0.007293744184584137</v>
       </c>
       <c r="D33" t="n">
-        <v>0.414515138921986</v>
+        <v>0.7225457586062494</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01479837462877072</v>
+        <v>0.01865810867195037</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007085296655765543</v>
+        <v>0.02286606432621126</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0367434395971276</v>
+        <v>0.4145151389219907</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.392</v>
+        <v>-0.09</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.028</v>
+        <v>-0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>0.364</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.181</v>
+        <v>0.014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="E7" t="n">
-        <v>0.168</v>
+        <v>-0.0009999999999999992</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.044</v>
+        <v>0.185</v>
       </c>
       <c r="D8" t="n">
-        <v>0.026</v>
+        <v>0.015</v>
       </c>
       <c r="E8" t="n">
-        <v>0.018</v>
+        <v>0.17</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.351</v>
+        <v>-0.019</v>
       </c>
       <c r="D9" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="E9" t="n">
-        <v>0.335</v>
+        <v>0.012</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.014</v>
+        <v>-0.181</v>
       </c>
       <c r="D10" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.168</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.095</v>
+        <v>0.013</v>
       </c>
       <c r="D11" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.215</v>
+        <v>-0.054</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.059</v>
+        <v>-0.023</v>
       </c>
       <c r="E12" t="n">
-        <v>0.156</v>
+        <v>0.031</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.01</v>
+        <v>-0.012</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E13" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.076</v>
+        <v>0.351</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.002</v>
+        <v>0.016</v>
       </c>
       <c r="E14" t="n">
-        <v>0.074</v>
+        <v>0.335</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.368</v>
+        <v>-0.015</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006</v>
+        <v>-0.032</v>
       </c>
       <c r="E15" t="n">
-        <v>0.362</v>
+        <v>-0.017</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.008</v>
+        <v>-0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.007</v>
+        <v>0.001</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="D18" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="E18" t="n">
         <v>0.006</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.006999999999999999</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.007</v>
+        <v>-0.392</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.005</v>
+        <v>-0.028</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002</v>
+        <v>0.364</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.054</v>
+        <v>-0.095</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.023</v>
+        <v>0.005</v>
       </c>
       <c r="E20" t="n">
-        <v>0.031</v>
+        <v>0.09</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.008</v>
+        <v>0.036</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.007</v>
+        <v>0.001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001</v>
+        <v>0.035</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.185</v>
+        <v>0.007</v>
       </c>
       <c r="D22" t="n">
-        <v>0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="E22" t="n">
-        <v>0.17</v>
+        <v>0.002</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.059</v>
+        <v>-0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.021</v>
+        <v>-0.008</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03799999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.09</v>
+        <v>-0.096</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.03</v>
+        <v>0.018</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06</v>
+        <v>0.078</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.033</v>
+        <v>-0.007</v>
       </c>
       <c r="D25" t="n">
-        <v>0.025</v>
+        <v>-0.025</v>
       </c>
       <c r="E25" t="n">
-        <v>0.008</v>
+        <v>-0.018</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.036</v>
+        <v>0.076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.035</v>
+        <v>0.074</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.012</v>
+        <v>0.368</v>
       </c>
       <c r="D27" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E27" t="n">
-        <v>0.007</v>
+        <v>0.362</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.075</v>
+        <v>-0.215</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005</v>
+        <v>-0.059</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.019</v>
+        <v>0.075</v>
       </c>
       <c r="D29" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.012</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.015</v>
+        <v>0.059</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.032</v>
+        <v>0.021</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.017</v>
+        <v>0.03799999999999999</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.096</v>
+        <v>0.033</v>
       </c>
       <c r="D31" t="n">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="E31" t="n">
-        <v>0.078</v>
+        <v>0.008</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.007</v>
+        <v>0.044</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.025</v>
+        <v>0.026</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.018</v>
+        <v>0.018</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1391,7 +1391,7 @@
         <v>6055.852863629239</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9954923524565367</v>
+        <v>0.9954923524565368</v>
       </c>
       <c r="D2" t="n">
         <v>0.1624039162238811</v>
@@ -1403,7 +1403,7 @@
         <v>1.149442947861497</v>
       </c>
       <c r="G2" t="n">
-        <v>1.858070037641443</v>
+        <v>1.858070037641444</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>2.02836611587179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.114279777760911</v>
+        <v>0.1142797777609079</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299163</v>
+        <v>1.804381867299169</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444417</v>
+        <v>2.252350364444411</v>
       </c>
       <c r="F2" t="n">
-        <v>1.750587924756419e-70</v>
+        <v>1.750587924741495e-70</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546861</v>
+        <v>-0.004454066658546881</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02264676650011666</v>
+        <v>0.02264676650011665</v>
       </c>
       <c r="D3" t="n">
         <v>-0.04884091336506372</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03993278004796999</v>
+        <v>0.03993278004796996</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8440813962195435</v>
+        <v>0.8440813962195427</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464311</v>
+        <v>-0.03389366488464316</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05785807270287897</v>
+        <v>0.05785807270287899</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1472934035971859</v>
+        <v>-0.147293403597186</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0795060738278997</v>
+        <v>0.07950607382789968</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5580052088357452</v>
+        <v>0.5580052088357446</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006875661103275434</v>
+        <v>-0.006875661103275418</v>
       </c>
       <c r="C5" t="n">
         <v>0.03808494585975136</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154593</v>
+        <v>-0.08152078334154592</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06776946113499506</v>
+        <v>0.06776946113499507</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8567326745156673</v>
+        <v>0.8567326745156676</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856113121</v>
+        <v>-0.001188297856112999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04119983828117572</v>
+        <v>0.0411998382811757</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609213</v>
+        <v>-0.08193849705609198</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0795619013438659</v>
+        <v>0.07956190134386597</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9769903690159498</v>
+        <v>0.9769903690159522</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06305858053336844</v>
+        <v>-0.06305858053336841</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04059008063935423</v>
+        <v>0.0405900806393542</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1426136767160793</v>
+        <v>-0.1426136767160792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01649651564934239</v>
+        <v>0.01649651564934236</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868605</v>
+        <v>0.1202926126868604</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06505644283206323</v>
+        <v>-0.0650564428320632</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04132988827693287</v>
+        <v>0.04132988827693283</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1460615353399158</v>
+        <v>-0.1460615353399157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01594864967578938</v>
+        <v>0.01594864967578934</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1154695580659504</v>
+        <v>0.1154695580659503</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.029056237606454</v>
+        <v>-0.02905623760645398</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03942354109662611</v>
+        <v>0.03942354109662607</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1063249582988759</v>
+        <v>-0.1063249582988758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596788</v>
+        <v>0.04821248308596782</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4611055694915073</v>
+        <v>0.4611055694915072</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.06885067313730643</v>
+        <v>-0.06885067313730656</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06211585669370266</v>
+        <v>0.06211585669370251</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258149</v>
+        <v>-0.1905955151258147</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05289416885120203</v>
+        <v>0.0528941688512016</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2676789754318678</v>
+        <v>0.2676789754318657</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1692,16 +1692,16 @@
         <v>-0.1221748468931794</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06092435583523104</v>
+        <v>0.06092435583523091</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2415843901115349</v>
+        <v>-0.2415843901115347</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674823832</v>
+        <v>-0.002765303674824096</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04492530998442472</v>
+        <v>0.04492530998442423</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07838540326732418</v>
+        <v>-0.07838540326732421</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06092691482148872</v>
+        <v>0.06092691482148858</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065817</v>
+        <v>-0.1977999620065815</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193332</v>
+        <v>0.04102915547193302</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1982518618524636</v>
+        <v>0.1982518618524622</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033593</v>
+        <v>0.008522193482033582</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05836873363374082</v>
+        <v>0.05836873363374077</v>
       </c>
       <c r="D13" t="n">
         <v>-0.1058784222633101</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1229228092273773</v>
+        <v>0.1229228092273772</v>
       </c>
       <c r="F13" t="n">
         <v>0.8839165415238849</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04039308737240774</v>
+        <v>-0.04039308737240799</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615595</v>
+        <v>0.05674181331615576</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1516049978895687</v>
+        <v>-0.1516049978895685</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07081882314475317</v>
+        <v>0.07081882314475256</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642803</v>
+        <v>0.4765420859642759</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1154125116566348</v>
+        <v>-0.1154125116566347</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0605294268122291</v>
+        <v>0.06052942681222902</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2340480082134569</v>
+        <v>-0.2340480082134567</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003222984900187381</v>
+        <v>0.003222984900187242</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05655719180604749</v>
+        <v>0.05655719180604719</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1817,16 +1817,16 @@
         <v>-0.1015943982225829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05923345190504568</v>
+        <v>0.0592334519050455</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364579</v>
+        <v>-0.2176898306364575</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0145010341912921</v>
+        <v>0.01450103419129177</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154455</v>
+        <v>0.08631728613154363</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509293</v>
+        <v>-0.08898691774509294</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358301</v>
+        <v>0.05739926877358275</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2014874172802502</v>
+        <v>-0.2014874172802497</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02351358179006434</v>
+        <v>0.0235135817900638</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1210660526014495</v>
+        <v>0.1210660526014477</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04535069185511181</v>
+        <v>-0.04535069185511196</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0619069680440134</v>
+        <v>0.0619069680440133</v>
       </c>
       <c r="D18" t="n">
         <v>-0.1666861196134501</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07598473590322649</v>
+        <v>0.07598473590322613</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4638256196208023</v>
+        <v>0.4638256196208002</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01255984200078624</v>
+        <v>-0.01255984200078627</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072944</v>
+        <v>0.06121386203072934</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356198</v>
+        <v>-0.1325368069356197</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340474</v>
+        <v>0.1074171229340471</v>
       </c>
       <c r="F19" t="n">
-        <v>0.837431727134294</v>
+        <v>0.8374317271342933</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425865</v>
+        <v>-0.06233504608425874</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06145398822825722</v>
+        <v>0.06145398822825702</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1827826497179912</v>
+        <v>-0.1827826497179909</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05811255754947394</v>
+        <v>0.05811255754947347</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3104220364751129</v>
+        <v>0.3104220364751107</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05962283374156472</v>
+        <v>-0.05962283374156474</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066312</v>
+        <v>0.05902325596066299</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747535</v>
+        <v>-0.1753062896747533</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05606062219162408</v>
+        <v>0.05606062219162379</v>
       </c>
       <c r="F21" t="n">
-        <v>0.312419439295662</v>
+        <v>0.3124194392956607</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.05042994771853593</v>
+        <v>-0.05042994771853607</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06074201625882798</v>
+        <v>0.06074201625882803</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341852</v>
+        <v>-0.1694821119341854</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711331</v>
+        <v>0.06862221649711325</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516462</v>
+        <v>0.4064077928516453</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641245</v>
+        <v>-0.06558214032641253</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05881748257355469</v>
+        <v>0.0588174825735546</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1808622878318919</v>
+        <v>-0.1808622878318918</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04969800717906699</v>
+        <v>0.04969800717906674</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412744</v>
+        <v>0.2648457060412732</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007941985483982004</v>
+        <v>0.007941985483982006</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700065</v>
+        <v>0.05021926948700062</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09048597404045053</v>
+        <v>-0.09048597404045049</v>
       </c>
       <c r="E24" t="n">
         <v>0.1063699450084145</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8743416143866741</v>
+        <v>0.874341614386674</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04275887538360294</v>
+        <v>0.04275887538360301</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02899531241893934</v>
+        <v>0.02899531241893925</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800513</v>
+        <v>-0.01407089267800488</v>
       </c>
       <c r="E25" t="n">
-        <v>0.099588643445211</v>
+        <v>0.09958864344521089</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1402979641274852</v>
+        <v>0.1402979641274832</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01702773825292602</v>
+        <v>0.01702773825292627</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03628839344655835</v>
+        <v>0.03628839344655833</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914766</v>
+        <v>-0.05409620595914739</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499971</v>
+        <v>0.08815168246499994</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6389025774131499</v>
+        <v>0.6389025774131449</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04776265836687561</v>
+        <v>0.04776265836687567</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03631243242202283</v>
+        <v>0.03631243242202281</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0234084013713337</v>
+        <v>-0.02340840137133361</v>
       </c>
       <c r="E27" t="n">
         <v>0.1189337181050849</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1884006237939565</v>
+        <v>0.1884006237939557</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0384952889225078</v>
+        <v>0.03849528892250783</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03513724130562731</v>
+        <v>0.03513724130562727</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.03037243855261488</v>
+        <v>-0.03037243855261475</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1073630163976305</v>
+        <v>0.1073630163976304</v>
       </c>
       <c r="F28" t="n">
-        <v>0.27326722730529</v>
+        <v>0.2732672273052889</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649678</v>
+        <v>0.005380707237649708</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03555582911908342</v>
+        <v>0.03555582911908338</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06430743727621435</v>
+        <v>-0.06430743727621424</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0750688517515137</v>
+        <v>0.07506885175151365</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731932</v>
+        <v>0.8797144375731925</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.003320233432694986</v>
+        <v>-0.003320233432695015</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05015882681790459</v>
+        <v>0.05015882681790457</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1016297275025698</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09498926063717981</v>
+        <v>0.09498926063717975</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604777</v>
+        <v>0.9472230553604772</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0002152465134243671</v>
+        <v>-0.0003007900296359803</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001692811914196198</v>
+        <v>0.001948498754003048</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.00310260387100049</v>
+        <v>-0.004119777411403126</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003533096897849224</v>
+        <v>0.003518197352131165</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8988191168516224</v>
+        <v>0.8773178945520037</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0003007900296359844</v>
+        <v>-0.009549274128434494</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001948498754003064</v>
+        <v>0.005236570244876932</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00411977741140316</v>
+        <v>-0.01981276321090737</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003518197352131191</v>
+        <v>0.0007142149540383842</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8773178945520029</v>
+        <v>0.06821647769402626</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001543895502937994</v>
+        <v>-0.001543895502937996</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001581102582020392</v>
+        <v>0.001581102582020395</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004642799619561249</v>
+        <v>-0.004642799619561256</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001555008613685261</v>
+        <v>0.001555008613685264</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3288327776696812</v>
+        <v>0.3288327776696813</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.434691752414487</v>
+        <v>0.4346917524144869</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01226316783229007</v>
+        <v>0.01226316783229009</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4106563851268283</v>
+        <v>0.4106563851268282</v>
       </c>
       <c r="E34" t="n">
         <v>0.4587271197021456</v>
       </c>
       <c r="F34" t="n">
-        <v>3.233495669649517e-275</v>
+        <v>3.23349566965761e-275</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.009549274128434503</v>
+        <v>0.0002152465134243686</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005236570244876946</v>
+        <v>0.001692811914196191</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.01981276321090741</v>
+        <v>-0.003102603871000474</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0007142149540384033</v>
+        <v>0.003533096897849211</v>
       </c>
       <c r="F35" t="n">
-        <v>0.06821647769402675</v>
+        <v>0.8988191168516213</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.589409473419878</v>
+        <v>-2.58940947341988</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5031045718144701</v>
+        <v>0.5031045718144537</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631191609e-07</v>
+        <v>2.648809631189163e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254685</v>
+        <v>0.04318498161254689</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065435099103228</v>
+        <v>0.1065435099103227</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6852370218892518</v>
+        <v>0.6852370218892514</v>
       </c>
     </row>
     <row r="4">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7562320294942515</v>
+        <v>0.7562320294942516</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1748738694459635</v>
+        <v>0.1748738694459631</v>
       </c>
       <c r="D5" t="n">
-        <v>1.529179373687554e-05</v>
+        <v>1.52917937368748e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2417,10 +2417,10 @@
         <v>-0.1784790633221359</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2136767975499141</v>
+        <v>0.2136767975499137</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4035624257334068</v>
+        <v>0.4035624257334062</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1341634292941743</v>
+        <v>0.1341634292941744</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1953208674076423</v>
+        <v>0.1953208674076419</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921537310985474</v>
+        <v>0.4921537310985461</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09566226402322769</v>
+        <v>-0.09566226402322763</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2104081937814556</v>
+        <v>0.2104081937814554</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6493604462404068</v>
+        <v>0.6493604462404067</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.070551836763826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645069</v>
+        <v>0.1703735435645065</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524996e-10</v>
+        <v>3.309132456524719e-10</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828926</v>
+        <v>0.09554047552828965</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992097</v>
+        <v>0.2825463042992074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7352569730944847</v>
+        <v>0.7352569730944816</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2120911081526142</v>
+        <v>0.2120911081526145</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2723979177423718</v>
+        <v>0.272397917742371</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4362108592987923</v>
+        <v>0.4362108592987907</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2444325881052893</v>
+        <v>-0.2444325881052889</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3070429002527506</v>
+        <v>0.3070429002527493</v>
       </c>
       <c r="D12" t="n">
-        <v>0.425981986859253</v>
+        <v>0.4259819868592519</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2496062680064456</v>
+        <v>0.2496062680064459</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718417</v>
+        <v>0.2703388739718404</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3558462903511534</v>
+        <v>0.3558462903511507</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2898175614664941</v>
+        <v>0.2898175614664946</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071132</v>
+        <v>0.2803190610071123</v>
       </c>
       <c r="D14" t="n">
-        <v>0.301190113218497</v>
+        <v>0.3011901132184945</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3398205166536106</v>
+        <v>0.3398205166536111</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2686928948980226</v>
+        <v>0.2686928948980213</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404611</v>
+        <v>0.2059727340404583</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1269289753942512</v>
+        <v>0.1269289753942515</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2681297806792991</v>
+        <v>0.2681297806792978</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959066</v>
+        <v>0.6359375739959043</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766424</v>
+        <v>0.1818641012766428</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752098117728798</v>
+        <v>0.2752098117728791</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920081</v>
+        <v>0.5087278635920058</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3864469590948255</v>
+        <v>0.386446959094826</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451039</v>
+        <v>0.2676140000451032</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1487260018447602</v>
+        <v>0.1487260018447586</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1244402747085726</v>
+        <v>0.124440274708573</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2778369782669702</v>
+        <v>0.277836978266969</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218893</v>
+        <v>0.6542329221218868</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230524</v>
+        <v>0.2308101909230527</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2780833406064979</v>
+        <v>0.2780833406064969</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4065367134519948</v>
+        <v>0.4065367134519926</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.233033534216167</v>
+        <v>0.2330335342161674</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673196819648372</v>
+        <v>0.2673196819648357</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885936</v>
+        <v>0.3833496727885901</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0507743880038909</v>
+        <v>0.05077438800389136</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476463</v>
+        <v>0.2847519964476453</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8584788100921659</v>
+        <v>0.8584788100921641</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197914</v>
+        <v>-0.01709893916197886</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712279</v>
+        <v>0.2925638244712255</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9533940447535796</v>
+        <v>0.95339404475358</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8751793875051905</v>
+        <v>0.8751793875051906</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1599839947303408</v>
+        <v>0.1599839947303407</v>
       </c>
       <c r="D24" t="n">
-        <v>4.489744023837755e-08</v>
+        <v>4.489744023837655e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5929479835845772</v>
+        <v>-0.5929479835845771</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169096769872894</v>
+        <v>0.1169096769872893</v>
       </c>
       <c r="D25" t="n">
-        <v>3.939732815876743e-07</v>
+        <v>3.939732815876656e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,10 +2734,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1383512112984197</v>
+        <v>-0.1383512112984195</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1508106992062235</v>
+        <v>0.1508106992062233</v>
       </c>
       <c r="D26" t="n">
         <v>0.3589418401519312</v>
@@ -2756,7 +2756,7 @@
         <v>0.1573755377854197</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5947813778609787</v>
+        <v>0.594781377860979</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1111753607446195</v>
+        <v>-0.1111753607446196</v>
       </c>
       <c r="C28" t="n">
         <v>0.1482387657619015</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4532697926760273</v>
+        <v>0.453269792676027</v>
       </c>
     </row>
     <row r="29">
@@ -2782,45 +2782,45 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3186427171078558</v>
+        <v>-0.3186427171078557</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1545279196022678</v>
+        <v>0.1545279196022677</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03920394898235136</v>
+        <v>0.03920394898235133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01479837462877072</v>
+        <v>-0.01286655354973574</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007085296655765553</v>
+        <v>0.008184547747939083</v>
       </c>
       <c r="D30" t="n">
-        <v>0.03674343959712793</v>
+        <v>0.1159379568008997</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01286655354973579</v>
+        <v>0.01865810867195043</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008184547747939069</v>
+        <v>0.02286606432621095</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1159379568008977</v>
+        <v>0.4145151389219831</v>
       </c>
     </row>
     <row r="32">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002589705940363016</v>
+        <v>0.002589705940363019</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007293744184584179</v>
+        <v>0.007293744184584137</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7225457586062503</v>
+        <v>0.7225457586062485</v>
       </c>
     </row>
     <row r="33">
@@ -2846,29 +2846,29 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01704998181899492</v>
+        <v>0.01704998181899496</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04993149462297874</v>
+        <v>0.04993149462297854</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7327516797914995</v>
+        <v>0.7327516797914978</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0186581086719504</v>
+        <v>0.01479837462877072</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02286606432621106</v>
+        <v>0.007085296655765528</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4145151389219861</v>
+        <v>0.03674343959712725</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -480,13 +480,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.058</v>
+        <v>-0.055</v>
       </c>
       <c r="D2" t="n">
         <v>-0.029</v>
       </c>
       <c r="E2" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.109</v>
+        <v>0.103</v>
       </c>
       <c r="D3" t="n">
         <v>0.022</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08099999999999999</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.063</v>
+        <v>-0.022</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001</v>
+        <v>-0.023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.062</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.036</v>
+        <v>0.026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03</v>
+        <v>0.011</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005999999999999998</v>
+        <v>0.015</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.09</v>
+        <v>-0.018</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03</v>
+        <v>0.005</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="D7" t="n">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0009999999999999992</v>
+        <v>0.013</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.185</v>
+        <v>0.024</v>
       </c>
       <c r="D8" t="n">
-        <v>0.015</v>
+        <v>0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.019</v>
+        <v>0.045</v>
       </c>
       <c r="D9" t="n">
         <v>0.007</v>
       </c>
       <c r="E9" t="n">
-        <v>0.012</v>
+        <v>0.038</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.181</v>
+        <v>0.369</v>
       </c>
       <c r="D10" t="n">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.168</v>
+        <v>0.36</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.013</v>
+        <v>-0.216</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006</v>
+        <v>-0.059</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.157</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.054</v>
+        <v>-0.183</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.023</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.031</v>
+        <v>0.174</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.012</v>
+        <v>-0.015</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005</v>
+        <v>-0.026</v>
       </c>
       <c r="E13" t="n">
-        <v>0.007</v>
+        <v>-0.011</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.351</v>
+        <v>0.075</v>
       </c>
       <c r="D14" t="n">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="E14" t="n">
-        <v>0.335</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.015</v>
+        <v>0.035</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.032</v>
+        <v>0.022</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.017</v>
+        <v>0.013</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.001</v>
+        <v>0.011</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.008</v>
+        <v>0.015</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.007</v>
+        <v>0.017</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.392</v>
+        <v>-0.117</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.028</v>
+        <v>-0.004</v>
       </c>
       <c r="E19" t="n">
-        <v>0.364</v>
+        <v>0.113</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.095</v>
+        <v>0.19</v>
       </c>
       <c r="D20" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09</v>
+        <v>0.165</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -996,10 +996,10 @@
         <v>0.036</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="E21" t="n">
-        <v>0.035</v>
+        <v>0.028</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.007</v>
+        <v>-0.095</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.005</v>
+        <v>0.015</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002</v>
+        <v>0.08</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.001</v>
+        <v>0.35</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.008</v>
+        <v>0.018</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.007</v>
+        <v>0.332</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.096</v>
+        <v>0.003</v>
       </c>
       <c r="D24" t="n">
-        <v>0.018</v>
+        <v>0.001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.078</v>
+        <v>0.002</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.007</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.025</v>
+        <v>-0.029</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.018</v>
+        <v>0.042</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.076</v>
+        <v>0.099</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.074</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.368</v>
+        <v>-0.388</v>
       </c>
       <c r="D27" t="n">
-        <v>0.006</v>
+        <v>-0.03</v>
       </c>
       <c r="E27" t="n">
-        <v>0.362</v>
+        <v>0.358</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.215</v>
+        <v>0.036</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.059</v>
+        <v>0.019</v>
       </c>
       <c r="E28" t="n">
-        <v>0.156</v>
+        <v>0.017</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.075</v>
+        <v>-0.031</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.059</v>
+        <v>-0.008</v>
       </c>
       <c r="D30" t="n">
-        <v>0.021</v>
+        <v>-0.018</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03799999999999999</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="D31" t="n">
-        <v>0.025</v>
+        <v>0.003</v>
       </c>
       <c r="E31" t="n">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.044</v>
+        <v>-0.082</v>
       </c>
       <c r="D32" t="n">
-        <v>0.026</v>
+        <v>-0.028</v>
       </c>
       <c r="E32" t="n">
-        <v>0.018</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
       <c r="D33" t="n">
         <v>0.01</v>
       </c>
       <c r="E33" t="n">
-        <v>0.019</v>
+        <v>0.023</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1385,25 +1385,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6217</v>
+        <v>6044</v>
       </c>
       <c r="B2" t="n">
-        <v>6055.852863629239</v>
+        <v>5880.506490622341</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9954923524565368</v>
+        <v>0.9950471690165205</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1624039162238811</v>
+        <v>0.1659290743085242</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858123712730966</v>
+        <v>1.858369290792679</v>
       </c>
       <c r="F2" t="n">
-        <v>1.149442947861497</v>
+        <v>1.165474339027959</v>
       </c>
       <c r="G2" t="n">
-        <v>1.858070037641444</v>
+        <v>1.856659647949909</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.02836611587179</v>
+        <v>1.91628664450469</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1142797777609079</v>
+        <v>0.1135774763851162</v>
       </c>
       <c r="D2" t="n">
-        <v>1.804381867299169</v>
+        <v>1.693678881334913</v>
       </c>
       <c r="E2" t="n">
-        <v>2.252350364444411</v>
+        <v>2.138894407674466</v>
       </c>
       <c r="F2" t="n">
-        <v>1.750587924741495e-70</v>
+        <v>7.222578944580643e-64</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.004454066658546881</v>
+        <v>-0.01050744562892867</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02264676650011665</v>
+        <v>0.02313482841481903</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04884091336506372</v>
+        <v>-0.05585087611048783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03993278004796996</v>
+        <v>0.03483598485263049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8440813962195427</v>
+        <v>0.6496971222641865</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03389366488464316</v>
+        <v>-0.03640287469709135</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05785807270287899</v>
+        <v>0.05763586703459977</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.147293403597186</v>
+        <v>-0.1493670983026463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07950607382789968</v>
+        <v>0.07656134890846356</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5580052088357446</v>
+        <v>0.5276475939331993</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006875661103275418</v>
+        <v>-0.01048610640451848</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03808494585975136</v>
+        <v>0.038138687678579</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08152078334154592</v>
+        <v>-0.08523656067215485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06776946113499507</v>
+        <v>0.06426434786311788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8567326745156676</v>
+        <v>0.7833571861041335</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001188297856112999</v>
+        <v>-0.001511275113782383</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0411998382811757</v>
+        <v>0.04211864645461955</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08193849705609198</v>
+        <v>-0.08406230524241233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07956190134386597</v>
+        <v>0.08103975501484757</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9769903690159522</v>
+        <v>0.9713769437607231</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06305858053336841</v>
+        <v>-0.06364683252462018</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0405900806393542</v>
+        <v>0.04016802682897487</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1426136767160792</v>
+        <v>-0.1423747184394495</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01649651564934236</v>
+        <v>0.0150810533902092</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1202926126868604</v>
+        <v>0.1130766190665093</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0650564428320632</v>
+        <v>-0.06421840671360726</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04132988827693283</v>
+        <v>0.04041046821576316</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1460615353399157</v>
+        <v>-0.1434214690149036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01594864967578934</v>
+        <v>0.01498465558768911</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1154695580659503</v>
+        <v>0.1120259108770083</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02905623760645398</v>
+        <v>-0.02659716766236243</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03942354109662607</v>
+        <v>0.03890930153463092</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1063249582988758</v>
+        <v>-0.1028579973338481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04821248308596782</v>
+        <v>0.04966366200912323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4611055694915072</v>
+        <v>0.4942477661537689</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.06885067313730656</v>
+        <v>-0.08243544392281288</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06211585669370251</v>
+        <v>0.06337665689811482</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1905955151258147</v>
+        <v>-0.2066514089036699</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0528941688512016</v>
+        <v>0.04178052105804415</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2676789754318657</v>
+        <v>0.1933534561005055</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1221748468931794</v>
+        <v>-0.1356569674250366</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06092435583523091</v>
+        <v>0.06253796406675889</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2415843901115347</v>
+        <v>-0.258229124662344</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.002765303674824096</v>
+        <v>-0.01308481018772907</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04492530998442423</v>
+        <v>0.03006796939972239</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.07838540326732421</v>
+        <v>-0.1007904685653378</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06092691482148858</v>
+        <v>0.06371050484176445</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1977999620065815</v>
+        <v>-0.2256607634920609</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04102915547193302</v>
+        <v>0.02407982636138521</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1982518618524622</v>
+        <v>0.113647958400898</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008522193482033582</v>
+        <v>-0.006633880711504745</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05836873363374077</v>
+        <v>0.06033231536084682</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1058784222633101</v>
+        <v>-0.1248830459226772</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1229228092273772</v>
+        <v>0.1116152844996677</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8839165415238849</v>
+        <v>0.9124445246059475</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04039308737240799</v>
+        <v>-0.04852525054058572</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05674181331615576</v>
+        <v>0.0611500934678508</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1516049978895685</v>
+        <v>-0.1683772313888313</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07081882314475256</v>
+        <v>0.07132673030765986</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4765420859642759</v>
+        <v>0.4274613181377229</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1154125116566347</v>
+        <v>-0.1427721540964335</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06052942681222902</v>
+        <v>0.0649788575039197</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2340480082134567</v>
+        <v>-0.2701283745606763</v>
       </c>
       <c r="E15" t="n">
-        <v>0.003222984900187242</v>
+        <v>-0.01541593363219068</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05655719180604719</v>
+        <v>0.02800549722683545</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1015943982225829</v>
+        <v>-0.09890443698017597</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0592334519050455</v>
+        <v>0.05966171038444367</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2176898306364575</v>
+        <v>-0.2158392405897449</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01450103419129177</v>
+        <v>0.01803036662939297</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08631728613154363</v>
+        <v>0.09736713642719769</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08898691774509294</v>
+        <v>-0.08736850131641766</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05739926877358275</v>
+        <v>0.06144897675671657</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2014874172802497</v>
+        <v>-0.207806282646421</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0235135817900638</v>
+        <v>0.03306928001358571</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1210660526014477</v>
+        <v>0.1550826837763973</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.04535069185511196</v>
+        <v>-0.06583221967935282</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0619069680440133</v>
+        <v>0.06142509279704658</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1666861196134501</v>
+        <v>-0.1862231893085948</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07598473590322613</v>
+        <v>0.05455874994988917</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4638256196208002</v>
+        <v>0.2838332398704615</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.01255984200078627</v>
+        <v>-0.03558523015264689</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06121386203072934</v>
+        <v>0.06209835410094819</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1325368069356197</v>
+        <v>-0.1572957676897205</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1074171229340471</v>
+        <v>0.08612530738442672</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8374317271342933</v>
+        <v>0.566613366003584</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06233504608425874</v>
+        <v>-0.08036967353394857</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06145398822825702</v>
+        <v>0.06209993601337664</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1827826497179909</v>
+        <v>-0.2020833115624087</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05811255754947347</v>
+        <v>0.04134396449451151</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3104220364751107</v>
+        <v>0.1955967007635262</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05962283374156474</v>
+        <v>-0.0849242913998821</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05902325596066299</v>
+        <v>0.06272335023210078</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1753062896747533</v>
+        <v>-0.2078597988444917</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05606062219162379</v>
+        <v>0.03801121604472747</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3124194392956607</v>
+        <v>0.1757522723372715</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.05042994771853607</v>
+        <v>-0.04976148596577818</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06074201625882803</v>
+        <v>0.06616872223007148</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1694821119341854</v>
+        <v>-0.1794497984397531</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06862221649711325</v>
+        <v>0.07992682650819677</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4064077928516453</v>
+        <v>0.4520273669320789</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.06558214032641253</v>
+        <v>-0.07216349561442487</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0588174825735546</v>
+        <v>0.06023148981336583</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1808622878318918</v>
+        <v>-0.190215046383813</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04969800717906674</v>
+        <v>0.0458880551549633</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2648457060412732</v>
+        <v>0.230877134522401</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.007941985483982006</v>
+        <v>-0.002140600051701904</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05021926948700062</v>
+        <v>0.05102175602657194</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09048597404045049</v>
+        <v>-0.1021414042917724</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1063699450084145</v>
+        <v>0.09786020418836856</v>
       </c>
       <c r="F24" t="n">
-        <v>0.874341614386674</v>
+        <v>0.966534848204692</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.04275887538360301</v>
+        <v>0.03377723702718433</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02899531241893925</v>
+        <v>0.02826966249252102</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01407089267800488</v>
+        <v>-0.02163028331325968</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09958864344521089</v>
+        <v>0.08918475736762835</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1402979641274832</v>
+        <v>0.2321562739706974</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01702773825292627</v>
+        <v>0.01185029725512772</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03628839344655833</v>
+        <v>0.03531972237812558</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05409620595914739</v>
+        <v>-0.05737508654995181</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08815168246499994</v>
+        <v>0.08107568106020725</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6389025774131449</v>
+        <v>0.7372366186039921</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04776265836687567</v>
+        <v>0.0471000185492244</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03631243242202281</v>
+        <v>0.03670272747213624</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02340840137133361</v>
+        <v>-0.02483600543055146</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1189337181050849</v>
+        <v>0.1190360425290003</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1884006237939557</v>
+        <v>0.1993926378384793</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.03849528892250783</v>
+        <v>0.0279150995030522</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03513724130562727</v>
+        <v>0.03688860617765247</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.03037243855261475</v>
+        <v>-0.0443852400450284</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1073630163976304</v>
+        <v>0.1002154390511328</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2732672273052889</v>
+        <v>0.449205391031644</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005380707237649708</v>
+        <v>0.002028448287522428</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03555582911908338</v>
+        <v>0.03699514228435766</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06430743727621424</v>
+        <v>-0.07048069819275345</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07506885175151365</v>
+        <v>0.0745375947677983</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8797144375731925</v>
+        <v>0.9562737999639485</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.003320233432695015</v>
+        <v>-0.008532607932754623</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05015882681790457</v>
+        <v>0.04743349094085852</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1016297275025698</v>
+        <v>-0.1015005418378443</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09498926063717975</v>
+        <v>0.08443532597233501</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9472230553604772</v>
+        <v>0.8572422817678185</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0003007900296359803</v>
+        <v>-0.000439215948822769</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001948498754003048</v>
+        <v>0.001854819509338089</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004119777411403126</v>
+        <v>-0.004074595384947677</v>
       </c>
       <c r="E31" t="n">
-        <v>0.003518197352131165</v>
+        <v>0.00319616348730214</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8773178945520037</v>
+        <v>0.8128141730106142</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.009549274128434494</v>
+        <v>0.4341439838076169</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005236570244876932</v>
+        <v>0.01233167034636801</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.01981276321090737</v>
+        <v>0.409974354059515</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0007142149540383842</v>
+        <v>0.4583136135557188</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06821647769402626</v>
+        <v>1.640909443395484e-271</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.001543895502937996</v>
+        <v>0.0009410812065911153</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001581102582020395</v>
+        <v>0.001598281733026354</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004642799619561256</v>
+        <v>-0.0021914934272888</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001555008613685264</v>
+        <v>0.00407365584047103</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3288327776696813</v>
+        <v>0.5559900216047683</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4346917524144869</v>
+        <v>0.002599540092059315</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01226316783229009</v>
+        <v>0.005215369690511478</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4106563851268282</v>
+        <v>-0.00762239666740499</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4587271197021456</v>
+        <v>0.01282147685152362</v>
       </c>
       <c r="F34" t="n">
-        <v>3.23349566965761e-275</v>
+        <v>0.6181751351723382</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0002152465134243686</v>
+        <v>0.0001837898545406334</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001692811914196191</v>
+        <v>0.001724872936764039</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003102603871000474</v>
+        <v>-0.003196898979424718</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003533096897849211</v>
+        <v>0.003564478688505984</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8988191168516213</v>
+        <v>0.9151438512506984</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.58940947341988</v>
+        <v>-2.338987226254025</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5031045718144537</v>
+        <v>0.5055991410637884</v>
       </c>
       <c r="D2" t="n">
-        <v>2.648809631189163e-07</v>
+        <v>3.724908496211631e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04318498161254689</v>
+        <v>0.0125629325177608</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1065435099103227</v>
+        <v>0.1067715806898984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6852370218892514</v>
+        <v>0.9063356642598711</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3414291668173601</v>
+        <v>0.3234998731582306</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2253255698874617</v>
+        <v>0.2296824580519298</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1297039406487215</v>
+        <v>0.1589932049199888</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7562320294942516</v>
+        <v>0.773863427899792</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1748738694459631</v>
+        <v>0.1687469244012594</v>
       </c>
       <c r="D5" t="n">
-        <v>1.52917937368748e-05</v>
+        <v>4.519463710118189e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1784790633221359</v>
+        <v>-0.178376859680824</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2136767975499137</v>
+        <v>0.2079311667841182</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4035624257334062</v>
+        <v>0.3909670410803544</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1341634292941744</v>
+        <v>0.1377408491060987</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1953208674076419</v>
+        <v>0.1831232046369752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4921537310985461</v>
+        <v>0.4519453245419605</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09566226402322763</v>
+        <v>-0.09506786697132874</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2104081937814554</v>
+        <v>0.1943228459617254</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6493604462404067</v>
+        <v>0.6246814188469619</v>
       </c>
     </row>
     <row r="9">
@@ -2462,13 +2462,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.070551836763826</v>
+        <v>1.071572205240918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1703735435645065</v>
+        <v>0.1651060633318494</v>
       </c>
       <c r="D9" t="n">
-        <v>3.309132456524719e-10</v>
+        <v>8.571962941862197e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.09554047552828965</v>
+        <v>0.1122239612642839</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2825463042992074</v>
+        <v>0.283664263967282</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7352569730944816</v>
+        <v>0.6923835464094192</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2120911081526145</v>
+        <v>0.262235519870838</v>
       </c>
       <c r="C11" t="n">
-        <v>0.272397917742371</v>
+        <v>0.2783540080934925</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4362108592987907</v>
+        <v>0.3461447386877377</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.2444325881052889</v>
+        <v>-0.1888101216478684</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3070429002527493</v>
+        <v>0.3063764302491617</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4259819868592519</v>
+        <v>0.5377173713587766</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2496062680064459</v>
+        <v>0.3127315418553181</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2703388739718404</v>
+        <v>0.2741146153277002</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3558462903511507</v>
+        <v>0.2539203802608845</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2898175614664946</v>
+        <v>0.2705944435743411</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2803190610071123</v>
+        <v>0.2618702913171497</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011901132184945</v>
+        <v>0.3014566107781679</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3398205166536111</v>
+        <v>0.3028665560997517</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2686928948980213</v>
+        <v>0.2681769459926674</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2059727340404583</v>
+        <v>0.2587487663172114</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1269289753942515</v>
+        <v>0.1363845397670083</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2681297806792978</v>
+        <v>0.2557002711895599</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6359375739959043</v>
+        <v>0.5937729164140181</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1818641012766428</v>
+        <v>0.1940322365781458</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2752098117728791</v>
+        <v>0.2735957160328493</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5087278635920058</v>
+        <v>0.4782045582119642</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.386446959094826</v>
+        <v>0.4857181530086626</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2676140000451032</v>
+        <v>0.2539438750025451</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1487260018447586</v>
+        <v>0.05578661886604918</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.124440274708573</v>
+        <v>0.12210302869821</v>
       </c>
       <c r="C19" t="n">
-        <v>0.277836978266969</v>
+        <v>0.2803928791452478</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6542329221218868</v>
+        <v>0.6632204259123742</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2308101909230527</v>
+        <v>0.2579106665510232</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2780833406064969</v>
+        <v>0.280841715110821</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4065367134519926</v>
+        <v>0.3584362594442273</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2330335342161674</v>
+        <v>0.2543410650746326</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2673196819648357</v>
+        <v>0.2766729067347422</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3833496727885901</v>
+        <v>0.3579468768346228</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.05077438800389136</v>
+        <v>0.006839691327090455</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2847519964476453</v>
+        <v>0.2924114759179854</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8584788100921641</v>
+        <v>0.9813386718121045</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01709893916197886</v>
+        <v>-0.0747669407486906</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2925638244712255</v>
+        <v>0.2923674493803827</v>
       </c>
       <c r="D23" t="n">
-        <v>0.95339404475358</v>
+        <v>0.7981598227109667</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8751793875051906</v>
+        <v>0.8922385821553231</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1599839947303407</v>
+        <v>0.1585806900026265</v>
       </c>
       <c r="D24" t="n">
-        <v>4.489744023837655e-08</v>
+        <v>1.840081150019075e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5929479835845771</v>
+        <v>-0.5774441439879955</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1169096769872893</v>
+        <v>0.1158769831635338</v>
       </c>
       <c r="D25" t="n">
-        <v>3.939732815876656e-07</v>
+        <v>6.25246141790553e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1383512112984195</v>
+        <v>-0.1485372199650263</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1508106992062233</v>
+        <v>0.1534302542675076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3589418401519312</v>
+        <v>0.3329899032073049</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08371120214432404</v>
+        <v>-0.08883446031032122</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1573755377854197</v>
+        <v>0.1507497724290648</v>
       </c>
       <c r="D27" t="n">
-        <v>0.594781377860979</v>
+        <v>0.5556706364059282</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1111753607446196</v>
+        <v>-0.05597729137794842</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1482387657619015</v>
+        <v>0.1541767646161665</v>
       </c>
       <c r="D28" t="n">
-        <v>0.453269792676027</v>
+        <v>0.7165509786784028</v>
       </c>
     </row>
     <row r="29">
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3186427171078557</v>
+        <v>-0.3669690670720733</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1545279196022677</v>
+        <v>0.1613874819745223</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03920394898235133</v>
+        <v>0.02297569956216923</v>
       </c>
     </row>
     <row r="30">
@@ -2798,29 +2798,29 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01286655354973574</v>
+        <v>-0.01284483543314756</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008184547747939083</v>
+        <v>0.008409368149555611</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1159379568008997</v>
+        <v>0.1266507454755506</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01865810867195043</v>
+        <v>0.02286123471747232</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02286606432621095</v>
+        <v>0.05080677610550075</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4145151389219831</v>
+        <v>0.65273619274109</v>
       </c>
     </row>
     <row r="32">
@@ -2830,29 +2830,29 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002589705940363019</v>
+        <v>0.007242589222325571</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007293744184584137</v>
+        <v>0.006273236664278045</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7225457586062485</v>
+        <v>0.2482862581653684</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01704998181899496</v>
+        <v>-0.01746478001170591</v>
       </c>
       <c r="C33" t="n">
-        <v>0.04993149462297854</v>
+        <v>0.02279409042051461</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7327516797914978</v>
+        <v>0.4435586673664934</v>
       </c>
     </row>
     <row r="34">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01479837462877072</v>
+        <v>0.01392592672011598</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007085296655765528</v>
+        <v>0.006893603746700839</v>
       </c>
       <c r="D34" t="n">
-        <v>0.03674343959712725</v>
+        <v>0.04337064213536444</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.018</v>
+        <v>0.024</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E6" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.015</v>
+        <v>0.369</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.013</v>
+        <v>0.36</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.024</v>
+        <v>-0.388</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004</v>
+        <v>-0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.358</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.045</v>
+        <v>0.003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.038</v>
+        <v>0.002</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.369</v>
+        <v>0.036</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.36</v>
+        <v>0.028</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.216</v>
+        <v>-0.095</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.059</v>
+        <v>0.015</v>
       </c>
       <c r="E11" t="n">
-        <v>0.157</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.183</v>
+        <v>0.008</v>
       </c>
       <c r="D12" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="E12" t="n">
-        <v>0.174</v>
+        <v>0.002</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.015</v>
+        <v>-0.082</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.026</v>
+        <v>-0.028</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.011</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.075</v>
+        <v>0.035</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005</v>
+        <v>0.022</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.035</v>
+        <v>-0.183</v>
       </c>
       <c r="D15" t="n">
-        <v>0.022</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.013</v>
+        <v>0.174</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.011</v>
+        <v>-0.216</v>
       </c>
       <c r="D16" t="n">
-        <v>0.003</v>
+        <v>-0.059</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.157</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="D17" t="n">
-        <v>0.017</v>
+        <v>0.003</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.008</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.008</v>
+        <v>-0.015</v>
       </c>
       <c r="D18" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.117</v>
+        <v>-0.015</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.004</v>
+        <v>-0.026</v>
       </c>
       <c r="E19" t="n">
-        <v>0.113</v>
+        <v>-0.011</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.19</v>
+        <v>-0.117</v>
       </c>
       <c r="D20" t="n">
-        <v>0.025</v>
+        <v>-0.004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.165</v>
+        <v>0.113</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="E21" t="n">
-        <v>0.028</v>
+        <v>0.038</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.095</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.015</v>
+        <v>-0.029</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08</v>
+        <v>0.042</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.35</v>
+        <v>-0.031</v>
       </c>
       <c r="D23" t="n">
-        <v>0.018</v>
+        <v>-0.005</v>
       </c>
       <c r="E23" t="n">
-        <v>0.332</v>
+        <v>0.026</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.003</v>
+        <v>0.075</v>
       </c>
       <c r="D24" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.029</v>
+        <v>-0.018</v>
       </c>
       <c r="E25" t="n">
-        <v>0.042</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.388</v>
+        <v>0.02</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.03</v>
+        <v>0.003</v>
       </c>
       <c r="E27" t="n">
-        <v>0.358</v>
+        <v>0.017</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.036</v>
+        <v>0.19</v>
       </c>
       <c r="D28" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="E28" t="n">
-        <v>0.017</v>
+        <v>0.165</v>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.031</v>
+        <v>-0.018</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.008</v>
+        <v>0.35</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.018</v>
+        <v>0.018</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.332</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D31" t="n">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="E31" t="n">
-        <v>0.017</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.082</v>
+        <v>0.036</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.028</v>
+        <v>0.019</v>
       </c>
       <c r="E32" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1397,13 +1397,13 @@
         <v>0.1659290743085242</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858369290792679</v>
+        <v>1.858369290792677</v>
       </c>
       <c r="F2" t="n">
         <v>1.165474339027959</v>
       </c>
       <c r="G2" t="n">
-        <v>1.856659647949909</v>
+        <v>1.856659647949908</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.91628664450469</v>
+        <v>1.916286644504689</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1135774763851162</v>
+        <v>0.1135774763851138</v>
       </c>
       <c r="D2" t="n">
-        <v>1.693678881334913</v>
+        <v>1.693678881334918</v>
       </c>
       <c r="E2" t="n">
-        <v>2.138894407674466</v>
+        <v>2.138894407674461</v>
       </c>
       <c r="F2" t="n">
-        <v>7.222578944580643e-64</v>
+        <v>7.222578944537179e-64</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1492,13 +1492,13 @@
         <v>-0.01050744562892867</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02313482841481903</v>
+        <v>0.02313482841481902</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05585087611048783</v>
+        <v>-0.05585087611048782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03483598485263049</v>
+        <v>0.03483598485263048</v>
       </c>
       <c r="F3" t="n">
         <v>0.6496971222641865</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03640287469709135</v>
+        <v>-0.03640287469709131</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05763586703459977</v>
+        <v>0.05763586703459975</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1493670983026463</v>
+        <v>-0.1493670983026462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07656134890846356</v>
+        <v>0.07656134890846358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5276475939331993</v>
+        <v>0.5276475939331997</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1542,16 +1542,16 @@
         <v>-0.01048610640451848</v>
       </c>
       <c r="C5" t="n">
-        <v>0.038138687678579</v>
+        <v>0.03813868767857897</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08523656067215485</v>
+        <v>-0.08523656067215478</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06426434786311788</v>
+        <v>0.06426434786311781</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7833571861041335</v>
+        <v>0.7833571861041332</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001511275113782383</v>
+        <v>-0.001511275113782342</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04211864645461955</v>
+        <v>0.04211864645461957</v>
       </c>
       <c r="D6" t="n">
         <v>-0.08406230524241233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08103975501484757</v>
+        <v>0.08103975501484766</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9713769437607231</v>
+        <v>0.9713769437607239</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06364683252462018</v>
+        <v>-0.06364683252462017</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04016802682897487</v>
+        <v>0.04016802682897486</v>
       </c>
       <c r="D7" t="n">
         <v>-0.1423747184394495</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0150810533902092</v>
+        <v>0.01508105339020918</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1130766190665093</v>
+        <v>0.1130766190665092</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1617,16 +1617,16 @@
         <v>-0.06421840671360726</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04041046821576316</v>
+        <v>0.04041046821576312</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1434214690149036</v>
+        <v>-0.1434214690149035</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01498465558768911</v>
+        <v>0.01498465558768904</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1120259108770083</v>
+        <v>0.112025910877008</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02659716766236243</v>
+        <v>-0.02659716766236244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03890930153463092</v>
+        <v>0.0389093015346309</v>
       </c>
       <c r="D9" t="n">
         <v>-0.1028579973338481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04966366200912323</v>
+        <v>0.04966366200912317</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4942477661537689</v>
+        <v>0.4942477661537685</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.08243544392281288</v>
+        <v>-0.08243544392281296</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06337665689811482</v>
+        <v>0.06337665689811478</v>
       </c>
       <c r="D10" t="n">
         <v>-0.2066514089036699</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04178052105804415</v>
+        <v>0.04178052105804399</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1933534561005055</v>
+        <v>0.1933534561005047</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1692,16 +1692,16 @@
         <v>-0.1356569674250366</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06253796406675889</v>
+        <v>0.06253796406675879</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.258229124662344</v>
+        <v>-0.2582291246623439</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01308481018772907</v>
+        <v>-0.01308481018772932</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03006796939972239</v>
+        <v>0.03006796939972206</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1717,16 +1717,16 @@
         <v>-0.1007904685653378</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06371050484176445</v>
+        <v>0.06371050484176433</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2256607634920609</v>
+        <v>-0.2256607634920607</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02407982636138521</v>
+        <v>0.02407982636138498</v>
       </c>
       <c r="F12" t="n">
-        <v>0.113647958400898</v>
+        <v>0.1136479584008973</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006633880711504745</v>
+        <v>-0.006633880711504852</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06033231536084682</v>
+        <v>0.06033231536084661</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1248830459226772</v>
+        <v>-0.1248830459226769</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1116152844996677</v>
+        <v>0.1116152844996672</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9124445246059475</v>
+        <v>0.9124445246059457</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04852525054058572</v>
+        <v>-0.04852525054058577</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0611500934678508</v>
+        <v>0.06115009346785072</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1683772313888313</v>
+        <v>-0.1683772313888312</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07132673030765986</v>
+        <v>0.07132673030765965</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4274613181377229</v>
+        <v>0.4274613181377219</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1427721540964335</v>
+        <v>-0.1427721540964336</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0649788575039197</v>
+        <v>0.06497885750391966</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2701283745606763</v>
+        <v>-0.2701283745606764</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01541593363219068</v>
+        <v>-0.01541593363219082</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02800549722683545</v>
+        <v>0.02800549722683524</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09890443698017597</v>
+        <v>-0.09890443698017599</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05966171038444367</v>
+        <v>0.05966171038444365</v>
       </c>
       <c r="D16" t="n">
         <v>-0.2158392405897449</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01803036662939297</v>
+        <v>0.0180303666293929</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09736713642719769</v>
+        <v>0.09736713642719751</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08736850131641766</v>
+        <v>-0.08736850131641771</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06144897675671657</v>
+        <v>0.06144897675671648</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.207806282646421</v>
+        <v>-0.2078062826464209</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03306928001358571</v>
+        <v>0.03306928001358549</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1550826837763973</v>
+        <v>0.1550826837763965</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06583221967935282</v>
+        <v>-0.06583221967935284</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06142509279704658</v>
+        <v>0.0614250927970466</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1862231893085948</v>
+        <v>-0.1862231893085949</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05455874994988917</v>
+        <v>0.0545587499498892</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2838332398704615</v>
+        <v>0.2838332398704616</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03558523015264689</v>
+        <v>-0.03558523015264693</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06209835410094819</v>
+        <v>0.06209835410094822</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1572957676897205</v>
+        <v>-0.1572957676897206</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08612530738442672</v>
+        <v>0.08612530738442674</v>
       </c>
       <c r="F19" t="n">
-        <v>0.566613366003584</v>
+        <v>0.5666133660035837</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08036967353394857</v>
+        <v>-0.08036967353394858</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06209993601337664</v>
+        <v>0.06209993601337647</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2020833115624087</v>
+        <v>-0.2020833115624083</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04134396449451151</v>
+        <v>0.04134396449451118</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1955967007635262</v>
+        <v>0.1955967007635249</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0849242913998821</v>
+        <v>-0.08492429139988221</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06272335023210078</v>
+        <v>0.06272335023210063</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2078597988444917</v>
+        <v>-0.2078597988444915</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03801121604472747</v>
+        <v>0.03801121604472706</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1757522723372715</v>
+        <v>0.1757522723372701</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.04976148596577818</v>
+        <v>-0.04976148596577821</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06616872223007148</v>
+        <v>0.06616872223007156</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1794497984397531</v>
+        <v>-0.1794497984397533</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07992682650819677</v>
+        <v>0.07992682650819691</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4520273669320789</v>
+        <v>0.4520273669320792</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07216349561442487</v>
+        <v>-0.07216349561442491</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06023148981336583</v>
+        <v>0.06023148981336574</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.190215046383813</v>
+        <v>-0.1902150463838129</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0458880551549633</v>
+        <v>0.04588805515496308</v>
       </c>
       <c r="F23" t="n">
-        <v>0.230877134522401</v>
+        <v>0.2308771345223999</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.002140600051701904</v>
+        <v>-0.002140600051701927</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05102175602657194</v>
+        <v>0.05102175602657195</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1021414042917724</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09786020418836856</v>
+        <v>0.09786020418836855</v>
       </c>
       <c r="F24" t="n">
-        <v>0.966534848204692</v>
+        <v>0.9665348482046917</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03377723702718433</v>
+        <v>0.03377723702718432</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02826966249252102</v>
+        <v>0.02826966249252098</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02163028331325968</v>
+        <v>-0.02163028331325962</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08918475736762835</v>
+        <v>0.08918475736762826</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2321562739706974</v>
+        <v>0.232156273970697</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01185029725512772</v>
+        <v>0.01185029725512765</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03531972237812558</v>
+        <v>0.03531972237812556</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05737508654995181</v>
+        <v>-0.05737508654995183</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08107568106020725</v>
+        <v>0.08107568106020713</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7372366186039921</v>
+        <v>0.7372366186039934</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0471000185492244</v>
+        <v>0.04710001854922439</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03670272747213624</v>
+        <v>0.03670272747213621</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02483600543055146</v>
+        <v>-0.0248360054305514</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1190360425290003</v>
+        <v>0.1190360425290002</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1993926378384793</v>
+        <v>0.1993926378384789</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0279150995030522</v>
+        <v>0.02791509950305223</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03688860617765247</v>
+        <v>0.03688860617765243</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0443852400450284</v>
+        <v>-0.04438524004502829</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1002154390511328</v>
+        <v>0.1002154390511327</v>
       </c>
       <c r="F28" t="n">
-        <v>0.449205391031644</v>
+        <v>0.4492053910316429</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002028448287522428</v>
+        <v>0.002028448287522435</v>
       </c>
       <c r="C29" t="n">
         <v>0.03699514228435766</v>
@@ -2148,10 +2148,10 @@
         <v>-0.07048069819275345</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0745375947677983</v>
+        <v>0.07453759476779832</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9562737999639485</v>
+        <v>0.9562737999639482</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.008532607932754623</v>
+        <v>-0.008532607932754597</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04743349094085852</v>
+        <v>0.0474334909408585</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1015005418378443</v>
+        <v>-0.1015005418378442</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08443532597233501</v>
+        <v>0.08443532597233498</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8572422817678185</v>
+        <v>0.8572422817678189</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.000439215948822769</v>
+        <v>0.002599540092059323</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001854819509338089</v>
+        <v>0.005215369690511485</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004074595384947677</v>
+        <v>-0.007622396667404996</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00319616348730214</v>
+        <v>0.01282147685152364</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8128141730106142</v>
+        <v>0.6181751351723377</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2217,16 +2217,16 @@
         <v>0.4341439838076169</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01233167034636801</v>
+        <v>0.01233167034636804</v>
       </c>
       <c r="D32" t="n">
         <v>0.409974354059515</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4583136135557188</v>
+        <v>0.4583136135557189</v>
       </c>
       <c r="F32" t="n">
-        <v>1.640909443395484e-271</v>
+        <v>1.640909443400152e-271</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0009410812065911153</v>
+        <v>-0.0004392159488227687</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001598281733026354</v>
+        <v>0.001854819509338078</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0021914934272888</v>
+        <v>-0.004074595384947656</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00407365584047103</v>
+        <v>0.003196163487302118</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5559900216047683</v>
+        <v>0.8128141730106133</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.002599540092059315</v>
+        <v>0.0009410812065911193</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005215369690511478</v>
+        <v>0.001598281733026356</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00762239666740499</v>
+        <v>-0.002191493427288801</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01282147685152362</v>
+        <v>0.00407365584047104</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6181751351723382</v>
+        <v>0.5559900216047673</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0001837898545406334</v>
+        <v>0.0001837898545406331</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001724872936764039</v>
+        <v>0.001724872936764036</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003196898979424718</v>
+        <v>-0.003196898979424712</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003564478688505984</v>
+        <v>0.003564478688505978</v>
       </c>
       <c r="F35" t="n">
         <v>0.9151438512506984</v>
@@ -2353,10 +2353,10 @@
         <v>-2.338987226254025</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5055991410637884</v>
+        <v>0.5055991410637978</v>
       </c>
       <c r="D2" t="n">
-        <v>3.724908496211631e-06</v>
+        <v>3.724908496213204e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0125629325177608</v>
+        <v>0.01256293251776085</v>
       </c>
       <c r="C3" t="n">
         <v>0.1067715806898984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9063356642598711</v>
+        <v>0.9063356642598708</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3234998731582306</v>
+        <v>0.3234998731582308</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2296824580519298</v>
+        <v>0.2296824580519299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589932049199888</v>
+        <v>0.1589932049199887</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.773863427899792</v>
+        <v>0.7738634278997921</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1687469244012594</v>
+        <v>0.1687469244012597</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519463710118189e-06</v>
+        <v>4.519463710118297e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.178376859680824</v>
+        <v>-0.1783768596808243</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2079311667841182</v>
+        <v>0.2079311667841183</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3909670410803544</v>
+        <v>0.3909670410803541</v>
       </c>
     </row>
     <row r="7">
@@ -2436,7 +2436,7 @@
         <v>0.1831232046369752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4519453245419605</v>
+        <v>0.4519453245419603</v>
       </c>
     </row>
     <row r="8">
@@ -2449,10 +2449,10 @@
         <v>-0.09506786697132874</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943228459617254</v>
+        <v>0.1943228459617253</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6246814188469619</v>
+        <v>0.6246814188469618</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.071572205240918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651060633318494</v>
+        <v>0.1651060633318497</v>
       </c>
       <c r="D9" t="n">
-        <v>8.571962941862197e-11</v>
+        <v>8.571962941862631e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1122239612642839</v>
+        <v>0.1122239612642833</v>
       </c>
       <c r="C10" t="n">
-        <v>0.283664263967282</v>
+        <v>0.2836642639672833</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6923835464094192</v>
+        <v>0.6923835464094221</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.262235519870838</v>
+        <v>0.2622355198708376</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2783540080934925</v>
+        <v>0.2783540080934938</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3461447386877377</v>
+        <v>0.3461447386877406</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1888101216478684</v>
+        <v>-0.1888101216478686</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3063764302491617</v>
+        <v>0.3063764302491637</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5377173713587766</v>
+        <v>0.5377173713587788</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3127315418553181</v>
+        <v>0.3127315418553179</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2741146153277002</v>
+        <v>0.2741146153277014</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2539203802608845</v>
+        <v>0.253920380260887</v>
       </c>
     </row>
     <row r="14">
@@ -2545,10 +2545,10 @@
         <v>0.2705944435743411</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2618702913171497</v>
+        <v>0.2618702913171512</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3014566107781679</v>
+        <v>0.3014566107781707</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3028665560997517</v>
+        <v>0.3028665560997512</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681769459926674</v>
+        <v>0.2681769459926689</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2587487663172114</v>
+        <v>0.2587487663172148</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1363845397670083</v>
+        <v>0.1363845397670079</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2557002711895599</v>
+        <v>0.2557002711895606</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5937729164140181</v>
+        <v>0.5937729164140201</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1940322365781458</v>
+        <v>0.1940322365781457</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2735957160328493</v>
+        <v>0.2735957160328508</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4782045582119642</v>
+        <v>0.4782045582119668</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4857181530086626</v>
+        <v>0.4857181530086623</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2539438750025451</v>
+        <v>0.2539438750025471</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05578661886604918</v>
+        <v>0.0557866188660513</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.12210302869821</v>
+        <v>0.1221030286982098</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2803928791452478</v>
+        <v>0.2803928791452491</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6632204259123742</v>
+        <v>0.6632204259123764</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2579106665510232</v>
+        <v>0.257910666551023</v>
       </c>
       <c r="C20" t="n">
-        <v>0.280841715110821</v>
+        <v>0.2808417151108229</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3584362594442273</v>
+        <v>0.358436259444231</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2543410650746326</v>
+        <v>0.2543410650746324</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766729067347422</v>
+        <v>0.2766729067347433</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3579468768346228</v>
+        <v>0.3579468768346249</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006839691327090455</v>
+        <v>0.006839691327090229</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2924114759179854</v>
+        <v>0.2924114759179867</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9813386718121045</v>
+        <v>0.9813386718121052</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.0747669407486906</v>
+        <v>-0.07476694074869081</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2923674493803827</v>
+        <v>0.292367449380384</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7981598227109667</v>
+        <v>0.7981598227109671</v>
       </c>
     </row>
     <row r="24">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8922385821553231</v>
+        <v>0.892238582155323</v>
       </c>
       <c r="C24" t="n">
         <v>0.1585806900026265</v>
@@ -2724,7 +2724,7 @@
         <v>0.1158769831635338</v>
       </c>
       <c r="D25" t="n">
-        <v>6.25246141790553e-07</v>
+        <v>6.252461417905484e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1485372199650263</v>
+        <v>-0.148537219965026</v>
       </c>
       <c r="C26" t="n">
         <v>0.1534302542675076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3329899032073049</v>
+        <v>0.3329899032073059</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08883446031032122</v>
+        <v>-0.08883446031032111</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1507497724290648</v>
+        <v>0.1507497724290651</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5556706364059282</v>
+        <v>0.5556706364059293</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05597729137794842</v>
+        <v>-0.05597729137794841</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1541767646161665</v>
+        <v>0.1541767646161668</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7165509786784028</v>
+        <v>0.7165509786784033</v>
       </c>
     </row>
     <row r="29">
@@ -2782,29 +2782,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3669690670720733</v>
+        <v>-0.3669690670720732</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1613874819745223</v>
+        <v>0.1613874819745224</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02297569956216923</v>
+        <v>0.02297569956216942</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.01284483543314756</v>
+        <v>-0.0174647800117059</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008409368149555611</v>
+        <v>0.0227940904205145</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1266507454755506</v>
+        <v>0.4435586673664915</v>
       </c>
     </row>
     <row r="31">
@@ -2814,45 +2814,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.02286123471747232</v>
+        <v>0.02286123471747219</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05080677610550075</v>
+        <v>0.05080677610550104</v>
       </c>
       <c r="D31" t="n">
-        <v>0.65273619274109</v>
+        <v>0.6527361927410935</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.007242589222325571</v>
+        <v>-0.01284483543314755</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006273236664278045</v>
+        <v>0.008409368149555754</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2482862581653684</v>
+        <v>0.1266507454755573</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01746478001170591</v>
+        <v>0.007242589222325578</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02279409042051461</v>
+        <v>0.006273236664278017</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4435586673664934</v>
+        <v>0.248286258165366</v>
       </c>
     </row>
     <row r="34">
@@ -2865,10 +2865,10 @@
         <v>0.01392592672011598</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006893603746700839</v>
+        <v>0.00689360374670087</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04337064213536444</v>
+        <v>0.04337064213536546</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.082</v>
+        <v>0.035</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.028</v>
+        <v>0.022</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.045</v>
+        <v>-0.082</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007</v>
+        <v>-0.028</v>
       </c>
       <c r="E7" t="n">
-        <v>0.038</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.008</v>
+        <v>0.003</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.018</v>
+        <v>0.001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.002</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.031</v>
+        <v>0.024</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.005</v>
+        <v>0.004</v>
       </c>
       <c r="E9" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.117</v>
+        <v>-0.031</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="E10" t="n">
-        <v>0.113</v>
+        <v>0.026</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.19</v>
+        <v>0.045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
       <c r="E11" t="n">
-        <v>0.165</v>
+        <v>0.038</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.183</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="E12" t="n">
-        <v>0.174</v>
+        <v>0.042</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.036</v>
+        <v>-0.018</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="E14" t="n">
-        <v>0.028</v>
+        <v>0.013</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003</v>
+        <v>-0.008</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001</v>
+        <v>-0.018</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.075</v>
+        <v>-0.117</v>
       </c>
       <c r="D16" t="n">
-        <v>0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.018</v>
+        <v>0.036</v>
       </c>
       <c r="D17" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.013</v>
+        <v>0.028</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.015</v>
+        <v>0.35</v>
       </c>
       <c r="D18" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.332</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.35</v>
+        <v>0.011</v>
       </c>
       <c r="D20" t="n">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="E20" t="n">
-        <v>0.332</v>
+        <v>0.008</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.369</v>
+        <v>-0.183</v>
       </c>
       <c r="D21" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>0.36</v>
+        <v>0.174</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.029</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.042</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.388</v>
+        <v>0.02</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.03</v>
+        <v>0.003</v>
       </c>
       <c r="E23" t="n">
-        <v>0.358</v>
+        <v>0.017</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,10 +1077,10 @@
         <v>-0.015</v>
       </c>
       <c r="D24" t="n">
-        <v>0.002</v>
+        <v>-0.026</v>
       </c>
       <c r="E24" t="n">
-        <v>0.013</v>
+        <v>-0.011</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.216</v>
+        <v>0.19</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.059</v>
+        <v>0.025</v>
       </c>
       <c r="E25" t="n">
-        <v>0.157</v>
+        <v>0.165</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.024</v>
+        <v>-0.216</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004</v>
+        <v>-0.059</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02</v>
+        <v>0.157</v>
       </c>
       <c r="F26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.035</v>
+        <v>0.369</v>
       </c>
       <c r="D27" t="n">
-        <v>0.022</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.013</v>
+        <v>0.36</v>
       </c>
       <c r="F27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.036</v>
+        <v>-0.095</v>
       </c>
       <c r="D28" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="E28" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,10 +1212,10 @@
         <v>-0.015</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.026</v>
+        <v>0.002</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.011</v>
+        <v>0.013</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.099</v>
+        <v>0.075</v>
       </c>
       <c r="D30" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.095</v>
+        <v>-0.388</v>
       </c>
       <c r="D31" t="n">
-        <v>0.015</v>
+        <v>-0.03</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08</v>
+        <v>0.358</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="D32" t="n">
-        <v>0.003</v>
+        <v>0.019</v>
       </c>
       <c r="E32" t="n">
         <v>0.017</v>
@@ -1397,13 +1397,13 @@
         <v>0.1659290743085242</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858369290792677</v>
+        <v>1.858369290792679</v>
       </c>
       <c r="F2" t="n">
         <v>1.165474339027959</v>
       </c>
       <c r="G2" t="n">
-        <v>1.856659647949909</v>
+        <v>1.85665964794991</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.91628664450469</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1135774763851155</v>
+        <v>0.1135774763851172</v>
       </c>
       <c r="D2" t="n">
-        <v>1.693678881334915</v>
+        <v>1.693678881334912</v>
       </c>
       <c r="E2" t="n">
-        <v>2.138894407674464</v>
+        <v>2.138894407674468</v>
       </c>
       <c r="F2" t="n">
-        <v>7.222578944566633e-64</v>
+        <v>7.222578944598151e-64</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01050744562892867</v>
+        <v>-0.01050744562892865</v>
       </c>
       <c r="C3" t="n">
         <v>0.02313482841481903</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05585087611048783</v>
+        <v>-0.05585087611048782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03483598485263049</v>
+        <v>0.03483598485263052</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6496971222641869</v>
+        <v>0.6496971222641876</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03640287469709131</v>
+        <v>-0.03640287469709132</v>
       </c>
       <c r="C4" t="n">
         <v>0.05763586703459977</v>
@@ -1526,7 +1526,7 @@
         <v>0.07656134890846361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5276475939331999</v>
+        <v>0.5276475939331998</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01048610640451846</v>
+        <v>-0.01048610640451847</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03813868767857902</v>
+        <v>0.038138687678579</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08523656067215485</v>
+        <v>-0.08523656067215482</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06426434786311794</v>
+        <v>0.06426434786311788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.783357186104134</v>
+        <v>0.7833571861041336</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001511275113782287</v>
+        <v>-0.00151127511378226</v>
       </c>
       <c r="C6" t="n">
         <v>0.04211864645461957</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08406230524241229</v>
+        <v>-0.08406230524241226</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08103975501484773</v>
+        <v>0.08103975501484775</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9713769437607249</v>
+        <v>0.9713769437607255</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06364683252462019</v>
+        <v>-0.06364683252462018</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04016802682897489</v>
+        <v>0.04016802682897487</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1423747184394496</v>
+        <v>-0.1423747184394495</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01508105339020922</v>
+        <v>0.0150810533902092</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1130766190665095</v>
+        <v>0.1130766190665093</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06421840671360725</v>
+        <v>-0.06421840671360723</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04041046821576316</v>
+        <v>0.04041046821576317</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1434214690149036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01498465558768913</v>
+        <v>0.01498465558768916</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1120259108770085</v>
+        <v>0.1120259108770086</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02659716766236244</v>
+        <v>-0.02659716766236245</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03890930153463093</v>
+        <v>0.03890930153463094</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1028579973338481</v>
+        <v>-0.1028579973338482</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04966366200912323</v>
+        <v>0.04966366200912325</v>
       </c>
       <c r="F9" t="n">
         <v>0.4942477661537688</v>
@@ -1667,16 +1667,16 @@
         <v>-0.08243544392281284</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06337665689811482</v>
+        <v>0.06337665689811485</v>
       </c>
       <c r="D10" t="n">
         <v>-0.2066514089036699</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0417805210580442</v>
+        <v>0.04178052105804425</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1933534561005057</v>
+        <v>0.1933534561005059</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1692,16 +1692,16 @@
         <v>-0.1356569674250366</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06253796406675885</v>
+        <v>0.062537964066759</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.258229124662344</v>
+        <v>-0.2582291246623443</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01308481018772924</v>
+        <v>-0.01308481018772893</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03006796939972217</v>
+        <v>0.03006796939972257</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1717,16 +1717,16 @@
         <v>-0.1007904685653379</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06371050484176442</v>
+        <v>0.06371050484176448</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2256607634920609</v>
+        <v>-0.225660763492061</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02407982636138514</v>
+        <v>0.02407982636138523</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1136479584008977</v>
+        <v>0.113647958400898</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006633880711504859</v>
+        <v>-0.006633880711504809</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06033231536084677</v>
+        <v>0.06033231536084679</v>
       </c>
       <c r="D13" t="n">
         <v>-0.1248830459226772</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1116152844996675</v>
+        <v>0.1116152844996676</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9124445246059459</v>
+        <v>0.9124445246059466</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04852525054058585</v>
+        <v>-0.04852525054058566</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0611500934678508</v>
+        <v>0.06115009346785089</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1683772313888315</v>
+        <v>-0.1683772313888314</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07132673030765974</v>
+        <v>0.0713267303076601</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4274613181377217</v>
+        <v>0.4274613181377243</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1427721540964336</v>
+        <v>-0.1427721540964335</v>
       </c>
       <c r="C15" t="n">
         <v>0.06497885750391977</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2701283745606766</v>
+        <v>-0.2701283745606765</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01541593363219063</v>
+        <v>-0.01541593363219057</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02800549722683549</v>
+        <v>0.02800549722683557</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09890443698017604</v>
+        <v>-0.09890443698017601</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05966171038444369</v>
+        <v>0.0596617103844439</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.215839240589745</v>
+        <v>-0.2158392405897454</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01803036662939295</v>
+        <v>0.01803036662939338</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09736713642719758</v>
+        <v>0.09736713642719888</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08736850131641773</v>
+        <v>-0.08736850131641767</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06144897675671651</v>
+        <v>0.06144897675671666</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.207806282646421</v>
+        <v>-0.2078062826464212</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03306928001358553</v>
+        <v>0.03306928001358589</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1550826837763966</v>
+        <v>0.1550826837763979</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06583221967935282</v>
+        <v>-0.06583221967935278</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06142509279704649</v>
+        <v>0.06142509279704667</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1862231893085946</v>
+        <v>-0.1862231893085949</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05455874994988899</v>
+        <v>0.05455874994988938</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2838332398704608</v>
+        <v>0.2838332398704625</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03558523015264695</v>
+        <v>-0.03558523015264692</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06209835410094817</v>
+        <v>0.06209835410094828</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1572957676897205</v>
+        <v>-0.1572957676897207</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08612530738442661</v>
+        <v>0.08612530738442688</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5666133660035833</v>
+        <v>0.5666133660035843</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08036967353394864</v>
+        <v>-0.0803696735339486</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06209993601337659</v>
+        <v>0.0620999360133767</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2020833115624086</v>
+        <v>-0.2020833115624088</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04134396449451135</v>
+        <v>0.0413439644945116</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1955967007635255</v>
+        <v>0.1955967007635264</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.08492429139988221</v>
+        <v>-0.08492429139988217</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06272335023210077</v>
+        <v>0.06272335023210086</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2078597988444917</v>
+        <v>-0.2078597988444919</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03801121604472733</v>
+        <v>0.03801121604472757</v>
       </c>
       <c r="F21" t="n">
-        <v>0.175752272337271</v>
+        <v>0.1757522723372719</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.04976148596577828</v>
+        <v>-0.04976148596577829</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06616872223007154</v>
+        <v>0.06616872223007161</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1794497984397534</v>
+        <v>-0.1794497984397535</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0799268265081968</v>
+        <v>0.07992682650819694</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4520273669320783</v>
+        <v>0.4520273669320788</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07216349561442494</v>
+        <v>-0.07216349561442487</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06023148981336574</v>
+        <v>0.06023148981336585</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1902150463838129</v>
+        <v>-0.1902150463838131</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04588805515496305</v>
+        <v>0.04588805515496333</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2308771345223998</v>
+        <v>0.230877134522401</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.002140600051701965</v>
+        <v>-0.002140600051701931</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05102175602657193</v>
+        <v>0.05102175602657194</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1021414042917724</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09786020418836847</v>
+        <v>0.09786020418836854</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9665348482046912</v>
+        <v>0.9665348482046916</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03377723702718428</v>
+        <v>0.03377723702718432</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02826966249252097</v>
+        <v>0.02826966249252099</v>
       </c>
       <c r="D25" t="n">
         <v>-0.02163028331325964</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0891847573676282</v>
+        <v>0.08918475736762828</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2321562739706974</v>
+        <v>0.2321562739706973</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0118502972551276</v>
+        <v>0.01185029725512755</v>
       </c>
       <c r="C26" t="n">
         <v>0.03531972237812556</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05737508654995188</v>
+        <v>-0.05737508654995192</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08107568106020707</v>
+        <v>0.08107568106020703</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7372366186039944</v>
+        <v>0.7372366186039954</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04710001854922437</v>
+        <v>0.04710001854922439</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03670272747213622</v>
+        <v>0.03670272747213627</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02483600543055144</v>
+        <v>-0.02483600543055153</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1190360425290002</v>
+        <v>0.1190360425290003</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1993926378384792</v>
+        <v>0.1993926378384797</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0279150995030522</v>
+        <v>0.02791509950305218</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03688860617765245</v>
+        <v>0.03688860617765249</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04438524004502835</v>
+        <v>-0.04438524004502846</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1002154390511327</v>
+        <v>0.1002154390511328</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4492053910316437</v>
+        <v>0.4492053910316445</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002028448287522409</v>
+        <v>0.002028448287522412</v>
       </c>
       <c r="C29" t="n">
         <v>0.03699514228435767</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.008532607932754718</v>
+        <v>-0.008532607932754725</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04743349094085851</v>
+        <v>0.04743349094085852</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1015005418378443</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08443532597233488</v>
+        <v>0.08443532597233491</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8572422817678169</v>
+        <v>0.8572422817678168</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2192,16 +2192,16 @@
         <v>0.4341439838076169</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01233167034636807</v>
+        <v>0.01233167034636812</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4099743540595149</v>
+        <v>0.4099743540595148</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4583136135557189</v>
+        <v>0.458313613555719</v>
       </c>
       <c r="F31" t="n">
-        <v>1.640909443405939e-271</v>
+        <v>1.640909443414154e-271</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0004392159488227707</v>
+        <v>-0.0004392159488227743</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001854819509338051</v>
+        <v>0.001854819509338084</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004074595384947605</v>
+        <v>-0.004074595384947673</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003196163487302064</v>
+        <v>0.003196163487302124</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8128141730106098</v>
+        <v>0.8128141730106115</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2239,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0001837898545406304</v>
+        <v>0.0001837898545406309</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001724872936764035</v>
+        <v>0.001724872936764037</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003196898979424713</v>
+        <v>-0.003196898979424715</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003564478688505974</v>
+        <v>0.003564478688505977</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9151438512506996</v>
+        <v>0.9151438512506994</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0009410812065911147</v>
+        <v>0.002599540092059302</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001598281733026356</v>
+        <v>0.005215369690511507</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.002191493427288804</v>
+        <v>-0.00762239666740506</v>
       </c>
       <c r="E34" t="n">
-        <v>0.004073655840471034</v>
+        <v>0.01282147685152366</v>
       </c>
       <c r="F34" t="n">
-        <v>0.555990021604769</v>
+        <v>0.6181751351723419</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.002599540092059322</v>
+        <v>0.0009410812065911181</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005215369690511499</v>
+        <v>0.001598281733026359</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.007622396667405024</v>
+        <v>-0.002191493427288808</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01282147685152367</v>
+        <v>0.004073655840471044</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6181751351723388</v>
+        <v>0.5559900216047686</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.338987226254024</v>
+        <v>-2.338987226254025</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5055991410637918</v>
+        <v>0.5055991410637762</v>
       </c>
       <c r="D2" t="n">
-        <v>3.724908496212245e-06</v>
+        <v>3.724908496209657e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01256293251776077</v>
+        <v>0.01256293251776087</v>
       </c>
       <c r="C3" t="n">
         <v>0.1067715806898984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9063356642598713</v>
+        <v>0.9063356642598706</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3234998731582306</v>
+        <v>0.3234998731582308</v>
       </c>
       <c r="C4" t="n">
         <v>0.2296824580519299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589932049199888</v>
+        <v>0.1589932049199886</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.773863427899792</v>
+        <v>0.7738634278997921</v>
       </c>
       <c r="C5" t="n">
         <v>0.1687469244012598</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519463710118381e-06</v>
+        <v>4.519463710118364e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1783768596808241</v>
+        <v>-0.178376859680824</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2079311667841183</v>
+        <v>0.2079311667841182</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3909670410803544</v>
+        <v>0.3909670410803545</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1377408491060986</v>
+        <v>0.1377408491060987</v>
       </c>
       <c r="C7" t="n">
         <v>0.1831232046369752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4519453245419608</v>
+        <v>0.4519453245419605</v>
       </c>
     </row>
     <row r="8">
@@ -2449,10 +2449,10 @@
         <v>-0.09506786697132887</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943228459617255</v>
+        <v>0.1943228459617254</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6246814188469617</v>
+        <v>0.6246814188469614</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.071572205240918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651060633318497</v>
+        <v>0.1651060633318495</v>
       </c>
       <c r="D9" t="n">
-        <v>8.571962941862759e-11</v>
+        <v>8.57196294186226e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1122239612642835</v>
+        <v>0.1122239612642839</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2836642639672833</v>
+        <v>0.2836642639672831</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6923835464094216</v>
+        <v>0.6923835464094203</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2622355198708377</v>
+        <v>0.2622355198708382</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2783540080934941</v>
+        <v>0.2783540080934933</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3461447386877412</v>
+        <v>0.3461447386877388</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1888101216478687</v>
+        <v>-0.1888101216478681</v>
       </c>
       <c r="C12" t="n">
-        <v>0.306376430249163</v>
+        <v>0.3063764302491623</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5377173713587777</v>
+        <v>0.537717371358778</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3127315418553178</v>
+        <v>0.3127315418553183</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2741146153277019</v>
+        <v>0.2741146153277012</v>
       </c>
       <c r="D13" t="n">
-        <v>0.253920380260888</v>
+        <v>0.2539203802608861</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2705944435743409</v>
+        <v>0.2705944435743417</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2618702913171503</v>
+        <v>0.2618702913171504</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3014566107781694</v>
+        <v>0.3014566107781683</v>
       </c>
     </row>
     <row r="15">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3028665560997513</v>
+        <v>0.3028665560997518</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681769459926689</v>
+        <v>0.2681769459926688</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2587487663172143</v>
+        <v>0.2587487663172137</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1363845397670079</v>
+        <v>0.1363845397670084</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2557002711895608</v>
+        <v>0.2557002711895604</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5937729164140206</v>
+        <v>0.5937729164140186</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1940322365781456</v>
+        <v>0.1940322365781461</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2735957160328507</v>
+        <v>0.2735957160328503</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4782045582119668</v>
+        <v>0.4782045582119651</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4857181530086623</v>
+        <v>0.4857181530086627</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2539438750025463</v>
+        <v>0.2539438750025458</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05578661886605048</v>
+        <v>0.05578661886604987</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1221030286982097</v>
+        <v>0.1221030286982102</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2803928791452491</v>
+        <v>0.2803928791452487</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6632204259123766</v>
+        <v>0.663220425912375</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.257910666551023</v>
+        <v>0.2579106665510233</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2808417151108216</v>
+        <v>0.280841715110822</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3584362594442287</v>
+        <v>0.3584362594442286</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2543410650746321</v>
+        <v>0.2543410650746327</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766729067347432</v>
+        <v>0.2766729067347429</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3579468768346254</v>
+        <v>0.3579468768346239</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006839691327090175</v>
+        <v>0.006839691327090862</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2924114759179862</v>
+        <v>0.2924114759179857</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9813386718121053</v>
+        <v>0.9813386718121034</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07476694074869106</v>
+        <v>-0.07476694074869042</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2923674493803828</v>
+        <v>0.2923674493803836</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7981598227109656</v>
+        <v>0.7981598227109677</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8922385821553231</v>
+        <v>0.892238582155323</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1585806900026265</v>
+        <v>0.1585806900026266</v>
       </c>
       <c r="D24" t="n">
-        <v>1.840081150019075e-08</v>
+        <v>1.840081150019112e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2718,13 +2718,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5774441439879955</v>
+        <v>-0.5774441439879956</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158769831635337</v>
+        <v>0.1158769831635338</v>
       </c>
       <c r="D25" t="n">
-        <v>6.252461417905463e-07</v>
+        <v>6.25246141790559e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1485372199650261</v>
+        <v>-0.1485372199650263</v>
       </c>
       <c r="C26" t="n">
         <v>0.1534302542675076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3329899032073057</v>
+        <v>0.3329899032073051</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08883446031032109</v>
+        <v>-0.08883446031032112</v>
       </c>
       <c r="C27" t="n">
-        <v>0.150749772429065</v>
+        <v>0.1507497724290651</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5556706364059293</v>
+        <v>0.5556706364059292</v>
       </c>
     </row>
     <row r="28">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05597729137794842</v>
+        <v>-0.05597729137794846</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1541767646161666</v>
+        <v>0.1541767646161667</v>
       </c>
       <c r="D28" t="n">
         <v>0.716550978678403</v>
@@ -2782,13 +2782,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3669690670720732</v>
+        <v>-0.3669690670720731</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1613874819745223</v>
+        <v>0.1613874819745224</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0229756995621693</v>
+        <v>0.02297569956216942</v>
       </c>
     </row>
     <row r="30">
@@ -2798,13 +2798,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.02286123471747222</v>
+        <v>0.02286123471747226</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05080677610550082</v>
+        <v>0.05080677610550098</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6527361927410917</v>
+        <v>0.6527361927410922</v>
       </c>
     </row>
     <row r="31">
@@ -2817,10 +2817,10 @@
         <v>-0.01284483543314758</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008409368149555639</v>
+        <v>0.008409368149555604</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1266507454755514</v>
+        <v>0.1266507454755499</v>
       </c>
     </row>
     <row r="32">
@@ -2836,39 +2836,39 @@
         <v>0.006893603746700861</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04337064213536521</v>
+        <v>0.04337064213536518</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.007242589222325576</v>
+        <v>-0.01746478001170591</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006273236664278018</v>
+        <v>0.02279409042051449</v>
       </c>
       <c r="D33" t="n">
-        <v>0.248286258165366</v>
+        <v>0.4435586673664911</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01746478001170588</v>
+        <v>0.007242589222325582</v>
       </c>
       <c r="C34" t="n">
-        <v>0.02279409042051461</v>
+        <v>0.006273236664278013</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4435586673664942</v>
+        <v>0.2482862581653653</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.035</v>
+        <v>-0.095</v>
       </c>
       <c r="D6" t="n">
-        <v>0.022</v>
+        <v>0.015</v>
       </c>
       <c r="E6" t="n">
-        <v>0.013</v>
+        <v>0.08</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.082</v>
+        <v>0.02</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.028</v>
+        <v>0.003</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.003</v>
+        <v>0.024</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.024</v>
+        <v>-0.216</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004</v>
+        <v>-0.059</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02</v>
+        <v>0.157</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.031</v>
+        <v>-0.008</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.005</v>
+        <v>-0.018</v>
       </c>
       <c r="E10" t="n">
-        <v>0.026</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.045</v>
+        <v>0.036</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="E11" t="n">
-        <v>0.038</v>
+        <v>0.017</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.082</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.029</v>
+        <v>-0.028</v>
       </c>
       <c r="E12" t="n">
-        <v>0.042</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.015</v>
+        <v>-0.117</v>
       </c>
       <c r="D13" t="n">
-        <v>0.017</v>
+        <v>-0.004</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.002000000000000002</v>
+        <v>0.113</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.018</v>
+        <v>-0.015</v>
       </c>
       <c r="D14" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="E14" t="n">
         <v>0.013</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.008</v>
+        <v>-0.015</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.018</v>
+        <v>-0.026</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.009999999999999998</v>
+        <v>-0.011</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.117</v>
+        <v>-0.031</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.004</v>
+        <v>-0.005</v>
       </c>
       <c r="E16" t="n">
-        <v>0.113</v>
+        <v>0.026</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="D17" t="n">
-        <v>0.008</v>
+        <v>0.022</v>
       </c>
       <c r="E17" t="n">
-        <v>0.028</v>
+        <v>0.013</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.35</v>
+        <v>0.008</v>
       </c>
       <c r="D18" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="E18" t="n">
-        <v>0.332</v>
+        <v>0.002</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.008</v>
+        <v>0.099</v>
       </c>
       <c r="D19" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.011</v>
+        <v>0.35</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003</v>
+        <v>0.018</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008</v>
+        <v>0.332</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.183</v>
+        <v>0.036</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="E21" t="n">
-        <v>0.174</v>
+        <v>0.028</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.099</v>
+        <v>0.045</v>
       </c>
       <c r="D22" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02</v>
+        <v>-0.388</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003</v>
+        <v>-0.03</v>
       </c>
       <c r="E23" t="n">
-        <v>0.017</v>
+        <v>0.358</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.015</v>
+        <v>-0.183</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.026</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.011</v>
+        <v>0.174</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.19</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.025</v>
+        <v>-0.029</v>
       </c>
       <c r="E25" t="n">
-        <v>0.165</v>
+        <v>0.042</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.216</v>
+        <v>0.369</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.059</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.157</v>
+        <v>0.36</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.369</v>
+        <v>0.011</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="E27" t="n">
-        <v>0.36</v>
+        <v>0.008</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.095</v>
+        <v>0.003</v>
       </c>
       <c r="D28" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08</v>
+        <v>0.002</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.015</v>
+        <v>0.015</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002</v>
+        <v>0.017</v>
       </c>
       <c r="E29" t="n">
-        <v>0.013</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.075</v>
+        <v>-0.018</v>
       </c>
       <c r="D30" t="n">
         <v>0.005</v>
       </c>
       <c r="E30" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.388</v>
+        <v>0.19</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.03</v>
+        <v>0.025</v>
       </c>
       <c r="E31" t="n">
-        <v>0.358</v>
+        <v>0.165</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.036</v>
+        <v>0.075</v>
       </c>
       <c r="D32" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="E32" t="n">
-        <v>0.017</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1397,13 +1397,13 @@
         <v>0.1659290743085242</v>
       </c>
       <c r="E2" t="n">
-        <v>1.858369290792679</v>
+        <v>1.858369290792678</v>
       </c>
       <c r="F2" t="n">
         <v>1.165474339027959</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85665964794991</v>
+        <v>1.856659647949909</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.91628664450469</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1135774763851172</v>
+        <v>0.1135774763851165</v>
       </c>
       <c r="D2" t="n">
-        <v>1.693678881334912</v>
+        <v>1.693678881334913</v>
       </c>
       <c r="E2" t="n">
-        <v>2.138894407674468</v>
+        <v>2.138894407674467</v>
       </c>
       <c r="F2" t="n">
-        <v>7.222578944598151e-64</v>
+        <v>7.222578944584555e-64</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01050744562892865</v>
+        <v>-0.01050744562892866</v>
       </c>
       <c r="C3" t="n">
         <v>0.02313482841481903</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05585087611048782</v>
+        <v>-0.05585087611048783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03483598485263052</v>
+        <v>0.03483598485263051</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6496971222641876</v>
+        <v>0.6496971222641871</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03640287469709132</v>
+        <v>-0.03640287469709135</v>
       </c>
       <c r="C4" t="n">
         <v>0.05763586703459977</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1493670983026462</v>
+        <v>-0.1493670983026463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07656134890846361</v>
+        <v>0.07656134890846358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5276475939331998</v>
+        <v>0.5276475939331995</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01048610640451847</v>
+        <v>-0.01048610640451849</v>
       </c>
       <c r="C5" t="n">
-        <v>0.038138687678579</v>
+        <v>0.03813868767857899</v>
       </c>
       <c r="D5" t="n">
         <v>-0.08523656067215482</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06426434786311788</v>
+        <v>0.06426434786311785</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7833571861041336</v>
+        <v>0.7833571861041332</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.00151127511378226</v>
+        <v>-0.001511275113782194</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04211864645461957</v>
+        <v>0.04211864645461955</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08406230524241226</v>
+        <v>-0.08406230524241216</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08103975501484775</v>
+        <v>0.08103975501484777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9713769437607255</v>
+        <v>0.9713769437607267</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.06364683252462018</v>
+        <v>-0.06364683252462017</v>
       </c>
       <c r="C7" t="n">
         <v>0.04016802682897487</v>
@@ -1598,10 +1598,10 @@
         <v>-0.1423747184394495</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0150810533902092</v>
+        <v>0.01508105339020921</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1130766190665093</v>
+        <v>0.1130766190665095</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06421840671360723</v>
+        <v>-0.06421840671360726</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04041046821576317</v>
+        <v>0.04041046821576315</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1434214690149036</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01498465558768916</v>
+        <v>0.01498465558768909</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1120259108770086</v>
+        <v>0.1120259108770083</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02659716766236245</v>
+        <v>-0.02659716766236246</v>
       </c>
       <c r="C9" t="n">
         <v>0.03890930153463094</v>
@@ -1648,10 +1648,10 @@
         <v>-0.1028579973338482</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04966366200912325</v>
+        <v>0.04966366200912323</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4942477661537688</v>
+        <v>0.4942477661537685</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.08243544392281284</v>
+        <v>-0.08243544392281291</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06337665689811485</v>
+        <v>0.06337665689811477</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2066514089036699</v>
+        <v>-0.2066514089036698</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04178052105804425</v>
+        <v>0.04178052105804402</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1933534561005059</v>
+        <v>0.1933534561005049</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1356569674250366</v>
+        <v>-0.1356569674250367</v>
       </c>
       <c r="C11" t="n">
-        <v>0.062537964066759</v>
+        <v>0.06253796406675889</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2582291246623443</v>
+        <v>-0.2582291246623442</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01308481018772893</v>
+        <v>-0.01308481018772921</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03006796939972257</v>
+        <v>0.03006796939972221</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1717,16 +1717,16 @@
         <v>-0.1007904685653379</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06371050484176448</v>
+        <v>0.06371050484176442</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.225660763492061</v>
+        <v>-0.2256607634920609</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02407982636138523</v>
+        <v>0.02407982636138509</v>
       </c>
       <c r="F12" t="n">
-        <v>0.113647958400898</v>
+        <v>0.1136479584008975</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006633880711504809</v>
+        <v>-0.006633880711504913</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06033231536084679</v>
+        <v>0.06033231536084671</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1248830459226772</v>
+        <v>-0.1248830459226771</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1116152844996676</v>
+        <v>0.1116152844996673</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9124445246059466</v>
+        <v>0.9124445246059452</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04852525054058566</v>
+        <v>-0.04852525054058594</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06115009346785089</v>
+        <v>0.06115009346785085</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1683772313888314</v>
+        <v>-0.1683772313888316</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0713267303076601</v>
+        <v>0.07132673030765974</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4274613181377243</v>
+        <v>0.4274613181377213</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1427721540964335</v>
+        <v>-0.1427721540964337</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06497885750391977</v>
+        <v>0.06497885750391974</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2701283745606765</v>
+        <v>-0.2701283745606766</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01541593363219057</v>
+        <v>-0.01541593363219074</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02800549722683557</v>
+        <v>0.02800549722683537</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09890443698017601</v>
+        <v>-0.09890443698017612</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0596617103844439</v>
+        <v>0.0596617103844438</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2158392405897454</v>
+        <v>-0.2158392405897453</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01803036662939338</v>
+        <v>0.01803036662939306</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09736713642719888</v>
+        <v>0.09736713642719785</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.08736850131641767</v>
+        <v>-0.0873685013164178</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06144897675671666</v>
+        <v>0.0614489767567166</v>
       </c>
       <c r="D17" t="n">
         <v>-0.2078062826464212</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03306928001358589</v>
+        <v>0.03306928001358564</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1550826837763979</v>
+        <v>0.155082683776397</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06583221967935278</v>
+        <v>-0.06583221967935289</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06142509279704667</v>
+        <v>0.06142509279704668</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1862231893085949</v>
+        <v>-0.1862231893085951</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05455874994988938</v>
+        <v>0.0545587499498893</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2838332398704625</v>
+        <v>0.2838332398704617</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03558523015264692</v>
+        <v>-0.03558523015264702</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06209835410094828</v>
+        <v>0.06209835410094822</v>
       </c>
       <c r="D19" t="n">
         <v>-0.1572957676897207</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08612530738442688</v>
+        <v>0.08612530738442667</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5666133660035843</v>
+        <v>0.5666133660035829</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0803696735339486</v>
+        <v>-0.08036967353394864</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0620999360133767</v>
+        <v>0.06209993601337668</v>
       </c>
       <c r="D20" t="n">
         <v>-0.2020833115624088</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0413439644945116</v>
+        <v>0.04134396449451153</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1955967007635264</v>
+        <v>0.1955967007635262</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.08492429139988217</v>
+        <v>-0.08492429139988233</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06272335023210086</v>
+        <v>0.06272335023210079</v>
       </c>
       <c r="D21" t="n">
         <v>-0.2078597988444919</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03801121604472757</v>
+        <v>0.03801121604472726</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1757522723372719</v>
+        <v>0.1757522723372706</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.04976148596577829</v>
+        <v>-0.04976148596577851</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06616872223007161</v>
+        <v>0.06616872223007157</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1794497984397535</v>
+        <v>-0.1794497984397536</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07992682650819694</v>
+        <v>0.07992682650819663</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4520273669320788</v>
+        <v>0.4520273669320766</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07216349561442487</v>
+        <v>-0.07216349561442496</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06023148981336585</v>
+        <v>0.06023148981336576</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1902150463838131</v>
+        <v>-0.190215046383813</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04588805515496333</v>
+        <v>0.04588805515496307</v>
       </c>
       <c r="F23" t="n">
-        <v>0.230877134522401</v>
+        <v>0.2308771345223998</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,16 +2014,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.002140600051701931</v>
+        <v>-0.002140600051701934</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05102175602657194</v>
+        <v>0.05102175602657195</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1021414042917724</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09786020418836854</v>
+        <v>0.09786020418836855</v>
       </c>
       <c r="F24" t="n">
         <v>0.9665348482046916</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03377723702718432</v>
+        <v>0.03377723702718437</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02826966249252099</v>
+        <v>0.02826966249252101</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02163028331325964</v>
+        <v>-0.02163028331325963</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08918475736762828</v>
+        <v>0.08918475736762838</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2321562739706973</v>
+        <v>0.2321562739706969</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01185029725512755</v>
+        <v>0.01185029725512754</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03531972237812556</v>
+        <v>0.03531972237812557</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05737508654995192</v>
+        <v>-0.05737508654995196</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08107568106020703</v>
+        <v>0.08107568106020704</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7372366186039954</v>
+        <v>0.7372366186039958</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04710001854922439</v>
+        <v>0.04710001854922437</v>
       </c>
       <c r="C27" t="n">
         <v>0.03670272747213627</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02791509950305218</v>
+        <v>0.02791509950305224</v>
       </c>
       <c r="C28" t="n">
         <v>0.03688860617765249</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04438524004502846</v>
+        <v>-0.04438524004502839</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1002154390511328</v>
+        <v>0.1002154390511329</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4492053910316445</v>
+        <v>0.4492053910316435</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002028448287522412</v>
+        <v>0.002028448287522394</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03699514228435767</v>
+        <v>0.03699514228435769</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07048069819275349</v>
+        <v>-0.07048069819275354</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07453759476779831</v>
+        <v>0.07453759476779834</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9562737999639488</v>
+        <v>0.9562737999639492</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.008532607932754725</v>
+        <v>-0.008532607932754689</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04743349094085852</v>
+        <v>0.0474334909408585</v>
       </c>
       <c r="D30" t="n">
         <v>-0.1015005418378443</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08443532597233491</v>
+        <v>0.08443532597233488</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8572422817678168</v>
+        <v>0.8572422817678174</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4341439838076169</v>
+        <v>0.4341439838076168</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01233167034636812</v>
+        <v>0.01233167034636806</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4099743540595148</v>
+        <v>0.4099743540595149</v>
       </c>
       <c r="E31" t="n">
-        <v>0.458313613555719</v>
+        <v>0.4583136135557188</v>
       </c>
       <c r="F31" t="n">
-        <v>1.640909443414154e-271</v>
+        <v>1.640909443404259e-271</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0004392159488227743</v>
+        <v>0.0001837898545406308</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001854819509338084</v>
+        <v>0.001724872936764038</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004074595384947673</v>
+        <v>-0.003196898979424717</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003196163487302124</v>
+        <v>0.003564478688505979</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8128141730106115</v>
+        <v>0.9151438512506995</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0001837898545406309</v>
+        <v>0.002599540092059321</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001724872936764037</v>
+        <v>0.005215369690511481</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.003196898979424715</v>
+        <v>-0.007622396667404991</v>
       </c>
       <c r="E33" t="n">
-        <v>0.003564478688505977</v>
+        <v>0.01282147685152363</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9151438512506994</v>
+        <v>0.6181751351723377</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.002599540092059302</v>
+        <v>-0.0004392159488227686</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005215369690511507</v>
+        <v>0.001854819509338072</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00762239666740506</v>
+        <v>-0.004074595384947644</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01282147685152366</v>
+        <v>0.003196163487302108</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6181751351723419</v>
+        <v>0.8128141730106128</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0009410812065911181</v>
+        <v>0.0009410812065911139</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001598281733026359</v>
+        <v>0.001598281733026353</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.002191493427288808</v>
+        <v>-0.0021914934272888</v>
       </c>
       <c r="E35" t="n">
-        <v>0.004073655840471044</v>
+        <v>0.004073655840471029</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5559900216047686</v>
+        <v>0.5559900216047687</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.338987226254025</v>
+        <v>-2.338987226254024</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5055991410637762</v>
+        <v>0.5055991410638138</v>
       </c>
       <c r="D2" t="n">
-        <v>3.724908496209657e-06</v>
+        <v>3.724908496215856e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01256293251776087</v>
+        <v>0.01256293251776086</v>
       </c>
       <c r="C3" t="n">
         <v>0.1067715806898984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9063356642598706</v>
+        <v>0.9063356642598707</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3234998731582308</v>
+        <v>0.3234998731582306</v>
       </c>
       <c r="C4" t="n">
         <v>0.2296824580519299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589932049199886</v>
+        <v>0.158993204919989</v>
       </c>
     </row>
     <row r="5">
@@ -2401,10 +2401,10 @@
         <v>0.7738634278997921</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1687469244012598</v>
+        <v>0.16874692440126</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519463710118364e-06</v>
+        <v>4.519463710118472e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.178376859680824</v>
+        <v>-0.1783768596808243</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2079311667841182</v>
+        <v>0.2079311667841184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3909670410803545</v>
+        <v>0.3909670410803542</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1377408491060987</v>
+        <v>0.1377408491060986</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1831232046369752</v>
+        <v>0.1831232046369754</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4519453245419605</v>
+        <v>0.4519453245419613</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09506786697132887</v>
+        <v>-0.09506786697132875</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1943228459617254</v>
+        <v>0.1943228459617256</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6246814188469614</v>
+        <v>0.6246814188469623</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.071572205240918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651060633318495</v>
+        <v>0.1651060633318498</v>
       </c>
       <c r="D9" t="n">
-        <v>8.57196294186226e-11</v>
+        <v>8.57196294186304e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1122239612642839</v>
+        <v>0.1122239612642838</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2836642639672831</v>
+        <v>0.2836642639672838</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6923835464094203</v>
+        <v>0.6923835464094215</v>
       </c>
     </row>
     <row r="11">
@@ -2497,10 +2497,10 @@
         <v>0.2622355198708382</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2783540080934933</v>
+        <v>0.2783540080934942</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3461447386877388</v>
+        <v>0.3461447386877404</v>
       </c>
     </row>
     <row r="12">
@@ -2513,10 +2513,10 @@
         <v>-0.1888101216478681</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3063764302491623</v>
+        <v>0.3063764302491628</v>
       </c>
       <c r="D12" t="n">
-        <v>0.537717371358778</v>
+        <v>0.5377173713587788</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3127315418553183</v>
+        <v>0.3127315418553182</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2741146153277012</v>
+        <v>0.2741146153277016</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2539203802608861</v>
+        <v>0.2539203802608869</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2705944435743417</v>
+        <v>0.2705944435743414</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2618702913171504</v>
+        <v>0.2618702913171513</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3014566107781683</v>
+        <v>0.3014566107781703</v>
       </c>
     </row>
     <row r="15">
@@ -2561,10 +2561,10 @@
         <v>0.3028665560997518</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681769459926688</v>
+        <v>0.2681769459926692</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2587487663172137</v>
+        <v>0.2587487663172143</v>
       </c>
     </row>
     <row r="16">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1363845397670084</v>
+        <v>0.1363845397670083</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2557002711895604</v>
+        <v>0.2557002711895612</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5937729164140186</v>
+        <v>0.59377291641402</v>
       </c>
     </row>
     <row r="17">
@@ -2593,10 +2593,10 @@
         <v>0.1940322365781461</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2735957160328503</v>
+        <v>0.2735957160328507</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4782045582119651</v>
+        <v>0.4782045582119657</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4857181530086627</v>
+        <v>0.4857181530086626</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2539438750025458</v>
+        <v>0.2539438750025466</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05578661886604987</v>
+        <v>0.05578661886605062</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1221030286982102</v>
+        <v>0.1221030286982103</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2803928791452487</v>
+        <v>0.2803928791452494</v>
       </c>
       <c r="D19" t="n">
-        <v>0.663220425912375</v>
+        <v>0.6632204259123754</v>
       </c>
     </row>
     <row r="20">
@@ -2641,10 +2641,10 @@
         <v>0.2579106665510233</v>
       </c>
       <c r="C20" t="n">
-        <v>0.280841715110822</v>
+        <v>0.2808417151108225</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3584362594442286</v>
+        <v>0.3584362594442296</v>
       </c>
     </row>
     <row r="21">
@@ -2657,10 +2657,10 @@
         <v>0.2543410650746327</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766729067347429</v>
+        <v>0.2766729067347437</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3579468768346239</v>
+        <v>0.3579468768346251</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006839691327090862</v>
+        <v>0.006839691327090471</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2924114759179857</v>
+        <v>0.2924114759179866</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9813386718121034</v>
+        <v>0.9813386718121045</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07476694074869042</v>
+        <v>-0.07476694074869057</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2923674493803836</v>
+        <v>0.2923674493803833</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7981598227109677</v>
+        <v>0.7981598227109672</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.892238582155323</v>
+        <v>0.8922385821553229</v>
       </c>
       <c r="C24" t="n">
         <v>0.1585806900026266</v>
       </c>
       <c r="D24" t="n">
-        <v>1.840081150019112e-08</v>
+        <v>1.840081150019105e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2721,10 +2721,10 @@
         <v>-0.5774441439879956</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1158769831635338</v>
+        <v>0.1158769831635337</v>
       </c>
       <c r="D25" t="n">
-        <v>6.25246141790559e-07</v>
+        <v>6.252461417905323e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1485372199650263</v>
+        <v>-0.148537219965026</v>
       </c>
       <c r="C26" t="n">
         <v>0.1534302542675076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3329899032073051</v>
+        <v>0.332989903207306</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08883446031032112</v>
+        <v>-0.08883446031032097</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1507497724290651</v>
+        <v>0.150749772429065</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5556706364059292</v>
+        <v>0.5556706364059296</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.05597729137794846</v>
+        <v>-0.05597729137794832</v>
       </c>
       <c r="C28" t="n">
         <v>0.1541767646161667</v>
       </c>
       <c r="D28" t="n">
-        <v>0.716550978678403</v>
+        <v>0.7165509786784037</v>
       </c>
     </row>
     <row r="29">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3669690670720731</v>
+        <v>-0.366969067072073</v>
       </c>
       <c r="C29" t="n">
         <v>0.1613874819745224</v>
@@ -2798,61 +2798,61 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.02286123471747226</v>
+        <v>0.02286123471747216</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05080677610550098</v>
+        <v>0.05080677610550113</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6527361927410922</v>
+        <v>0.6527361927410945</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01284483543314758</v>
+        <v>0.01392592672011598</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008409368149555604</v>
+        <v>0.006893603746700875</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1266507454755499</v>
+        <v>0.04337064213536566</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01392592672011598</v>
+        <v>-0.01746478001170591</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006893603746700861</v>
+        <v>0.02279409042051463</v>
       </c>
       <c r="D32" t="n">
-        <v>0.04337064213536518</v>
+        <v>0.443558667366494</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01746478001170591</v>
+        <v>-0.01284483543314758</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02279409042051449</v>
+        <v>0.008409368149555781</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4435586673664911</v>
+        <v>0.1266507454755577</v>
       </c>
     </row>
     <row r="34">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.007242589222325582</v>
+        <v>0.00724258922232557</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006273236664278013</v>
+        <v>0.006273236664278007</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2482862581653653</v>
+        <v>0.2482862581653656</v>
       </c>
     </row>
   </sheetData>

--- a/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.011</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.029</v>
+        <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.042</v>
+        <v>0.008</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.095</v>
+        <v>-0.008</v>
       </c>
       <c r="D7" t="n">
-        <v>0.015</v>
+        <v>-0.018</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08</v>
+        <v>-0.009999999999999998</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.369</v>
+        <v>-0.082</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.028</v>
       </c>
       <c r="E8" t="n">
-        <v>0.36</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.183</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="E9" t="n">
-        <v>0.174</v>
+        <v>0.042</v>
       </c>
       <c r="F9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="D10" t="n">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="E10" t="n">
-        <v>0.017</v>
+        <v>-0.002000000000000002</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.019</v>
+        <v>0.007</v>
       </c>
       <c r="E11" t="n">
-        <v>0.017</v>
+        <v>0.038</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="D12" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E12" t="n">
         <v>0.017</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.002000000000000002</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.008</v>
+        <v>-0.216</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006</v>
+        <v>-0.059</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002</v>
+        <v>0.157</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.216</v>
+        <v>-0.183</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.059</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.157</v>
+        <v>0.174</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.35</v>
+        <v>-0.015</v>
       </c>
       <c r="D15" t="n">
-        <v>0.018</v>
+        <v>-0.026</v>
       </c>
       <c r="E15" t="n">
-        <v>0.332</v>
+        <v>-0.011</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.082</v>
+        <v>0.003</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.028</v>
+        <v>0.001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,16 +885,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.117</v>
+        <v>0.075</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E17" t="n">
-        <v>0.113</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.011</v>
+        <v>0.035</v>
       </c>
       <c r="D18" t="n">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.19</v>
+        <v>0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="E19" t="n">
-        <v>0.165</v>
+        <v>0.002</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="D20" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02</v>
+        <v>0.028</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.099</v>
+        <v>-0.031</v>
       </c>
       <c r="D21" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09000000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.008</v>
+        <v>0.036</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.018</v>
+        <v>0.019</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.009999999999999998</v>
+        <v>0.017</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.388</v>
+        <v>0.19</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.03</v>
+        <v>0.025</v>
       </c>
       <c r="E23" t="n">
-        <v>0.358</v>
+        <v>0.165</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.031</v>
+        <v>-0.388</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.005</v>
+        <v>-0.03</v>
       </c>
       <c r="E25" t="n">
-        <v>0.026</v>
+        <v>0.358</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.003</v>
+        <v>0.369</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.002</v>
+        <v>0.36</v>
       </c>
       <c r="F26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,10 +1155,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.035</v>
+        <v>-0.015</v>
       </c>
       <c r="D27" t="n">
-        <v>0.022</v>
+        <v>0.002</v>
       </c>
       <c r="E27" t="n">
         <v>0.013</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.015</v>
+        <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="E28" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.036</v>
+        <v>-0.095</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="E29" t="n">
-        <v>0.028</v>
+        <v>0.08</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.045</v>
+        <v>0.099</v>
       </c>
       <c r="D30" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.038</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.015</v>
+        <v>-0.117</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.026</v>
+        <v>-0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.011</v>
+        <v>0.113</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.075</v>
+        <v>0.35</v>
       </c>
       <c r="D32" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.332</v>
       </c>
       <c r="F32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="b">
         <v>1</v>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.91628664450469</v>
+        <v>1.916286644504689</v>
       </c>
       <c r="C2" t="n">
         <v>0.1135774763851155</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01050744562892867</v>
+        <v>-0.01050744562892865</v>
       </c>
       <c r="C3" t="n">
         <v>0.02313482841481903</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05585087611048783</v>
+        <v>-0.05585087611048782</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03483598485263049</v>
+        <v>0.03483598485263052</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6496971222641867</v>
+        <v>0.6496971222641874</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03640287469709134</v>
+        <v>-0.03640287469709133</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05763586703459976</v>
+        <v>0.05763586703459977</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1493670983026462</v>
+        <v>-0.1493670983026463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07656134890846356</v>
+        <v>0.0765613489084636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5276475939331995</v>
+        <v>0.5276475939331997</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.01048610640451848</v>
+        <v>-0.01048610640451845</v>
       </c>
       <c r="C5" t="n">
         <v>0.03813868767857898</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08523656067215479</v>
+        <v>-0.08523656067215477</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06426434786311783</v>
+        <v>0.06426434786311788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7833571861041333</v>
+        <v>0.783357186104134</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001511275113782305</v>
+        <v>-0.001511275113782164</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04211864645461956</v>
+        <v>0.04211864645461955</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.08406230524241229</v>
+        <v>-0.08406230524241212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08103975501484767</v>
+        <v>0.08103975501484781</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9713769437607246</v>
+        <v>0.9713769437607273</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1592,13 +1592,13 @@
         <v>-0.06364683252462017</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04016802682897487</v>
+        <v>0.04016802682897488</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1423747184394495</v>
+        <v>-0.1423747184394496</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01508105339020921</v>
+        <v>0.01508105339020924</v>
       </c>
       <c r="F7" t="n">
         <v>0.1130766190665095</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.06421840671360723</v>
+        <v>-0.06421840671360725</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04041046821576315</v>
+        <v>0.04041046821576316</v>
       </c>
       <c r="D8" t="n">
         <v>-0.1434214690149036</v>
@@ -1642,13 +1642,13 @@
         <v>-0.02659716766236244</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03890930153463092</v>
+        <v>0.03890930153463094</v>
       </c>
       <c r="D9" t="n">
         <v>-0.1028579973338481</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04966366200912322</v>
+        <v>0.04966366200912324</v>
       </c>
       <c r="F9" t="n">
         <v>0.4942477661537688</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.08243544392281278</v>
+        <v>-0.08243544392281268</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06337665689811495</v>
+        <v>0.06337665689811475</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2066514089036701</v>
+        <v>-0.2066514089036696</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04178052105804449</v>
+        <v>0.04178052105804421</v>
       </c>
       <c r="F10" t="n">
-        <v>0.193353456100507</v>
+        <v>0.193353456100506</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1356569674250366</v>
+        <v>-0.1356569674250365</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06253796406675893</v>
+        <v>0.06253796406675886</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2582291246623442</v>
+        <v>-0.2582291246623439</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.01308481018772904</v>
+        <v>-0.01308481018772907</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03006796939972241</v>
+        <v>0.03006796939972239</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1717,16 +1717,16 @@
         <v>-0.1007904685653378</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06371050484176438</v>
+        <v>0.06371050484176433</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2256607634920607</v>
+        <v>-0.2256607634920606</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02407982636138513</v>
+        <v>0.02407982636138505</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1136479584008977</v>
+        <v>0.1136479584008975</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.006633880711504789</v>
+        <v>-0.00663388071150471</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06033231536084689</v>
+        <v>0.06033231536084676</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1248830459226774</v>
+        <v>-0.124883045922677</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1116152844996678</v>
+        <v>0.1116152844996676</v>
       </c>
       <c r="F13" t="n">
-        <v>0.912444524605947</v>
+        <v>0.9124445246059478</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1767,16 +1767,16 @@
         <v>-0.04852525054058562</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06115009346785094</v>
+        <v>0.06115009346785075</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1683772313888315</v>
+        <v>-0.1683772313888311</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07132673030766024</v>
+        <v>0.07132673030765987</v>
       </c>
       <c r="F14" t="n">
-        <v>0.427461318137725</v>
+        <v>0.4274613181377236</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1792,16 +1792,16 @@
         <v>-0.1427721540964335</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06497885750391988</v>
+        <v>0.06497885750391974</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2701283745606767</v>
+        <v>-0.2701283745606764</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01541593363219035</v>
+        <v>-0.01541593363219054</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02800549722683584</v>
+        <v>0.0280054972268356</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.09890443698017594</v>
+        <v>-0.09890443698017588</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05966171038444381</v>
+        <v>0.05966171038444359</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2158392405897451</v>
+        <v>-0.2158392405897447</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01803036662939327</v>
+        <v>0.01803036662939289</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09736713642719856</v>
+        <v>0.09736713642719751</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0873685013164177</v>
+        <v>-0.0873685013164176</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06144897675671667</v>
+        <v>0.06144897675671653</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2078062826464213</v>
+        <v>-0.2078062826464209</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03306928001358587</v>
+        <v>0.03306928001358568</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1550826837763979</v>
+        <v>0.1550826837763973</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06583221967935286</v>
+        <v>-0.06583221967935264</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06142509279704669</v>
+        <v>0.06142509279704656</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.186223189308595</v>
+        <v>-0.1862231893085946</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05455874994988934</v>
+        <v>0.05455874994988931</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2838332398704622</v>
+        <v>0.2838332398704627</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03558523015264693</v>
+        <v>-0.03558523015264684</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06209835410094836</v>
+        <v>0.06209835410094824</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1572957676897209</v>
+        <v>-0.1572957676897205</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08612530738442702</v>
+        <v>0.08612530738442688</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5666133660035846</v>
+        <v>0.566613366003585</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.08036967353394857</v>
+        <v>-0.08036967353394851</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06209993601337672</v>
+        <v>0.06209993601337665</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2020833115624088</v>
+        <v>-0.2020833115624086</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04134396449451166</v>
+        <v>0.04134396449451158</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1955967007635266</v>
+        <v>0.1955967007635265</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.08492429139988215</v>
+        <v>-0.0849242913998821</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06272335023210092</v>
+        <v>0.06272335023210075</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.207859798844492</v>
+        <v>-0.2078597988444916</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03801121604472768</v>
+        <v>0.03801121604472742</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1757522723372724</v>
+        <v>0.1757522723372713</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.04976148596577843</v>
+        <v>-0.04976148596577819</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0661687222300717</v>
+        <v>0.06616872223007157</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1794497984397538</v>
+        <v>-0.1794497984397533</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07992682650819696</v>
+        <v>0.07992682650819695</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4520273669320781</v>
+        <v>0.4520273669320795</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07216349561442485</v>
+        <v>-0.0721634956144248</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06023148981336584</v>
+        <v>0.06023148981336571</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.190215046383813</v>
+        <v>-0.1902150463838128</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04588805515496333</v>
+        <v>0.04588805515496315</v>
       </c>
       <c r="F23" t="n">
-        <v>0.230877134522401</v>
+        <v>0.2308771345224003</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.002140600051701927</v>
+        <v>-0.002140600051701947</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05102175602657195</v>
+        <v>0.05102175602657194</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1021414042917724</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09786020418836855</v>
+        <v>0.09786020418836852</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9665348482046917</v>
+        <v>0.9665348482046914</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.03377723702718431</v>
+        <v>0.03377723702718434</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02826966249252098</v>
+        <v>0.02826966249252101</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.02163028331325964</v>
+        <v>-0.02163028331325965</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08918475736762825</v>
+        <v>0.08918475736762832</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2321562739706973</v>
+        <v>0.2321562739706972</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01185029725512757</v>
+        <v>0.01185029725512762</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03531972237812558</v>
+        <v>0.03531972237812555</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05737508654995196</v>
+        <v>-0.05737508654995184</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0810756810602071</v>
+        <v>0.08107568106020709</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7372366186039951</v>
+        <v>0.7372366186039938</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.04710001854922434</v>
+        <v>0.04710001854922439</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03670272747213622</v>
+        <v>0.03670272747213626</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.02483600543055148</v>
+        <v>-0.0248360054305515</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1190360425290002</v>
+        <v>0.1190360425290003</v>
       </c>
       <c r="F27" t="n">
         <v>0.1993926378384795</v>
@@ -2117,16 +2117,16 @@
         <v>0.02791509950305224</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03688860617765245</v>
+        <v>0.03688860617765246</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04438524004502832</v>
+        <v>-0.04438524004502833</v>
       </c>
       <c r="E28" t="n">
         <v>0.1002154390511328</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4492053910316429</v>
+        <v>0.4492053910316431</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002028448287522432</v>
+        <v>0.002028448287522442</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03699514228435765</v>
+        <v>0.03699514228435766</v>
       </c>
       <c r="D29" t="n">
         <v>-0.07048069819275343</v>
       </c>
       <c r="E29" t="n">
-        <v>0.07453759476779828</v>
+        <v>0.07453759476779831</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9562737999639483</v>
+        <v>0.9562737999639481</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.008532607932754567</v>
+        <v>-0.008532607932754671</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04743349094085852</v>
+        <v>0.0474334909408585</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1015005418378442</v>
+        <v>-0.1015005418378443</v>
       </c>
       <c r="E30" t="n">
-        <v>0.08443532597233505</v>
+        <v>0.0844353259723349</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8572422817678194</v>
+        <v>0.8572422817678176</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0009410812065911163</v>
+        <v>0.4341439838076169</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001598281733026354</v>
+        <v>0.01233167034636797</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0021914934272888</v>
+        <v>0.4099743540595151</v>
       </c>
       <c r="E31" t="n">
-        <v>0.004073655840471033</v>
+        <v>0.4583136135557186</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5559900216047681</v>
+        <v>1.640909443389137e-271</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002599540092059309</v>
+        <v>0.0009410812065911157</v>
       </c>
       <c r="C32" t="n">
-        <v>0.005215369690511525</v>
+        <v>0.001598281733026355</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.007622396667405088</v>
+        <v>-0.002191493427288801</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01282147685152371</v>
+        <v>0.004073655840471033</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6181751351723421</v>
+        <v>0.5559900216047683</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4341439838076169</v>
+        <v>-0.0004392159488227705</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01233167034636802</v>
+        <v>0.001854819509338086</v>
       </c>
       <c r="D33" t="n">
-        <v>0.409974354059515</v>
+        <v>-0.004074595384947674</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4583136135557188</v>
+        <v>0.003196163487302133</v>
       </c>
       <c r="F33" t="n">
-        <v>1.640909443398472e-271</v>
+        <v>0.8128141730106134</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2260,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0004392159488227713</v>
+        <v>0.002599540092059329</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001854819509338099</v>
+        <v>0.005215369690511526</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004074595384947699</v>
+        <v>-0.007622396667405069</v>
       </c>
       <c r="E34" t="n">
-        <v>0.003196163487302156</v>
+        <v>0.01282147685152373</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8128141730106142</v>
+        <v>0.6181751351723395</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0001837898545406305</v>
+        <v>0.0001837898545406324</v>
       </c>
       <c r="C35" t="n">
-        <v>0.001724872936764038</v>
+        <v>0.001724872936764036</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.003196898979424717</v>
+        <v>-0.003196898979424713</v>
       </c>
       <c r="E35" t="n">
-        <v>0.003564478688505979</v>
+        <v>0.003564478688505978</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9151438512506996</v>
+        <v>0.9151438512506987</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2353,10 +2353,10 @@
         <v>-2.338987226254026</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5055991410638002</v>
+        <v>0.5055991410637954</v>
       </c>
       <c r="D2" t="n">
-        <v>3.724908496213564e-06</v>
+        <v>3.724908496212776e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01256293251776077</v>
+        <v>0.01256293251776092</v>
       </c>
       <c r="C3" t="n">
         <v>0.1067715806898984</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9063356642598713</v>
+        <v>0.9063356642598702</v>
       </c>
     </row>
     <row r="4">
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3234998731582304</v>
+        <v>0.3234998731582309</v>
       </c>
       <c r="C4" t="n">
         <v>0.2296824580519299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1589932049199891</v>
+        <v>0.1589932049199886</v>
       </c>
     </row>
     <row r="5">
@@ -2398,13 +2398,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.773863427899792</v>
+        <v>0.7738634278997921</v>
       </c>
       <c r="C5" t="n">
         <v>0.1687469244012597</v>
       </c>
       <c r="D5" t="n">
-        <v>4.519463710118322e-06</v>
+        <v>4.519463710118297e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1783768596808241</v>
+        <v>-0.1783768596808242</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2079311667841184</v>
+        <v>0.2079311667841183</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3909670410803546</v>
+        <v>0.3909670410803542</v>
       </c>
     </row>
     <row r="7">
@@ -2430,13 +2430,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1377408491060986</v>
+        <v>0.1377408491060987</v>
       </c>
       <c r="C7" t="n">
         <v>0.1831232046369752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4519453245419608</v>
+        <v>0.4519453245419603</v>
       </c>
     </row>
     <row r="8">
@@ -2446,13 +2446,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.09506786697132878</v>
+        <v>-0.09506786697132869</v>
       </c>
       <c r="C8" t="n">
         <v>0.1943228459617254</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6246814188469619</v>
+        <v>0.6246814188469623</v>
       </c>
     </row>
     <row r="9">
@@ -2465,10 +2465,10 @@
         <v>1.071572205240918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1651060633318495</v>
+        <v>0.1651060633318496</v>
       </c>
       <c r="D9" t="n">
-        <v>8.571962941862318e-11</v>
+        <v>8.571962941862477e-11</v>
       </c>
     </row>
     <row r="10">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1122239612642838</v>
+        <v>0.1122239612642844</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2836642639672835</v>
+        <v>0.2836642639672833</v>
       </c>
       <c r="D10" t="n">
-        <v>0.692383546409421</v>
+        <v>0.6923835464094192</v>
       </c>
     </row>
     <row r="11">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2622355198708383</v>
+        <v>0.2622355198708385</v>
       </c>
       <c r="C11" t="n">
-        <v>0.278354008093494</v>
+        <v>0.2783540080934929</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3461447386877399</v>
+        <v>0.3461447386877375</v>
       </c>
     </row>
     <row r="12">
@@ -2510,13 +2510,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.1888101216478681</v>
+        <v>-0.1888101216478676</v>
       </c>
       <c r="C12" t="n">
-        <v>0.306376430249163</v>
+        <v>0.3063764302491626</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5377173713587791</v>
+        <v>0.5377173713587795</v>
       </c>
     </row>
     <row r="13">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3127315418553183</v>
+        <v>0.3127315418553188</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2741146153277019</v>
+        <v>0.2741146153277013</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2539203802608874</v>
+        <v>0.2539203802608856</v>
       </c>
     </row>
     <row r="14">
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2705944435743414</v>
+        <v>0.2705944435743421</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2618702913171503</v>
+        <v>0.2618702913171512</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3014566107781685</v>
+        <v>0.3014566107781689</v>
       </c>
     </row>
     <row r="15">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.3028665560997519</v>
+        <v>0.3028665560997522</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2681769459926687</v>
+        <v>0.2681769459926689</v>
       </c>
       <c r="D15" t="n">
         <v>0.2587487663172132</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.1363845397670084</v>
+        <v>0.1363845397670087</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2557002711895613</v>
+        <v>0.2557002711895608</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5937729164140199</v>
+        <v>0.5937729164140184</v>
       </c>
     </row>
     <row r="17">
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1940322365781461</v>
+        <v>0.1940322365781466</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2735957160328512</v>
+        <v>0.2735957160328508</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4782045582119665</v>
+        <v>0.4782045582119647</v>
       </c>
     </row>
     <row r="18">
@@ -2606,13 +2606,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4857181530086626</v>
+        <v>0.4857181530086632</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2539438750025474</v>
+        <v>0.2539438750025463</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05578661886605148</v>
+        <v>0.05578661886605005</v>
       </c>
     </row>
     <row r="19">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1221030286982102</v>
+        <v>0.1221030286982105</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2803928791452489</v>
+        <v>0.2803928791452485</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6632204259123748</v>
+        <v>0.6632204259123737</v>
       </c>
     </row>
     <row r="20">
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2579106665510235</v>
+        <v>0.2579106665510238</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2808417151108231</v>
+        <v>0.2808417151108223</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3584362594442305</v>
+        <v>0.3584362594442284</v>
       </c>
     </row>
     <row r="21">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2543410650746326</v>
+        <v>0.2543410650746332</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2766729067347436</v>
+        <v>0.2766729067347429</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3579468768346252</v>
+        <v>0.3579468768346228</v>
       </c>
     </row>
     <row r="22">
@@ -2670,13 +2670,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006839691327090622</v>
+        <v>0.006839691327091045</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2924114759179859</v>
+        <v>0.2924114759179866</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9813386718121041</v>
+        <v>0.981338671812103</v>
       </c>
     </row>
     <row r="23">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07476694074869027</v>
+        <v>-0.0747669407486902</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2923674493803832</v>
+        <v>0.2923674493803834</v>
       </c>
       <c r="D23" t="n">
-        <v>0.798159822710968</v>
+        <v>0.7981598227109683</v>
       </c>
     </row>
     <row r="24">
@@ -2702,13 +2702,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8922385821553231</v>
+        <v>0.892238582155323</v>
       </c>
       <c r="C24" t="n">
         <v>0.1585806900026265</v>
       </c>
       <c r="D24" t="n">
-        <v>1.840081150019075e-08</v>
+        <v>1.840081150019068e-08</v>
       </c>
     </row>
     <row r="25">
@@ -2724,7 +2724,7 @@
         <v>0.1158769831635338</v>
       </c>
       <c r="D25" t="n">
-        <v>6.252461417905612e-07</v>
+        <v>6.252461417905484e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2734,13 +2734,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1485372199650264</v>
+        <v>-0.1485372199650259</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1534302542675077</v>
+        <v>0.1534302542675076</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3329899032073051</v>
+        <v>0.3329899032073064</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.08883446031032111</v>
+        <v>-0.088834460310321</v>
       </c>
       <c r="C27" t="n">
         <v>0.150749772429065</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5556706364059292</v>
+        <v>0.5556706364059296</v>
       </c>
     </row>
     <row r="28">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0559772913779484</v>
+        <v>-0.0559772913779483</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1541767646161667</v>
+        <v>0.1541767646161666</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7165509786784032</v>
+        <v>0.7165509786784037</v>
       </c>
     </row>
     <row r="29">
@@ -2782,77 +2782,77 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3669690670720732</v>
+        <v>-0.3669690670720731</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1613874819745222</v>
+        <v>0.1613874819745223</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02297569956216924</v>
+        <v>0.02297569956216935</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.00724258922232558</v>
+        <v>0.02286123471747233</v>
       </c>
       <c r="C30" t="n">
-        <v>0.006273236664278034</v>
+        <v>0.0508067761055007</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2482862581653671</v>
+        <v>0.6527361927410893</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01746478001170589</v>
+        <v>0.007242589222325582</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02279409042051449</v>
+        <v>0.006273236664278014</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4435586673664915</v>
+        <v>0.2482862581653653</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.02286123471747234</v>
+        <v>-0.01284483543314755</v>
       </c>
       <c r="C32" t="n">
-        <v>0.05080677610550093</v>
+        <v>0.008409368149555585</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6527361927410906</v>
+        <v>0.1266507454755496</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01284483543314756</v>
+        <v>-0.01746478001170591</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008409368149555702</v>
+        <v>0.02279409042051469</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1266507454755547</v>
+        <v>0.4435586673664952</v>
       </c>
     </row>
     <row r="34">
@@ -2865,10 +2865,10 @@
         <v>0.01392592672011598</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006893603746700875</v>
+        <v>0.006893603746700866</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04337064213536566</v>
+        <v>0.04337064213536541</v>
       </c>
     </row>
   </sheetData>
